--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE3532FA-BE92-4023-9A81-5244BEC5320B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BDB9639-7B91-45C1-9168-BF3772F66969}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Instructions" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Minutes of Meeting-'!$A$3:$H$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Minutes of Meeting-'!$A$3:$H$41</definedName>
     <definedName name="Status">Instructions!$A$3:$A$5</definedName>
   </definedNames>
   <calcPr calcId="191028" concurrentCalc="0"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="212">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -145,10 +145,7 @@
  </t>
   </si>
   <si>
-    <t>06.12.2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer,Dominik Bisslich,Henrik Schmielau, Seah Qiao Ling</t>
+    <t>13.09.2024</t>
   </si>
   <si>
     <t xml:space="preserve">Introduction, Presention </t>
@@ -157,46 +154,35 @@
     <t>All</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam: Maybe you can send the ball mill ontology; Also use a Logo – e.g. the one from Alica was nice                                                                  -- did you include in the ontology a class related to health impact from the ball mill and how to mitigate the health risks         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjara: Thank you very much. I would be really interested to see your ontology. Maybe you can send it to us                                                        - did you include how the music app an entity regarding the business model? How the app generate income        </t>
-  </si>
-  <si>
-    <t>Alica: Maybe you can send the ontology, The Project / Task text is a bit dark you may update. Maybe add a Wikipdia link to cowpea 
-- did you think of adding a class to the ontology related to the- waste which comes out of the machine so that this waste could be used e.g. as food for animal or to create fertilizers or biofuel e.g.</t>
-  </si>
-  <si>
-    <t>Charles: Please name you main topic: Maybe you can send me your ontology; Also use a Logo – e.g. the one from Alica was nice 
-did you include a class related to saving water in your irrigation system? Fresh water</t>
-  </si>
-  <si>
-    <t>Lucas: Maybe you can send me your smart dryer ontology; Also use a Logo – e.g. the one from Alica was is a nice one 
- did you add a class in the drowling related to the fruit/vegetal supplier? Local farmers e.g.</t>
-  </si>
-  <si>
-    <t>Boris: Maybe you can send me your Face recognition ontology; Also use a better Logo - – e.g. the one from Alica was is nice one 
- did you consider accuracy of the face recognition solution? also Privacy since you are collecting pictures of persons</t>
-  </si>
-  <si>
-    <t>Stephanie: Maybe you can send me your Solar ontology; The letter is Project/Task is not so good readable; maybe you use another (brighter color); you may also use the column “Updates”                                                              did you consider the suppliers of the inverters, batteries, ..etc.</t>
-  </si>
-  <si>
-    <t>Wilfried: Maybe you can send me your human language ontology; Also use a Logo – e.g. the one from Alica was is a nice one; you explained the ontology nicely 
-do you have a class regarding the output of the solar panel for comparison without solar tracking?</t>
-  </si>
-  <si>
-    <t>Hamado: Maybe you can send the Ne-Reesa and the English Ontology; Thanks for answering the question; Ontgology very well explained 
-a class about the accuracy of the translation and how to measure it in the app?</t>
+    <t xml:space="preserve">Mare: excellent presentation! Could you document the results in excel        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdoul: excellent presentation! Could you document the results in excel – could you also consider supplying other farm needs e.g. product transformation/drying process …    </t>
+  </si>
+  <si>
+    <t>Yannick: excellent presentation! Could you document the results in excel</t>
+  </si>
+  <si>
+    <t>Cedric: excellent presentation! Could you document the results in excel – excellent app for the inventory management, in the course of the project you could think how to link it the previous processes e.g. processing …etc.</t>
+  </si>
+  <si>
+    <t>Narcisse: had connection issues</t>
+  </si>
+  <si>
+    <t>Arcus: excellent presentation! Could you document the results in excel</t>
+  </si>
+  <si>
+    <t>Afiatou: could you make some examples of where the translation is need</t>
+  </si>
+  <si>
+    <t>Ange: excellent presentation! I like the ideas of biogas – are there any available data in BF or in Africa on getting biofuel as byproduct of such agricultural activity  -</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>two lines, visual of ontologie -&gt; two classes (nation:bf, institute (bit))</t>
-  </si>
-  <si>
-    <t>Hans</t>
+    <t xml:space="preserve">
+Fadila: please create an excel for the calculation of the farm/system size with a sheet for every topic e.g. farm, product processing and share it with the others.</t>
   </si>
   <si>
     <t>13.12.2024</t>
@@ -295,6 +281,9 @@
 Maybe you can be shorter in the presentation and only talk about what we also see on the homepage. 
 We have to stay within the 30’ and ideal would be 15’ presentation; 10’ feedback and 5 minutes free flow of information</t>
     </r>
+  </si>
+  <si>
+    <t>Hans</t>
   </si>
   <si>
     <t xml:space="preserve"> Hans Ehm,  Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer, Seah Qiao Ling, Tristan Scheuermann,James Cherupillet</t>
@@ -1720,6 +1709,24 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1744,28 +1751,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2660,16 +2649,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -2937,7 +2926,7 @@
       <c r="G14" s="19"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="43.5">
+    <row r="15" spans="1:8" ht="30.75">
       <c r="A15" s="9">
         <v>2</v>
       </c>
@@ -2945,7 +2934,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
@@ -2987,10 +2976,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>21</v>
@@ -3001,7 +2990,7 @@
       <c r="G17" s="20"/>
       <c r="H17" s="20"/>
     </row>
-    <row r="18" spans="1:8" ht="57.95">
+    <row r="18" spans="1:8" ht="30.75">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -3009,7 +2998,7 @@
         <v>23</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>25</v>
@@ -3021,7 +3010,7 @@
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
     </row>
-    <row r="19" spans="1:8" ht="57.95">
+    <row r="19" spans="1:8" ht="45.75">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3029,7 +3018,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>25</v>
@@ -3041,7 +3030,7 @@
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="1:8" ht="72.599999999999994">
+    <row r="20" spans="1:8" ht="30.75">
       <c r="A20" s="1">
         <v>4</v>
       </c>
@@ -3049,7 +3038,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>25</v>
@@ -3061,7 +3050,7 @@
       <c r="G20" s="20"/>
       <c r="H20" s="20"/>
     </row>
-    <row r="21" spans="1:8" ht="57.95">
+    <row r="21" spans="1:8" ht="60.75">
       <c r="A21" s="1">
         <v>5</v>
       </c>
@@ -3069,7 +3058,7 @@
         <v>23</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>25</v>
@@ -3081,7 +3070,7 @@
       <c r="G21" s="20"/>
       <c r="H21" s="20"/>
     </row>
-    <row r="22" spans="1:8" ht="57.95">
+    <row r="22" spans="1:8" ht="15">
       <c r="A22" s="1">
         <v>6</v>
       </c>
@@ -3089,7 +3078,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>25</v>
@@ -3101,7 +3090,7 @@
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8" ht="57.95">
+    <row r="23" spans="1:8" ht="30.75">
       <c r="A23" s="1">
         <v>7</v>
       </c>
@@ -3109,7 +3098,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>25</v>
@@ -3121,7 +3110,7 @@
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="57.95">
+    <row r="24" spans="1:8" ht="30.75">
       <c r="A24" s="1">
         <v>8</v>
       </c>
@@ -3129,7 +3118,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>25</v>
@@ -3141,7 +3130,7 @@
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
     </row>
-    <row r="25" spans="1:8" ht="72.599999999999994">
+    <row r="25" spans="1:8" ht="45.75">
       <c r="A25" s="1">
         <v>9</v>
       </c>
@@ -3149,7 +3138,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>25</v>
@@ -3161,12 +3150,12 @@
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
     </row>
-    <row r="26" spans="1:8" ht="57.95">
+    <row r="26" spans="1:8" ht="60.75">
       <c r="A26" s="1">
         <v>10</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>45</v>
@@ -3182,104 +3171,104 @@
       <c r="H26" s="20"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="1">
-        <v>11</v>
-      </c>
-      <c r="B27" s="19" t="s">
+      <c r="A27" s="9">
+        <v>3</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <v>1</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" ht="130.5">
+      <c r="A30" s="1">
+        <v>2</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="9">
-        <v>3</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="69" t="s">
+      <c r="D30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="1">
-        <v>1</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="4"/>
       <c r="F30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
     </row>
-    <row r="31" spans="1:8" ht="130.5">
+    <row r="31" spans="1:8" ht="72.599999999999994">
       <c r="A31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>22</v>
@@ -3289,19 +3278,19 @@
     </row>
     <row r="32" spans="1:8" ht="72.599999999999994">
       <c r="A32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>22</v>
@@ -3311,19 +3300,19 @@
     </row>
     <row r="33" spans="1:8" ht="72.599999999999994">
       <c r="A33" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>22</v>
@@ -3331,21 +3320,21 @@
       <c r="G33" s="20"/>
       <c r="H33" s="20"/>
     </row>
-    <row r="34" spans="1:8" ht="72.599999999999994">
+    <row r="34" spans="1:8" ht="116.1">
       <c r="A34" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>22</v>
@@ -3353,21 +3342,21 @@
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
     </row>
-    <row r="35" spans="1:8" ht="116.1">
+    <row r="35" spans="1:8" ht="57.95">
       <c r="A35" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>22</v>
@@ -3375,21 +3364,21 @@
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
     </row>
-    <row r="36" spans="1:8" ht="57.95">
+    <row r="36" spans="1:8" ht="72.599999999999994">
       <c r="A36" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>22</v>
@@ -3397,21 +3386,21 @@
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
     </row>
-    <row r="37" spans="1:8" ht="72.599999999999994">
+    <row r="37" spans="1:8" ht="87">
       <c r="A37" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>22</v>
@@ -3421,19 +3410,19 @@
     </row>
     <row r="38" spans="1:8" ht="87">
       <c r="A38" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>22</v>
@@ -3441,102 +3430,100 @@
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
     </row>
-    <row r="39" spans="1:8" ht="87">
+    <row r="39" spans="1:8" ht="160.5">
       <c r="A39" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>68</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="4" t="s">
         <v>69</v>
       </c>
+      <c r="E39" s="4"/>
       <c r="F39" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
     </row>
-    <row r="40" spans="1:8" ht="160.5">
-      <c r="A40" s="1">
-        <v>11</v>
-      </c>
-      <c r="B40" s="19" t="s">
+    <row r="40" spans="1:8">
+      <c r="A40" s="9">
+        <v>4</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1">
+        <v>1</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+    </row>
+    <row r="43" spans="1:8" ht="57.95">
+      <c r="A43" s="1">
+        <v>2</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="9">
-        <v>4</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="69" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="15"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="1">
-        <v>1</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="1" t="s">
@@ -3545,18 +3532,18 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
     </row>
-    <row r="44" spans="1:8" ht="57.95">
+    <row r="44" spans="1:8" ht="43.5">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="30" t="s">
-        <v>73</v>
+      <c r="C44" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="1" t="s">
@@ -3565,18 +3552,18 @@
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
     </row>
-    <row r="45" spans="1:8" ht="43.5">
+    <row r="45" spans="1:8" ht="57.95">
       <c r="A45" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="1" t="s">
@@ -3585,18 +3572,18 @@
       <c r="G45" s="20"/>
       <c r="H45" s="20"/>
     </row>
-    <row r="46" spans="1:8" ht="57.95">
+    <row r="46" spans="1:8" ht="43.5">
       <c r="A46" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="29" t="s">
-        <v>75</v>
+      <c r="C46" s="31" t="s">
+        <v>74</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="1" t="s">
@@ -3605,18 +3592,18 @@
       <c r="G46" s="20"/>
       <c r="H46" s="20"/>
     </row>
-    <row r="47" spans="1:8" ht="43.5">
+    <row r="47" spans="1:8" ht="57.95">
       <c r="A47" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="31" t="s">
-        <v>76</v>
+      <c r="C47" s="32" t="s">
+        <v>75</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="1" t="s">
@@ -3625,18 +3612,18 @@
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
     </row>
-    <row r="48" spans="1:8" ht="57.95">
+    <row r="48" spans="1:8" ht="43.5">
       <c r="A48" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="32" t="s">
-        <v>77</v>
+      <c r="C48" s="31" t="s">
+        <v>76</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="1" t="s">
@@ -3647,16 +3634,16 @@
     </row>
     <row r="49" spans="1:8" ht="43.5">
       <c r="A49" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="1" t="s">
@@ -3667,16 +3654,16 @@
     </row>
     <row r="50" spans="1:8" ht="43.5">
       <c r="A50" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="1" t="s">
@@ -3685,18 +3672,18 @@
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
     </row>
-    <row r="51" spans="1:8" ht="43.5">
+    <row r="51" spans="1:8" ht="57.95">
       <c r="A51" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="1" t="s">
@@ -3705,18 +3692,18 @@
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
     </row>
-    <row r="52" spans="1:8" ht="57.95">
+    <row r="52" spans="1:8" ht="159.6">
       <c r="A52" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="31" t="s">
-        <v>81</v>
+      <c r="C52" s="33" t="s">
+        <v>80</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="1" t="s">
@@ -3725,18 +3712,18 @@
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
     </row>
-    <row r="53" spans="1:8" ht="159.6">
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="1" t="s">
@@ -3746,163 +3733,163 @@
       <c r="H53" s="20"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="1">
-        <v>12</v>
-      </c>
-      <c r="B54" s="19" t="s">
+      <c r="A54" s="9">
+        <v>5</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="15"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <v>1</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="9">
-        <v>5</v>
-      </c>
-      <c r="B55" s="10" t="s">
+      <c r="C56" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+    </row>
+    <row r="57" spans="1:8" ht="304.5">
+      <c r="A57" s="1">
+        <v>2</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="D57" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="69"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="15"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="1">
-        <v>1</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E57" s="4"/>
+      <c r="E57" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="F57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="20"/>
     </row>
-    <row r="58" spans="1:8" ht="304.5">
-      <c r="A58" s="1">
+    <row r="58" spans="1:8">
+      <c r="A58" s="9">
+        <v>6</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="15"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1">
+        <v>1</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+    </row>
+    <row r="61" spans="1:8" ht="29.1">
+      <c r="A61" s="1">
         <v>2</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="B61" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="9">
-        <v>6</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="D59" s="69"/>
-      <c r="E59" s="69"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="15"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="1">
-        <v>1</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D61" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="1" t="s">
@@ -3911,18 +3898,18 @@
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8" ht="29.1">
+    <row r="62" spans="1:8" ht="57.95">
       <c r="A62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="30" t="s">
-        <v>91</v>
+      <c r="C62" s="29" t="s">
+        <v>90</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="1" t="s">
@@ -3931,18 +3918,18 @@
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63" spans="1:8" ht="57.95">
+    <row r="63" spans="1:8" ht="43.5">
       <c r="A63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C63" s="29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="1" t="s">
@@ -3951,18 +3938,18 @@
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64" spans="1:8" ht="43.5">
+    <row r="64" spans="1:8" ht="72.599999999999994">
       <c r="A64" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C64" s="29" t="s">
-        <v>93</v>
+      <c r="C64" s="31" t="s">
+        <v>92</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="1" t="s">
@@ -3971,18 +3958,18 @@
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="72.599999999999994">
+    <row r="65" spans="1:8" ht="43.5">
       <c r="A65" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="31" t="s">
-        <v>94</v>
+      <c r="C65" s="32" t="s">
+        <v>93</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="1" t="s">
@@ -3993,16 +3980,16 @@
     </row>
     <row r="66" spans="1:8" ht="43.5">
       <c r="A66" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C66" s="32" t="s">
-        <v>95</v>
+      <c r="C66" s="31" t="s">
+        <v>94</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="1" t="s">
@@ -4013,16 +4000,16 @@
     </row>
     <row r="67" spans="1:8" ht="43.5">
       <c r="A67" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="1" t="s">
@@ -4033,134 +4020,134 @@
     </row>
     <row r="68" spans="1:8" ht="43.5">
       <c r="A68" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E68" s="4"/>
-      <c r="F68" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F68" s="1"/>
       <c r="G68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69" spans="1:8" ht="43.5">
+    <row r="69" spans="1:8" ht="72.599999999999994">
       <c r="A69" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="1"/>
       <c r="G69" s="20"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70" spans="1:8" ht="72.599999999999994">
+    <row r="70" spans="1:8" ht="188.45">
       <c r="A70" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="1"/>
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
     </row>
-    <row r="71" spans="1:8" ht="188.45">
-      <c r="A71" s="1">
-        <v>11</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="31" t="s">
+    <row r="71" spans="1:8">
+      <c r="A71" s="9">
+        <v>7</v>
+      </c>
+      <c r="B71" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="C71" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" s="65"/>
+      <c r="E71" s="65"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1">
+        <v>1</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="9">
-        <v>7</v>
-      </c>
-      <c r="B72" s="10" t="s">
+      <c r="D73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+    </row>
+    <row r="74" spans="1:8" ht="72.599999999999994">
+      <c r="A74" s="1">
+        <v>2</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="15"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H73" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="1">
-        <v>1</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D74" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="1" t="s">
@@ -4169,18 +4156,18 @@
       <c r="G74" s="20"/>
       <c r="H74" s="20"/>
     </row>
-    <row r="75" spans="1:8" ht="72.599999999999994">
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C75" s="30" t="s">
-        <v>104</v>
+      <c r="C75" s="29" t="s">
+        <v>103</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="1" t="s">
@@ -4189,18 +4176,18 @@
       <c r="G75" s="20"/>
       <c r="H75" s="20"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" ht="43.5">
       <c r="A76" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="1" t="s">
@@ -4211,16 +4198,16 @@
     </row>
     <row r="77" spans="1:8" ht="43.5">
       <c r="A77" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C77" s="29" t="s">
-        <v>93</v>
+      <c r="C77" s="31" t="s">
+        <v>104</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="1" t="s">
@@ -4231,16 +4218,16 @@
     </row>
     <row r="78" spans="1:8" ht="43.5">
       <c r="A78" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="31" t="s">
-        <v>106</v>
+      <c r="C78" s="32" t="s">
+        <v>105</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="1" t="s">
@@ -4251,16 +4238,16 @@
     </row>
     <row r="79" spans="1:8" ht="43.5">
       <c r="A79" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C79" s="32" t="s">
-        <v>107</v>
+      <c r="C79" s="31" t="s">
+        <v>106</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="1" t="s">
@@ -4269,18 +4256,18 @@
       <c r="G79" s="20"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80" spans="1:8" ht="43.5">
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="1" t="s">
@@ -4289,136 +4276,136 @@
       <c r="G80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" ht="29.1">
       <c r="A81" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C81" s="31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E81" s="4"/>
-      <c r="F81" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F81" s="1"/>
       <c r="G81" s="20"/>
       <c r="H81" s="20"/>
     </row>
     <row r="82" spans="1:8" ht="29.1">
       <c r="A82" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="1"/>
       <c r="G82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" ht="29.1">
+    <row r="83" spans="1:8" ht="72.599999999999994">
       <c r="A83" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E83" s="4"/>
-      <c r="F83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="G83" s="20"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84" spans="1:8" ht="72.599999999999994">
-      <c r="A84" s="1">
-        <v>11</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C84" s="31" t="s">
+    <row r="84" spans="1:8">
+      <c r="A84" s="9">
+        <v>8</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="65"/>
+      <c r="E84" s="65"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="15"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1">
+        <v>1</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E84" s="4"/>
-      <c r="F84" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="9">
-        <v>8</v>
-      </c>
-      <c r="B85" s="10" t="s">
+      <c r="D86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+    </row>
+    <row r="87" spans="1:8" ht="72.599999999999994">
+      <c r="A87" s="1">
+        <v>2</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="C85" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" s="69"/>
-      <c r="E85" s="69"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="15"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G86" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H86" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="1">
-        <v>1</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D87" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="1" t="s">
@@ -4427,15 +4414,15 @@
       <c r="G87" s="20"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88" spans="1:8" ht="72.599999999999994">
+    <row r="88" spans="1:8" ht="57.95">
       <c r="A88" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C88" s="30" t="s">
-        <v>115</v>
+      <c r="C88" s="29" t="s">
+        <v>114</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>25</v>
@@ -4447,15 +4434,15 @@
       <c r="G88" s="20"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89" spans="1:8" ht="57.95">
+    <row r="89" spans="1:8" ht="76.5">
       <c r="A89" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="29" t="s">
-        <v>116</v>
+      <c r="C89" s="31" t="s">
+        <v>115</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>25</v>
@@ -4467,15 +4454,15 @@
       <c r="G89" s="20"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90" spans="1:8" ht="76.5">
+    <row r="90" spans="1:8" ht="72.599999999999994">
       <c r="A90" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C90" s="31" t="s">
-        <v>117</v>
+      <c r="C90" s="32" t="s">
+        <v>116</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>25</v>
@@ -4487,15 +4474,15 @@
       <c r="G90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91" spans="1:8" ht="72.599999999999994">
+    <row r="91" spans="1:8" ht="87">
       <c r="A91" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B91" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C91" s="32" t="s">
-        <v>118</v>
+      <c r="C91" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>25</v>
@@ -4509,13 +4496,13 @@
     </row>
     <row r="92" spans="1:8" ht="87">
       <c r="A92" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B92" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>25</v>
@@ -4527,35 +4514,33 @@
       <c r="G92" s="20"/>
       <c r="H92" s="20"/>
     </row>
-    <row r="93" spans="1:8" ht="87">
+    <row r="93" spans="1:8" ht="57.95">
       <c r="A93" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B93" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E93" s="4"/>
-      <c r="F93" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F93" s="1"/>
       <c r="G93" s="20"/>
       <c r="H93" s="20"/>
     </row>
-    <row r="94" spans="1:8" ht="57.95">
+    <row r="94" spans="1:8" ht="106.5">
       <c r="A94" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B94" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>25</v>
@@ -4565,80 +4550,82 @@
       <c r="G94" s="20"/>
       <c r="H94" s="20"/>
     </row>
-    <row r="95" spans="1:8" ht="106.5">
-      <c r="A95" s="1">
+    <row r="95" spans="1:8" s="37" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A95" s="35">
         <v>9</v>
       </c>
-      <c r="B95" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" s="31" t="s">
+      <c r="B95" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="69"/>
+      <c r="E95" s="70"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="15"/>
+    </row>
+    <row r="96" spans="1:8" s="37" customFormat="1" ht="15.75">
+      <c r="A96" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="16.5">
+      <c r="A97" s="40">
+        <v>1</v>
+      </c>
+      <c r="B97" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="42"/>
+      <c r="F97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="20"/>
+      <c r="H97" s="20"/>
+    </row>
+    <row r="98" spans="1:8" ht="46.5">
+      <c r="A98" s="43">
+        <v>2</v>
+      </c>
+      <c r="B98" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D98" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
-    </row>
-    <row r="96" spans="1:8" s="37" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A96" s="35">
-        <v>9</v>
-      </c>
-      <c r="B96" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="C96" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="D96" s="63"/>
-      <c r="E96" s="64"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="14"/>
-      <c r="H96" s="15"/>
-    </row>
-    <row r="97" spans="1:8" s="37" customFormat="1" ht="15.75">
-      <c r="A97" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="B97" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C97" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E97" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G97" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H97" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="16.5">
-      <c r="A98" s="40">
-        <v>1</v>
-      </c>
-      <c r="B98" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="C98" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="D98" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="E98" s="42"/>
+      <c r="E98" s="45"/>
       <c r="F98" s="1" t="s">
         <v>22</v>
       </c>
@@ -4646,19 +4633,13 @@
       <c r="H98" s="20"/>
     </row>
     <row r="99" spans="1:8" ht="46.5">
-      <c r="A99" s="43">
-        <v>2</v>
-      </c>
-      <c r="B99" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C99" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="D99" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E99" s="45"/>
+      <c r="A99" s="46"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
       <c r="F99" s="1" t="s">
         <v>22</v>
       </c>
@@ -4666,167 +4647,173 @@
       <c r="H99" s="20"/>
     </row>
     <row r="100" spans="1:8" ht="46.5">
-      <c r="A100" s="46"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="48" t="s">
+      <c r="A100" s="43">
+        <v>3</v>
+      </c>
+      <c r="B100" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="D100" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" s="45"/>
+      <c r="F100" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="20"/>
+      <c r="H100" s="73"/>
+    </row>
+    <row r="101" spans="1:8" ht="46.5">
+      <c r="A101" s="46"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-    </row>
-    <row r="101" spans="1:8" ht="46.5">
-      <c r="A101" s="43">
-        <v>3</v>
-      </c>
-      <c r="B101" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" s="44" t="s">
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="72"/>
+      <c r="G101" s="20"/>
+      <c r="H101" s="74"/>
+    </row>
+    <row r="102" spans="1:8" ht="30.75">
+      <c r="A102" s="43">
+        <v>4</v>
+      </c>
+      <c r="B102" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="D101" s="44" t="s">
+      <c r="D102" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="E101" s="45"/>
-      <c r="F101" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="G101" s="20"/>
-      <c r="H101" s="67"/>
-    </row>
-    <row r="102" spans="1:8" ht="46.5">
-      <c r="A102" s="46"/>
-      <c r="B102" s="47"/>
-      <c r="C102" s="48" t="s">
+      <c r="E102" s="45"/>
+      <c r="F102" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="73"/>
+      <c r="H102" s="73"/>
+    </row>
+    <row r="103" spans="1:8" ht="61.5">
+      <c r="A103" s="46"/>
+      <c r="B103" s="47"/>
+      <c r="C103" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="D102" s="47"/>
-      <c r="E102" s="47"/>
-      <c r="F102" s="66"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="68"/>
-    </row>
-    <row r="103" spans="1:8" ht="30.75">
-      <c r="A103" s="43">
-        <v>4</v>
-      </c>
-      <c r="B103" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C103" s="44" t="s">
+      <c r="D103" s="47"/>
+      <c r="E103" s="47"/>
+      <c r="F103" s="72"/>
+      <c r="G103" s="74"/>
+      <c r="H103" s="74"/>
+    </row>
+    <row r="104" spans="1:8" ht="30.75">
+      <c r="A104" s="43">
+        <v>5</v>
+      </c>
+      <c r="B104" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="D103" s="44" t="s">
+      <c r="D104" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="45"/>
-      <c r="F103" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="G103" s="67"/>
-      <c r="H103" s="67"/>
-    </row>
-    <row r="104" spans="1:8" ht="61.5">
-      <c r="A104" s="46"/>
-      <c r="B104" s="47"/>
-      <c r="C104" s="48" t="s">
+      <c r="E104" s="45"/>
+      <c r="F104" s="71"/>
+      <c r="G104" s="73"/>
+      <c r="H104" s="73"/>
+    </row>
+    <row r="105" spans="1:8" ht="30.75">
+      <c r="A105" s="46"/>
+      <c r="B105" s="47"/>
+      <c r="C105" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D104" s="47"/>
-      <c r="E104" s="47"/>
-      <c r="F104" s="66"/>
-      <c r="G104" s="68"/>
-      <c r="H104" s="68"/>
-    </row>
-    <row r="105" spans="1:8" ht="30.75">
-      <c r="A105" s="43">
-        <v>5</v>
-      </c>
-      <c r="B105" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C105" s="44" t="s">
+      <c r="D105" s="47"/>
+      <c r="E105" s="47"/>
+      <c r="F105" s="72"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="74"/>
+    </row>
+    <row r="106" spans="1:8" ht="15">
+      <c r="A106" s="9">
+        <v>10</v>
+      </c>
+      <c r="B106" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="D105" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E105" s="45"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="67"/>
-      <c r="H105" s="67"/>
-    </row>
-    <row r="106" spans="1:8" ht="30.75">
-      <c r="A106" s="46"/>
-      <c r="B106" s="47"/>
-      <c r="C106" s="48" t="s">
+      <c r="C106" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="D106" s="47"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="66"/>
-      <c r="G106" s="68"/>
-      <c r="H106" s="68"/>
+      <c r="D106" s="65"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="15"/>
     </row>
     <row r="107" spans="1:8" ht="15">
-      <c r="A107" s="9">
-        <v>10</v>
-      </c>
-      <c r="B107" s="10" t="s">
+      <c r="A107" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15">
+      <c r="A108" s="1">
+        <v>1</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+    </row>
+    <row r="109" spans="1:8" ht="60.75">
+      <c r="A109" s="1">
+        <v>2</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C107" s="69" t="s">
-        <v>134</v>
-      </c>
-      <c r="D107" s="69"/>
-      <c r="E107" s="69"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="14"/>
-      <c r="H107" s="15"/>
-    </row>
-    <row r="108" spans="1:8" ht="15">
-      <c r="A108" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B108" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E108" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F108" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G108" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H108" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="15">
-      <c r="A109" s="1">
-        <v>1</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D109" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="1" t="s">
@@ -4835,18 +4822,18 @@
       <c r="G109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110" spans="1:8" ht="60.75">
+    <row r="110" spans="1:8" ht="30.75">
       <c r="A110" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B110" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>135</v>
+      <c r="C110" s="19" t="s">
+        <v>134</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="1" t="s">
@@ -4855,18 +4842,18 @@
       <c r="G110" s="20"/>
       <c r="H110" s="20"/>
     </row>
-    <row r="111" spans="1:8" ht="30.75">
+    <row r="111" spans="1:8" ht="76.5">
       <c r="A111" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C111" s="19" t="s">
-        <v>136</v>
+      <c r="C111" s="31" t="s">
+        <v>135</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="1" t="s">
@@ -4877,16 +4864,16 @@
     </row>
     <row r="112" spans="1:8" ht="76.5">
       <c r="A112" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="31" t="s">
-        <v>137</v>
+      <c r="C112" s="49" t="s">
+        <v>136</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="1" t="s">
@@ -4895,18 +4882,18 @@
       <c r="G112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113" spans="1:8" ht="76.5">
+    <row r="113" spans="1:8" ht="45.75">
       <c r="A113" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B113" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="49" t="s">
-        <v>138</v>
+      <c r="C113" s="31" t="s">
+        <v>137</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="1" t="s">
@@ -4915,18 +4902,18 @@
       <c r="G113" s="20"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114" spans="1:8" ht="45.75">
+    <row r="114" spans="1:8" ht="76.5">
       <c r="A114" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B114" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C114" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="1" t="s">
@@ -4935,137 +4922,139 @@
       <c r="G114" s="20"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115" spans="1:8" ht="76.5">
+    <row r="115" spans="1:8" ht="91.5">
       <c r="A115" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B115" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C115" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E115" s="4"/>
-      <c r="F115" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F115" s="1"/>
       <c r="G115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116" spans="1:8" ht="91.5">
+    <row r="116" spans="1:8" ht="60.75">
       <c r="A116" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B116" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C116" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="1"/>
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117" spans="1:8" ht="60.75">
+    <row r="117" spans="1:8" ht="15">
       <c r="A117" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C117" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="1"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-    </row>
-    <row r="118" spans="1:8" ht="15">
-      <c r="A118" s="1">
-        <v>10</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C118" s="31" t="s">
+      <c r="G117" s="50"/>
+      <c r="H117" s="51"/>
+    </row>
+    <row r="118" spans="1:8" ht="15" customHeight="1">
+      <c r="A118" s="52">
+        <v>11</v>
+      </c>
+      <c r="B118" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C118" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="75"/>
+      <c r="E118" s="76"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="15"/>
+    </row>
+    <row r="119" spans="1:8" ht="15">
+      <c r="A119" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B119" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="15">
+      <c r="A120" s="56">
+        <v>1</v>
+      </c>
+      <c r="B120" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C120" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="E118" s="4"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="50"/>
-      <c r="H118" s="51"/>
-    </row>
-    <row r="119" spans="1:8" ht="15" customHeight="1">
-      <c r="A119" s="52">
-        <v>11</v>
-      </c>
-      <c r="B119" s="53" t="s">
+      <c r="D120" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="70" t="s">
+      <c r="F120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
+    </row>
+    <row r="121" spans="1:8" ht="15">
+      <c r="A121" s="61">
+        <v>2</v>
+      </c>
+      <c r="B121" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="D119" s="70"/>
-      <c r="E119" s="71"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="14"/>
-      <c r="H119" s="15"/>
-    </row>
-    <row r="120" spans="1:8" ht="15">
-      <c r="A120" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="B120" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C120" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="D120" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E120" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G120" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="15">
-      <c r="A121" s="56">
-        <v>1</v>
-      </c>
-      <c r="B121" s="57" t="s">
-        <v>18</v>
-      </c>
       <c r="C121" s="57" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="D121" s="57" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="E121" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>22</v>
@@ -5074,20 +5063,16 @@
       <c r="H121" s="20"/>
     </row>
     <row r="122" spans="1:8" ht="15">
-      <c r="A122" s="73">
-        <v>2</v>
-      </c>
-      <c r="B122" s="75" t="s">
-        <v>147</v>
-      </c>
+      <c r="A122" s="62"/>
+      <c r="B122" s="64"/>
       <c r="C122" s="57" t="s">
         <v>148</v>
       </c>
       <c r="D122" s="57" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E122" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>22</v>
@@ -5096,16 +5081,20 @@
       <c r="H122" s="20"/>
     </row>
     <row r="123" spans="1:8" ht="15">
-      <c r="A123" s="74"/>
-      <c r="B123" s="76"/>
+      <c r="A123" s="58">
+        <v>3</v>
+      </c>
+      <c r="B123" s="57" t="s">
+        <v>149</v>
+      </c>
       <c r="C123" s="57" t="s">
         <v>150</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E123" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>22</v>
@@ -5113,9 +5102,9 @@
       <c r="G123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124" spans="1:8" ht="15">
+    <row r="124" spans="1:8" ht="30.75">
       <c r="A124" s="58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B124" s="57" t="s">
         <v>151</v>
@@ -5124,10 +5113,10 @@
         <v>152</v>
       </c>
       <c r="D124" s="57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E124" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>22</v>
@@ -5135,21 +5124,21 @@
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125" spans="1:8" ht="30.75">
-      <c r="A125" s="58">
-        <v>4</v>
-      </c>
-      <c r="B125" s="57" t="s">
+    <row r="125" spans="1:8" ht="15">
+      <c r="A125" s="61">
+        <v>5</v>
+      </c>
+      <c r="B125" s="63" t="s">
         <v>153</v>
       </c>
       <c r="C125" s="57" t="s">
         <v>154</v>
       </c>
       <c r="D125" s="57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E125" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>22</v>
@@ -5158,20 +5147,16 @@
       <c r="H125" s="20"/>
     </row>
     <row r="126" spans="1:8" ht="15">
-      <c r="A126" s="73">
-        <v>5</v>
-      </c>
-      <c r="B126" s="75" t="s">
+      <c r="A126" s="61"/>
+      <c r="B126" s="63"/>
+      <c r="C126" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="C126" s="57" t="s">
-        <v>156</v>
-      </c>
       <c r="D126" s="57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E126" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>22</v>
@@ -5180,109 +5165,111 @@
       <c r="H126" s="20"/>
     </row>
     <row r="127" spans="1:8" ht="15">
-      <c r="A127" s="73"/>
-      <c r="B127" s="75"/>
+      <c r="A127" s="61"/>
+      <c r="B127" s="63"/>
       <c r="C127" s="57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D127" s="57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E127" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F127" s="1"/>
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
     </row>
     <row r="128" spans="1:8" ht="15">
-      <c r="A128" s="73"/>
-      <c r="B128" s="75"/>
+      <c r="A128" s="62"/>
+      <c r="B128" s="64"/>
       <c r="C128" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D128" s="57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E128" s="57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F128" s="1"/>
       <c r="G128" s="20"/>
       <c r="H128" s="20"/>
     </row>
     <row r="129" spans="1:8" ht="15">
-      <c r="A129" s="74"/>
-      <c r="B129" s="76"/>
-      <c r="C129" s="57" t="s">
+      <c r="A129" s="9">
+        <v>12</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C129" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="D129" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="E129" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="F129" s="1"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
+      <c r="D129" s="65"/>
+      <c r="E129" s="65"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="14"/>
+      <c r="H129" s="15"/>
     </row>
     <row r="130" spans="1:8" ht="15">
-      <c r="A130" s="9">
-        <v>12</v>
-      </c>
-      <c r="B130" s="10" t="s">
+      <c r="A130" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15">
+      <c r="A131" s="1">
+        <v>1</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="20"/>
+      <c r="H131" s="20"/>
+    </row>
+    <row r="132" spans="1:8" ht="121.5">
+      <c r="A132" s="1">
+        <v>2</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="C130" s="69" t="s">
+      <c r="D132" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D130" s="69"/>
-      <c r="E130" s="69"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="15"/>
-    </row>
-    <row r="131" spans="1:8" ht="15">
-      <c r="A131" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E131" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G131" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H131" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="15">
-      <c r="A132" s="1">
-        <v>1</v>
-      </c>
-      <c r="B132" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C132" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="1" t="s">
@@ -5291,18 +5278,18 @@
       <c r="G132" s="20"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133" spans="1:8" ht="121.5">
+    <row r="133" spans="1:8" ht="106.5">
       <c r="A133" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B133" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C133" s="59" t="s">
+      <c r="C133" s="19" t="s">
         <v>162</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="1" t="s">
@@ -5311,18 +5298,18 @@
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8" ht="106.5">
+    <row r="134" spans="1:8" ht="152.25">
       <c r="A134" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B134" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="19" t="s">
-        <v>164</v>
+      <c r="C134" s="31" t="s">
+        <v>163</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="1" t="s">
@@ -5333,16 +5320,16 @@
     </row>
     <row r="135" spans="1:8" ht="152.25">
       <c r="A135" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B135" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="31" t="s">
-        <v>165</v>
+      <c r="C135" s="49" t="s">
+        <v>164</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="1" t="s">
@@ -5353,16 +5340,16 @@
     </row>
     <row r="136" spans="1:8" ht="152.25">
       <c r="A136" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B136" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C136" s="49" t="s">
-        <v>166</v>
+      <c r="C136" s="60" t="s">
+        <v>165</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="1" t="s">
@@ -5373,16 +5360,16 @@
     </row>
     <row r="137" spans="1:8" ht="152.25">
       <c r="A137" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B137" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C137" s="60" t="s">
-        <v>167</v>
+      <c r="C137" s="31" t="s">
+        <v>166</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="1" t="s">
@@ -5391,116 +5378,116 @@
       <c r="G137" s="20"/>
       <c r="H137" s="20"/>
     </row>
-    <row r="138" spans="1:8" ht="152.25">
+    <row r="138" spans="1:8" ht="137.25">
       <c r="A138" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B138" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C138" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E138" s="4"/>
-      <c r="F138" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F138" s="1"/>
       <c r="G138" s="20"/>
       <c r="H138" s="20"/>
     </row>
-    <row r="139" spans="1:8" ht="137.25">
+    <row r="139" spans="1:8" ht="30.75">
       <c r="A139" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B139" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C139" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="20"/>
-    </row>
-    <row r="140" spans="1:8" ht="30.75">
-      <c r="A140" s="1">
+      <c r="G139" s="50"/>
+      <c r="H139" s="51"/>
+    </row>
+    <row r="140" spans="1:8" ht="15">
+      <c r="A140" s="9">
+        <v>13</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="D140" s="65"/>
+      <c r="E140" s="65"/>
+      <c r="F140" s="9"/>
+      <c r="G140" s="14"/>
+      <c r="H140" s="15"/>
+    </row>
+    <row r="141" spans="1:8" ht="15">
+      <c r="A141" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G141" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H141" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B140" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C140" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="D140" s="1" t="s">
+    </row>
+    <row r="142" spans="1:8" ht="15">
+      <c r="A142" s="1">
+        <v>1</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C142" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E140" s="4"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="50"/>
-      <c r="H140" s="51"/>
-    </row>
-    <row r="141" spans="1:8" ht="15">
-      <c r="A141" s="9">
-        <v>13</v>
-      </c>
-      <c r="B141" s="10" t="s">
+      <c r="D142" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142" s="20"/>
+      <c r="H142" s="20"/>
+    </row>
+    <row r="143" spans="1:8" ht="60.75">
+      <c r="A143" s="1">
+        <v>2</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="C141" s="69" t="s">
+      <c r="D143" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="D141" s="69"/>
-      <c r="E141" s="69"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="14"/>
-      <c r="H141" s="15"/>
-    </row>
-    <row r="142" spans="1:8" ht="15">
-      <c r="A142" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D142" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E142" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F142" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G142" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H142" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="15">
-      <c r="A143" s="1">
-        <v>1</v>
-      </c>
-      <c r="B143" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="1" t="s">
@@ -5511,16 +5498,16 @@
     </row>
     <row r="144" spans="1:8" ht="60.75">
       <c r="A144" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B144" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C144" s="59" t="s">
+      <c r="C144" s="19" t="s">
         <v>173</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="1" t="s">
@@ -5529,18 +5516,18 @@
       <c r="G144" s="20"/>
       <c r="H144" s="20"/>
     </row>
-    <row r="145" spans="1:8" ht="60.75">
+    <row r="145" spans="1:8" ht="30.75">
       <c r="A145" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B145" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C145" s="19" t="s">
-        <v>175</v>
+      <c r="C145" s="31" t="s">
+        <v>174</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="1" t="s">
@@ -5549,18 +5536,18 @@
       <c r="G145" s="20"/>
       <c r="H145" s="20"/>
     </row>
-    <row r="146" spans="1:8" ht="30.75">
+    <row r="146" spans="1:8" ht="76.5">
       <c r="A146" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B146" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C146" s="31" t="s">
-        <v>176</v>
+      <c r="C146" s="49" t="s">
+        <v>175</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="1" t="s">
@@ -5569,18 +5556,18 @@
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147" spans="1:8" ht="76.5">
+    <row r="147" spans="1:8" ht="60.75">
       <c r="A147" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B147" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C147" s="49" t="s">
-        <v>177</v>
+      <c r="C147" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="1" t="s">
@@ -5589,18 +5576,18 @@
       <c r="G147" s="20"/>
       <c r="H147" s="20"/>
     </row>
-    <row r="148" spans="1:8" ht="60.75">
+    <row r="148" spans="1:8" ht="76.5">
       <c r="A148" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B148" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C148" s="60" t="s">
-        <v>178</v>
+      <c r="C148" s="31" t="s">
+        <v>177</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="1" t="s">
@@ -5609,98 +5596,98 @@
       <c r="G148" s="20"/>
       <c r="H148" s="20"/>
     </row>
-    <row r="149" spans="1:8" ht="76.5">
+    <row r="149" spans="1:8" ht="60.75">
       <c r="A149" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B149" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C149" s="31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E149" s="4"/>
-      <c r="F149" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F149" s="1"/>
       <c r="G149" s="20"/>
       <c r="H149" s="20"/>
     </row>
-    <row r="150" spans="1:8" ht="60.75">
-      <c r="A150" s="1">
+    <row r="150" spans="1:8" ht="15">
+      <c r="A150" s="9">
+        <v>14</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C150" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="D150" s="65"/>
+      <c r="E150" s="65"/>
+      <c r="F150" s="9"/>
+      <c r="G150" s="14"/>
+      <c r="H150" s="15"/>
+    </row>
+    <row r="151" spans="1:8" ht="15">
+      <c r="A151" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G151" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B150" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C150" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E150" s="4"/>
-      <c r="F150" s="1"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
-    </row>
-    <row r="151" spans="1:8" ht="15">
-      <c r="A151" s="9">
-        <v>14</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C151" s="69" t="s">
-        <v>182</v>
-      </c>
-      <c r="D151" s="69"/>
-      <c r="E151" s="69"/>
-      <c r="F151" s="9"/>
-      <c r="G151" s="14"/>
-      <c r="H151" s="15"/>
+      <c r="H151" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="152" spans="1:8" ht="15">
-      <c r="A152" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D152" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E152" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F152" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G152" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="A152" s="1">
+        <v>1</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="4"/>
+      <c r="F152" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152" s="20"/>
+      <c r="H152" s="20"/>
     </row>
     <row r="153" spans="1:8" ht="15">
       <c r="A153" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="C153" s="59" t="s">
+        <v>181</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="1" t="s">
@@ -5709,18 +5696,18 @@
       <c r="G153" s="20"/>
       <c r="H153" s="20"/>
     </row>
-    <row r="154" spans="1:8" ht="15">
+    <row r="154" spans="1:8" ht="30.75">
       <c r="A154" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B154" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C154" s="59" t="s">
-        <v>183</v>
+      <c r="C154" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="1" t="s">
@@ -5731,16 +5718,16 @@
     </row>
     <row r="155" spans="1:8" ht="30.75">
       <c r="A155" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>184</v>
+        <v>18</v>
+      </c>
+      <c r="C155" s="31" t="s">
+        <v>183</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="1" t="s">
@@ -5749,80 +5736,80 @@
       <c r="G155" s="20"/>
       <c r="H155" s="20"/>
     </row>
-    <row r="156" spans="1:8" ht="30.75">
-      <c r="A156" s="1">
-        <v>4</v>
-      </c>
-      <c r="B156" s="19" t="s">
+    <row r="156" spans="1:8" ht="15">
+      <c r="A156" s="9">
+        <v>15</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C156" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="D156" s="65"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="9"/>
+      <c r="G156" s="14"/>
+      <c r="H156" s="15"/>
+    </row>
+    <row r="157" spans="1:8" ht="15">
+      <c r="A157" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G157" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H157" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="15">
+      <c r="A158" s="1">
+        <v>1</v>
+      </c>
+      <c r="B158" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C156" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="D156" s="1" t="s">
+      <c r="C158" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E156" s="4"/>
-      <c r="F156" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G156" s="20"/>
-      <c r="H156" s="20"/>
-    </row>
-    <row r="157" spans="1:8" ht="15">
-      <c r="A157" s="9">
-        <v>15</v>
-      </c>
-      <c r="B157" s="10" t="s">
+      <c r="D158" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="4"/>
+      <c r="F158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="20"/>
+      <c r="H158" s="20"/>
+    </row>
+    <row r="159" spans="1:8" ht="60.75">
+      <c r="A159" s="1">
+        <v>2</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C159" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="C157" s="69" t="s">
-        <v>187</v>
-      </c>
-      <c r="D157" s="69"/>
-      <c r="E157" s="69"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="14"/>
-      <c r="H157" s="15"/>
-    </row>
-    <row r="158" spans="1:8" ht="15">
-      <c r="A158" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B158" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C158" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E158" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F158" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G158" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H158" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="15">
-      <c r="A159" s="1">
-        <v>1</v>
-      </c>
-      <c r="B159" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C159" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D159" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="1" t="s">
@@ -5831,18 +5818,18 @@
       <c r="G159" s="20"/>
       <c r="H159" s="20"/>
     </row>
-    <row r="160" spans="1:8" ht="60.75">
+    <row r="160" spans="1:8" ht="15">
       <c r="A160" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B160" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C160" s="59" t="s">
-        <v>188</v>
+        <v>67</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>187</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="1" t="s">
@@ -5853,16 +5840,16 @@
     </row>
     <row r="161" spans="1:8" ht="15">
       <c r="A161" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B161" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C161" s="19" t="s">
-        <v>189</v>
+        <v>18</v>
+      </c>
+      <c r="C161" s="31" t="s">
+        <v>188</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="1" t="s">
@@ -5871,18 +5858,18 @@
       <c r="G161" s="20"/>
       <c r="H161" s="20"/>
     </row>
-    <row r="162" spans="1:8" ht="15">
+    <row r="162" spans="1:8" ht="60.75">
       <c r="A162" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B162" s="19" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="C162" s="31" t="s">
         <v>190</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E162" s="4"/>
       <c r="F162" s="1" t="s">
@@ -5891,80 +5878,80 @@
       <c r="G162" s="20"/>
       <c r="H162" s="20"/>
     </row>
-    <row r="163" spans="1:8" ht="60.75">
-      <c r="A163" s="1">
-        <v>5</v>
-      </c>
-      <c r="B163" s="19" t="s">
+    <row r="163" spans="1:8" ht="15">
+      <c r="A163" s="9">
+        <v>16</v>
+      </c>
+      <c r="B163" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C163" s="31" t="s">
+      <c r="C163" s="67" t="s">
         <v>192</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="D163" s="67"/>
+      <c r="E163" s="67"/>
+      <c r="F163" s="9"/>
+      <c r="G163" s="14"/>
+      <c r="H163" s="15"/>
+    </row>
+    <row r="164" spans="1:8" ht="15">
+      <c r="A164" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G164" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H164" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="15">
+      <c r="A165" s="1">
+        <v>1</v>
+      </c>
+      <c r="B165" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E163" s="4"/>
-      <c r="F163" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G163" s="20"/>
-      <c r="H163" s="20"/>
-    </row>
-    <row r="164" spans="1:8" ht="15">
-      <c r="A164" s="9">
-        <v>16</v>
-      </c>
-      <c r="B164" s="10" t="s">
+      <c r="D165" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="4"/>
+      <c r="F165" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="20"/>
+      <c r="H165" s="20"/>
+    </row>
+    <row r="166" spans="1:8" ht="76.5">
+      <c r="A166" s="1">
+        <v>2</v>
+      </c>
+      <c r="B166" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C164" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="D164" s="61"/>
-      <c r="E164" s="61"/>
-      <c r="F164" s="9"/>
-      <c r="G164" s="14"/>
-      <c r="H164" s="15"/>
-    </row>
-    <row r="165" spans="1:8" ht="15">
-      <c r="A165" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B165" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C165" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D165" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E165" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F165" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G165" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H165" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="15">
-      <c r="A166" s="1">
-        <v>1</v>
-      </c>
-      <c r="B166" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C166" s="19" t="s">
-        <v>51</v>
-      </c>
       <c r="D166" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="1" t="s">
@@ -5973,18 +5960,18 @@
       <c r="G166" s="20"/>
       <c r="H166" s="20"/>
     </row>
-    <row r="167" spans="1:8" ht="76.5">
+    <row r="167" spans="1:8" ht="106.5">
       <c r="A167" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B167" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C167" s="59" t="s">
-        <v>195</v>
+      <c r="C167" s="19" t="s">
+        <v>194</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="1" t="s">
@@ -5993,18 +5980,18 @@
       <c r="G167" s="20"/>
       <c r="H167" s="20"/>
     </row>
-    <row r="168" spans="1:8" ht="106.5">
+    <row r="168" spans="1:8" ht="76.5">
       <c r="A168" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B168" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C168" s="19" t="s">
-        <v>196</v>
+      <c r="C168" s="31" t="s">
+        <v>195</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="1" t="s">
@@ -6013,18 +6000,18 @@
       <c r="G168" s="20"/>
       <c r="H168" s="20"/>
     </row>
-    <row r="169" spans="1:8" ht="76.5">
+    <row r="169" spans="1:8" ht="60.75">
       <c r="A169" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B169" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C169" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="1" t="s">
@@ -6033,18 +6020,18 @@
       <c r="G169" s="20"/>
       <c r="H169" s="20"/>
     </row>
-    <row r="170" spans="1:8" ht="60.75">
+    <row r="170" spans="1:8" ht="76.5">
       <c r="A170" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B170" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C170" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="1" t="s">
@@ -6053,76 +6040,76 @@
       <c r="G170" s="20"/>
       <c r="H170" s="20"/>
     </row>
-    <row r="171" spans="1:8" ht="76.5">
-      <c r="A171" s="1">
+    <row r="171" spans="1:8" ht="15">
+      <c r="A171" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C171" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D171" s="67"/>
+      <c r="E171" s="67"/>
+      <c r="F171" s="9"/>
+      <c r="G171" s="14"/>
+      <c r="H171" s="15"/>
+    </row>
+    <row r="172" spans="1:8" ht="15">
+      <c r="A172" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B171" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C171" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E171" s="4"/>
-      <c r="F171" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G171" s="20"/>
-      <c r="H171" s="20"/>
-    </row>
-    <row r="172" spans="1:8" ht="15">
-      <c r="A172" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B172" s="10" t="s">
+      <c r="F172" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G172" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="76.5">
+      <c r="A173" s="1">
+        <v>1</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C173" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="C172" s="61" t="s">
+      <c r="D173" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D172" s="61"/>
-      <c r="E172" s="61"/>
-      <c r="F172" s="9"/>
-      <c r="G172" s="14"/>
-      <c r="H172" s="15"/>
-    </row>
-    <row r="173" spans="1:8" ht="15">
-      <c r="A173" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E173" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F173" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G173" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H173" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" ht="76.5">
+      <c r="E173" s="4"/>
+      <c r="F173" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="20"/>
+      <c r="H173" s="20"/>
+    </row>
+    <row r="174" spans="1:8" ht="15">
       <c r="A174" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B174" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C174" s="59" t="s">
+      <c r="C174" s="19" t="s">
         <v>203</v>
       </c>
       <c r="D174" s="1" t="s">
@@ -6135,26 +6122,7 @@
       <c r="G174" s="20"/>
       <c r="H174" s="20"/>
     </row>
-    <row r="175" spans="1:8" ht="15">
-      <c r="A175" s="1">
-        <v>2</v>
-      </c>
-      <c r="B175" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C175" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E175" s="4"/>
-      <c r="F175" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G175" s="20"/>
-      <c r="H175" s="20"/>
-    </row>
+    <row r="175" spans="1:8" ht="15"/>
     <row r="176" spans="1:8" ht="15"/>
     <row r="177" ht="15"/>
     <row r="178" ht="15"/>
@@ -6164,39 +6132,39 @@
     <row r="182" ht="15"/>
     <row r="183" ht="15"/>
   </sheetData>
-  <autoFilter ref="A3:H42" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="28">
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="F101:F102"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="F103:F104"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="F105:F106"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="A125:A128"/>
+    <mergeCell ref="B125:B128"/>
+    <mergeCell ref="C129:E129"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F107:F1048576 F3:F95">
+  <conditionalFormatting sqref="F1 F106:F1048576 F3:F94">
     <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -6207,7 +6175,7 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F101 F103 F105">
+  <conditionalFormatting sqref="F95:F100 F102 F104">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -6219,7 +6187,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F61:F71 F17:F27 F43:F54 F57:F58 F30:F40 F74:F84 F87:F95 F6:F14" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F60:F70 F17:F26 F42:F53 F56:F57 F29:F39 F73:F83 F86:F94 F6:F14" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -6240,7 +6208,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
       <c r="A1" s="77" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="77"/>
@@ -6252,26 +6220,26 @@
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6279,7 +6247,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -6301,12 +6269,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D22D72570E156D4F9C34B893E183F0BF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ec9c283aea1b7e9b2a2bfe7317a7796f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -6420,14 +6382,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
 </file>
--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29311"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BDB9639-7B91-45C1-9168-BF3772F66969}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A62829-5784-4A3C-985E-75691FC15AB8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Instructions" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Minutes of Meeting-'!$A$3:$H$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Minutes of Meeting-'!$A$3:$H$32</definedName>
     <definedName name="Status">Instructions!$A$3:$A$5</definedName>
   </definedNames>
   <calcPr calcId="191028" concurrentCalc="0"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="195">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -185,111 +185,31 @@
 Fadila: please create an excel for the calculation of the farm/system size with a sheet for every topic e.g. farm, product processing and share it with the others.</t>
   </si>
   <si>
-    <t>13.12.2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail, Diallo Fadilatou, Excellence program Students,botho schanze, Seah Qiao Ling</t>
+    <t>19.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Abdelgafar Ismail, Diallo Fadilatou, Excellence program Students,Vanessa Bleil</t>
   </si>
   <si>
     <t>Presentation</t>
   </si>
   <si>
-    <t>Adams: thanks a lot. Nice picture. Will have a look on the ontology; What data are you recording; any ideas in additional data (just pick two) and what kind of sensors would be interested for Ball Mill. What is an artisanal Mine. Maybe you can add a link to it. On the ontology also have the properties.                                                                                                      -Thank you for considering the Sustainability aspect (health, social and economic aspects), could you find any linkage to sustainable development Goals UN SDGs – 17 goals which ones your project address</t>
+    <t>General: Excellent presentation for today, please consolidate all your calculations in one excel sheet and share it with me by the middle of next week. Start working on the swimlane diagram to present it for next week JF</t>
+  </si>
+  <si>
+    <t>Abdo</t>
   </si>
   <si>
     <t>20.12.2024</t>
   </si>
   <si>
-    <t>Adjara; have you heard about Infineon loudspeaker and microphones. Maybe you can add those to your Ontology. It would be good to have properties between the classes.
- -Did you think of how your app could also reach customers outside Burkina, e.g. Spotify started in Sweden but also become worldwide</t>
-  </si>
-  <si>
-    <t>20.12.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alicia; great that you already used Protege, Are you recording any data in your cowpea thresher; any ideas in additional data (just pick two) and what kind of sensors would be interested for cowpea tresher.                                                                                                              - please also find link between your project and the sustainable development Goals UN SDGs - 17 goals which ones your project address                           </t>
-  </si>
-  <si>
-    <t>20.12.2026</t>
-  </si>
-  <si>
-    <t>Charles: Also put a picture of your ontology in. What data are you recording with the moisture sensor. Maybe you can add more details on the ontology on the moisture sensor and how it works.
- -please look at the linkage between your project and the sustainable development Goals UN SDGs - 17 goals which ones your project address</t>
-  </si>
-  <si>
-    <t>20.12.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lukas: Add a link to the smart dryer project (not just ontology). You explained verbally the sensors but add a picture and a document explaining the sensors. What data are you recording in which period. Make and example                                                                                                          -did you add a class in the drowling related to the fruit/vegetal supplier? Local farmers e.g. also look at the sustainable development Goals UN SDGs - 17 goals which ones your project address
-                            </t>
-  </si>
-  <si>
-    <t>20.12.2028</t>
-  </si>
-  <si>
-    <t>Boris: Face recognition - add a picture of the ontology, what sensors are aou using just camera and what camera?                                                                    -did you consider accuracy of the face recognition solution?  Did you consider security and trust in your application and how to ensure that</t>
-  </si>
-  <si>
-    <t>20.12.2029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gertrude: . What data are you recording on the PV power plant. Maybe you can add more details on the ontology on the used sensors.                -did you consider the suppliers of the inverters, batteries, ..etc. also look at the sustainable development Goals UN SDGs - 17 goals which ones your project address                </t>
-  </si>
-  <si>
-    <t>20.12.2030</t>
-  </si>
-  <si>
-    <t>Wilfried: nice homepage; What data are you recording on the tracking system . Maybe you can add more details on the ontology on the used sensors.                                                                                                                            -do you have a class regarding the output of the solar panel for comparison without solar tracking? also look at the sustainable development Goals UN SDGs - 17 goals which ones your project address</t>
-  </si>
-  <si>
-    <t>20.12.2031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamado: use also a picture for the ontology. Good explained how you added the ontology I will have a look – it sounded very reasonable:                     -a class about the accuracy of the translation and how to measure it in the app? also look at the sustainable development Goals UN SDGs - 17 goals which ones your project address
-                </t>
-  </si>
-  <si>
-    <t>20.12.2032</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Info</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>General:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  Take the one before you in the sequence to understand his and her project next time. 
-Give him/her feedback and overnext time explain what she / her is doing by using the ontology.
- Take the 3-5 most important classes and its relationships. 
-Make sure your files are in good quality and let Fadila know if you make changes as we will duplicate so we can also see the latest status. 
-Maybe you can be shorter in the presentation and only talk about what we also see on the homepage. 
-We have to stay within the 30’ and ideal would be 15’ presentation; 10’ feedback and 5 minutes free flow of information</t>
-    </r>
+    <t xml:space="preserve"> Hans Ehm,  Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer, Seah Qiao Ling, Tristan Scheuermann,James Cherupillet</t>
+  </si>
+  <si>
+    <t>Adam: thanks for talking about the data recording. It would be great of you could show a reduced version (5 classes) of your ontology as well. Make sure that you explain well to Hamado that he can select the key 5-8 most important classes and relationships of the Ball Mill</t>
   </si>
   <si>
     <t>Hans</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm,  Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer, Seah Qiao Ling, Tristan Scheuermann,James Cherupillet</t>
-  </si>
-  <si>
-    <t>Adam: thanks for talking about the data recording. It would be great of you could show a reduced version (5 classes) of your ontology as well. Make sure that you explain well to Hamado that he can select the key 5-8 most important classes and relationships of the Ball Mill</t>
   </si>
   <si>
     <t>Adjara: I liked a lot your reduced class approach. Make sure that you explain well to Adam that he can select the key 5-8 most important classes and relationships of the Music application</t>
@@ -493,9 +413,6 @@
 	   - Consider different steps in building the farm, such as preparing resources like land or a pond.</t>
   </si>
   <si>
-    <t>Abdo</t>
-  </si>
-  <si>
     <t>03.01.2025</t>
   </si>
   <si>
@@ -848,6 +765,9 @@
     <t>Review PPT file about the sustainable farm and Feedack:                                        -Add Hyperlink                                                                                                      -Add Litterarure review                                                                                       -Add Picture related to BF</t>
   </si>
   <si>
+    <t xml:space="preserve"> Info</t>
+  </si>
+  <si>
     <t>More Informaton about possible Internship</t>
   </si>
   <si>
@@ -932,7 +852,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -993,14 +913,6 @@
       <color rgb="FF222222"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1623,57 +1535,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1682,79 +1594,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2649,16 +2561,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -3170,18 +3082,18 @@
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" ht="15">
       <c r="A27" s="9">
         <v>3</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
@@ -3232,7 +3144,7 @@
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
     </row>
-    <row r="30" spans="1:8" ht="130.5">
+    <row r="30" spans="1:8" ht="60.75">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -3243,205 +3155,189 @@
         <v>49</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="E30" s="4"/>
       <c r="F30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
     </row>
-    <row r="31" spans="1:8" ht="72.599999999999994">
-      <c r="A31" s="1">
-        <v>3</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="19" t="s">
+    <row r="31" spans="1:8">
+      <c r="A31" s="9">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="C31" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-    </row>
-    <row r="32" spans="1:8" ht="72.599999999999994">
-      <c r="A32" s="1">
-        <v>4</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-    </row>
-    <row r="33" spans="1:8" ht="72.599999999999994">
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>56</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E33" s="4"/>
       <c r="F33" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G33" s="20"/>
       <c r="H33" s="20"/>
     </row>
-    <row r="34" spans="1:8" ht="116.1">
+    <row r="34" spans="1:8" ht="57.95">
       <c r="A34" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="19" t="s">
-        <v>57</v>
+      <c r="C34" s="30" t="s">
+        <v>53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E34" s="4"/>
       <c r="F34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
     </row>
-    <row r="35" spans="1:8" ht="57.95">
+    <row r="35" spans="1:8" ht="43.5">
       <c r="A35" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="19" t="s">
-        <v>59</v>
+      <c r="C35" s="29" t="s">
+        <v>55</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E35" s="4"/>
       <c r="F35" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
     </row>
-    <row r="36" spans="1:8" ht="72.599999999999994">
+    <row r="36" spans="1:8" ht="57.95">
       <c r="A36" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="19" t="s">
-        <v>61</v>
+      <c r="C36" s="29" t="s">
+        <v>56</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E36" s="4"/>
       <c r="F36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
     </row>
-    <row r="37" spans="1:8" ht="87">
+    <row r="37" spans="1:8" ht="43.5">
       <c r="A37" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="19" t="s">
-        <v>63</v>
+      <c r="C37" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E37" s="4"/>
       <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
     </row>
-    <row r="38" spans="1:8" ht="87">
+    <row r="38" spans="1:8" ht="57.95">
       <c r="A38" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="19" t="s">
-        <v>65</v>
+      <c r="C38" s="32" t="s">
+        <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E38" s="4"/>
       <c r="F38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
     </row>
-    <row r="39" spans="1:8" ht="160.5">
+    <row r="39" spans="1:8" ht="43.5">
       <c r="A39" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>68</v>
+        <v>23</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>59</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="1" t="s">
@@ -3450,60 +3346,58 @@
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="9">
-        <v>4</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="15"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="12" t="s">
+    <row r="40" spans="1:8" ht="43.5">
+      <c r="A40" s="1">
         <v>8</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="B40" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+    </row>
+    <row r="41" spans="1:8" ht="43.5">
+      <c r="A41" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="B41" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+    </row>
+    <row r="42" spans="1:8" ht="57.95">
       <c r="A42" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>62</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="1" t="s">
@@ -3512,18 +3406,18 @@
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
     </row>
-    <row r="43" spans="1:8" ht="57.95">
+    <row r="43" spans="1:8" ht="159.6">
       <c r="A43" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="30" t="s">
-        <v>71</v>
+      <c r="C43" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="1" t="s">
@@ -3532,18 +3426,18 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
     </row>
-    <row r="44" spans="1:8" ht="43.5">
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="29" t="s">
-        <v>72</v>
+        <v>18</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>64</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="1" t="s">
@@ -3552,58 +3446,60 @@
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
     </row>
-    <row r="45" spans="1:8" ht="57.95">
-      <c r="A45" s="1">
-        <v>4</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" ht="43.5">
-      <c r="A46" s="1">
+    <row r="45" spans="1:8">
+      <c r="A45" s="9">
         <v>5</v>
       </c>
-      <c r="B46" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-    </row>
-    <row r="47" spans="1:8" ht="57.95">
+      <c r="B45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="15"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="32" t="s">
-        <v>75</v>
+        <v>18</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="1" t="s">
@@ -3612,78 +3508,82 @@
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
     </row>
-    <row r="48" spans="1:8" ht="43.5">
+    <row r="48" spans="1:8" ht="304.5">
       <c r="A48" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>76</v>
+        <v>44</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="4"/>
       <c r="F48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
     </row>
-    <row r="49" spans="1:8" ht="43.5">
-      <c r="A49" s="1">
+    <row r="49" spans="1:8">
+      <c r="A49" s="9">
+        <v>6</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="15"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-    </row>
-    <row r="50" spans="1:8" ht="43.5">
-      <c r="A50" s="1">
+      <c r="H50" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-    </row>
-    <row r="51" spans="1:8" ht="57.95">
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>79</v>
+        <v>18</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="1" t="s">
@@ -3692,18 +3592,18 @@
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
     </row>
-    <row r="52" spans="1:8" ht="159.6">
+    <row r="52" spans="1:8" ht="29.1">
       <c r="A52" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="33" t="s">
-        <v>80</v>
+      <c r="C52" s="30" t="s">
+        <v>71</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="1" t="s">
@@ -3712,18 +3612,18 @@
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" ht="57.95">
       <c r="A53" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>81</v>
+        <v>23</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="1" t="s">
@@ -3732,60 +3632,58 @@
       <c r="G53" s="20"/>
       <c r="H53" s="20"/>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="9">
+    <row r="54" spans="1:8" ht="43.5">
+      <c r="A54" s="1">
+        <v>4</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" spans="1:8" ht="72.599999999999994">
+      <c r="A55" s="1">
         <v>5</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="D54" s="65"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="15"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="12" t="s">
+      <c r="B55" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+    </row>
+    <row r="56" spans="1:8" ht="43.5">
+      <c r="A56" s="1">
         <v>6</v>
       </c>
-      <c r="F55" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="1">
-        <v>1</v>
-      </c>
       <c r="B56" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>75</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="1" t="s">
@@ -3794,162 +3692,156 @@
       <c r="G56" s="20"/>
       <c r="H56" s="20"/>
     </row>
-    <row r="57" spans="1:8" ht="304.5">
+    <row r="57" spans="1:8" ht="43.5">
       <c r="A57" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>85</v>
+        <v>23</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>76</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>87</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E57" s="4"/>
       <c r="F57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="20"/>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="9">
-        <v>6</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="D58" s="65"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="15"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="12" t="s">
+    <row r="58" spans="1:8" ht="43.5">
+      <c r="A58" s="1">
         <v>8</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="B58" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+    </row>
+    <row r="59" spans="1:8" ht="43.5">
+      <c r="A59" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="B59" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+    </row>
+    <row r="60" spans="1:8" ht="72.599999999999994">
       <c r="A60" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C60" s="31" t="s">
+        <v>79</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E60" s="4"/>
-      <c r="F60" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F60" s="1"/>
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8" ht="29.1">
+    <row r="61" spans="1:8" ht="188.45">
       <c r="A61" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="30" t="s">
-        <v>89</v>
+      <c r="C61" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8" ht="57.95">
-      <c r="A62" s="1">
-        <v>3</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-    </row>
-    <row r="63" spans="1:8" ht="43.5">
-      <c r="A63" s="1">
-        <v>4</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E63" s="4"/>
-      <c r="F63" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-    </row>
-    <row r="64" spans="1:8" ht="72.599999999999994">
+    <row r="62" spans="1:8">
+      <c r="A62" s="9">
+        <v>7</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="69"/>
+      <c r="E62" s="69"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="15"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" s="31" t="s">
-        <v>92</v>
+        <v>18</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="1" t="s">
@@ -3958,18 +3850,18 @@
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="43.5">
+    <row r="65" spans="1:8" ht="72.599999999999994">
       <c r="A65" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="32" t="s">
-        <v>93</v>
+      <c r="C65" s="30" t="s">
+        <v>84</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="1" t="s">
@@ -3978,18 +3870,18 @@
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66" spans="1:8" ht="43.5">
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C66" s="31" t="s">
-        <v>94</v>
+      <c r="C66" s="29" t="s">
+        <v>85</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="1" t="s">
@@ -4000,16 +3892,16 @@
     </row>
     <row r="67" spans="1:8" ht="43.5">
       <c r="A67" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C67" s="31" t="s">
-        <v>95</v>
+      <c r="C67" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="1" t="s">
@@ -4020,194 +3912,194 @@
     </row>
     <row r="68" spans="1:8" ht="43.5">
       <c r="A68" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E68" s="4"/>
-      <c r="F68" s="1"/>
+      <c r="F68" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69" spans="1:8" ht="72.599999999999994">
+    <row r="69" spans="1:8" ht="43.5">
       <c r="A69" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="31" t="s">
-        <v>97</v>
+      <c r="C69" s="32" t="s">
+        <v>87</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="E69" s="4"/>
-      <c r="F69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G69" s="20"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70" spans="1:8" ht="188.45">
+    <row r="70" spans="1:8" ht="43.5">
       <c r="A70" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="1" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="9">
-        <v>7</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C71" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="D71" s="65"/>
-      <c r="E71" s="65"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="15"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G72" s="12" t="s">
+      <c r="A71" s="1">
         <v>8</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="B71" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+    </row>
+    <row r="72" spans="1:8" ht="29.1">
+      <c r="A72" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="B72" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+    </row>
+    <row r="73" spans="1:8" ht="29.1">
       <c r="A73" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>91</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E73" s="4"/>
-      <c r="F73" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F73" s="1"/>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
     </row>
     <row r="74" spans="1:8" ht="72.599999999999994">
       <c r="A74" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C74" s="30" t="s">
-        <v>102</v>
+      <c r="C74" s="31" t="s">
+        <v>92</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="G74" s="20"/>
       <c r="H74" s="20"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="1">
-        <v>3</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E75" s="4"/>
-      <c r="F75" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-    </row>
-    <row r="76" spans="1:8" ht="43.5">
-      <c r="A76" s="1">
-        <v>4</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
-    </row>
-    <row r="77" spans="1:8" ht="43.5">
+      <c r="A75" s="9">
+        <v>8</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="15"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="31" t="s">
-        <v>104</v>
+        <v>18</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="1" t="s">
@@ -4216,18 +4108,18 @@
       <c r="G77" s="20"/>
       <c r="H77" s="20"/>
     </row>
-    <row r="78" spans="1:8" ht="43.5">
+    <row r="78" spans="1:8" ht="72.599999999999994">
       <c r="A78" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="32" t="s">
-        <v>105</v>
+      <c r="C78" s="30" t="s">
+        <v>95</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="1" t="s">
@@ -4236,18 +4128,18 @@
       <c r="G78" s="20"/>
       <c r="H78" s="20"/>
     </row>
-    <row r="79" spans="1:8" ht="43.5">
+    <row r="79" spans="1:8" ht="57.95">
       <c r="A79" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C79" s="31" t="s">
-        <v>106</v>
+      <c r="C79" s="29" t="s">
+        <v>96</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="1" t="s">
@@ -4256,18 +4148,18 @@
       <c r="G79" s="20"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" ht="76.5">
       <c r="A80" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="1" t="s">
@@ -4276,1020 +4168,1020 @@
       <c r="G80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81" spans="1:8" ht="29.1">
+    <row r="81" spans="1:8" ht="72.599999999999994">
       <c r="A81" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="31" t="s">
-        <v>108</v>
+      <c r="C81" s="32" t="s">
+        <v>98</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E81" s="4"/>
-      <c r="F81" s="1"/>
+      <c r="F81" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G81" s="20"/>
       <c r="H81" s="20"/>
     </row>
-    <row r="82" spans="1:8" ht="29.1">
+    <row r="82" spans="1:8" ht="87">
       <c r="A82" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E82" s="4"/>
-      <c r="F82" s="1"/>
+      <c r="F82" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" ht="72.599999999999994">
+    <row r="83" spans="1:8" ht="87">
       <c r="A83" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="1" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G83" s="20"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="9">
+    <row r="84" spans="1:8" ht="57.95">
+      <c r="A84" s="1">
         <v>8</v>
       </c>
-      <c r="B84" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C84" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="D84" s="65"/>
-      <c r="E84" s="65"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="15"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="11" t="s">
+      <c r="B84" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+    </row>
+    <row r="85" spans="1:8" ht="106.5">
+      <c r="A85" s="1">
+        <v>9</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+    </row>
+    <row r="86" spans="1:8" s="37" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A86" s="35">
+        <v>9</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" s="63"/>
+      <c r="E86" s="64"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="15"/>
+    </row>
+    <row r="87" spans="1:8" s="37" customFormat="1" ht="15.75">
+      <c r="A87" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B87" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C87" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D87" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E87" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="F85" s="12" t="s">
+      <c r="F87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G87" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H87" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="1">
+    <row r="88" spans="1:8" ht="16.5">
+      <c r="A88" s="40">
         <v>1</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B88" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="19" t="s">
+      <c r="C88" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D88" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E86" s="4"/>
-      <c r="F86" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-    </row>
-    <row r="87" spans="1:8" ht="72.599999999999994">
-      <c r="A87" s="1">
-        <v>2</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E87" s="4"/>
-      <c r="F87" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-    </row>
-    <row r="88" spans="1:8" ht="57.95">
-      <c r="A88" s="1">
-        <v>3</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E88" s="4"/>
+      <c r="E88" s="42"/>
       <c r="F88" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G88" s="20"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89" spans="1:8" ht="76.5">
-      <c r="A89" s="1">
-        <v>4</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="D89" s="1" t="s">
+    <row r="89" spans="1:8" ht="46.5">
+      <c r="A89" s="43">
+        <v>2</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="E89" s="4"/>
+      <c r="E89" s="45"/>
       <c r="F89" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G89" s="20"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90" spans="1:8" ht="72.599999999999994">
-      <c r="A90" s="1">
-        <v>5</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E90" s="4"/>
+    <row r="90" spans="1:8" ht="46.5">
+      <c r="A90" s="46"/>
+      <c r="B90" s="47"/>
+      <c r="C90" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" s="47"/>
+      <c r="E90" s="47"/>
       <c r="F90" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91" spans="1:8" ht="87">
-      <c r="A91" s="1">
+    <row r="91" spans="1:8" ht="46.5">
+      <c r="A91" s="43">
+        <v>3</v>
+      </c>
+      <c r="B91" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="45"/>
+      <c r="F91" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="20"/>
+      <c r="H91" s="67"/>
+    </row>
+    <row r="92" spans="1:8" ht="46.5">
+      <c r="A92" s="46"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D92" s="47"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="66"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="68"/>
+    </row>
+    <row r="93" spans="1:8" ht="30.75">
+      <c r="A93" s="43">
+        <v>4</v>
+      </c>
+      <c r="B93" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D93" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" s="45"/>
+      <c r="F93" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="67"/>
+      <c r="H93" s="67"/>
+    </row>
+    <row r="94" spans="1:8" ht="61.5">
+      <c r="A94" s="46"/>
+      <c r="B94" s="47"/>
+      <c r="C94" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D94" s="47"/>
+      <c r="E94" s="47"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="68"/>
+      <c r="H94" s="68"/>
+    </row>
+    <row r="95" spans="1:8" ht="30.75">
+      <c r="A95" s="43">
+        <v>5</v>
+      </c>
+      <c r="B95" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="45"/>
+      <c r="F95" s="65"/>
+      <c r="G95" s="67"/>
+      <c r="H95" s="67"/>
+    </row>
+    <row r="96" spans="1:8" ht="30.75">
+      <c r="A96" s="46"/>
+      <c r="B96" s="47"/>
+      <c r="C96" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" s="47"/>
+      <c r="E96" s="47"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="68"/>
+      <c r="H96" s="68"/>
+    </row>
+    <row r="97" spans="1:8" ht="15">
+      <c r="A97" s="9">
+        <v>10</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C97" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" s="69"/>
+      <c r="E97" s="69"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="15"/>
+    </row>
+    <row r="98" spans="1:8" ht="15">
+      <c r="A98" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91" s="4"/>
-      <c r="F91" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" s="20"/>
-      <c r="H91" s="20"/>
-    </row>
-    <row r="92" spans="1:8" ht="87">
-      <c r="A92" s="1">
+      <c r="F98" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B92" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E92" s="4"/>
-      <c r="F92" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-    </row>
-    <row r="93" spans="1:8" ht="57.95">
-      <c r="A93" s="1">
+      <c r="G98" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B93" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E93" s="4"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-    </row>
-    <row r="94" spans="1:8" ht="106.5">
-      <c r="A94" s="1">
+      <c r="H98" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E94" s="4"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="20"/>
-      <c r="H94" s="20"/>
-    </row>
-    <row r="95" spans="1:8" s="37" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A95" s="35">
-        <v>9</v>
-      </c>
-      <c r="B95" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C95" s="68" t="s">
-        <v>122</v>
-      </c>
-      <c r="D95" s="69"/>
-      <c r="E95" s="70"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="14"/>
-      <c r="H95" s="15"/>
-    </row>
-    <row r="96" spans="1:8" s="37" customFormat="1" ht="15.75">
-      <c r="A96" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="B96" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C96" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E96" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G96" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="16.5">
-      <c r="A97" s="40">
+    </row>
+    <row r="99" spans="1:8" ht="15">
+      <c r="A99" s="1">
         <v>1</v>
       </c>
-      <c r="B97" s="41" t="s">
+      <c r="B99" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C97" s="41" t="s">
+      <c r="C99" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D97" s="41" t="s">
+      <c r="D99" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E97" s="42"/>
-      <c r="F97" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
-    </row>
-    <row r="98" spans="1:8" ht="46.5">
-      <c r="A98" s="43">
-        <v>2</v>
-      </c>
-      <c r="B98" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D98" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E98" s="45"/>
-      <c r="F98" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G98" s="20"/>
-      <c r="H98" s="20"/>
-    </row>
-    <row r="99" spans="1:8" ht="46.5">
-      <c r="A99" s="46"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
+      <c r="E99" s="4"/>
       <c r="F99" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
     </row>
-    <row r="100" spans="1:8" ht="46.5">
-      <c r="A100" s="43">
+    <row r="100" spans="1:8" ht="60.75">
+      <c r="A100" s="1">
+        <v>2</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="20"/>
+      <c r="H100" s="20"/>
+    </row>
+    <row r="101" spans="1:8" ht="30.75">
+      <c r="A101" s="1">
         <v>3</v>
       </c>
-      <c r="B100" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C100" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="D100" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E100" s="45"/>
-      <c r="F100" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="G100" s="20"/>
-      <c r="H100" s="73"/>
-    </row>
-    <row r="101" spans="1:8" ht="46.5">
-      <c r="A101" s="46"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="72"/>
+      <c r="B101" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G101" s="20"/>
-      <c r="H101" s="74"/>
-    </row>
-    <row r="102" spans="1:8" ht="30.75">
-      <c r="A102" s="43">
+      <c r="H101" s="20"/>
+    </row>
+    <row r="102" spans="1:8" ht="76.5">
+      <c r="A102" s="1">
         <v>4</v>
       </c>
-      <c r="B102" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D102" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E102" s="45"/>
-      <c r="F102" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="G102" s="73"/>
-      <c r="H102" s="73"/>
-    </row>
-    <row r="103" spans="1:8" ht="61.5">
-      <c r="A103" s="46"/>
-      <c r="B103" s="47"/>
-      <c r="C103" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="D103" s="47"/>
-      <c r="E103" s="47"/>
-      <c r="F103" s="72"/>
-      <c r="G103" s="74"/>
-      <c r="H103" s="74"/>
-    </row>
-    <row r="104" spans="1:8" ht="30.75">
-      <c r="A104" s="43">
+      <c r="B102" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="20"/>
+      <c r="H102" s="20"/>
+    </row>
+    <row r="103" spans="1:8" ht="76.5">
+      <c r="A103" s="1">
         <v>5</v>
       </c>
-      <c r="B104" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D104" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E104" s="45"/>
-      <c r="F104" s="71"/>
-      <c r="G104" s="73"/>
-      <c r="H104" s="73"/>
-    </row>
-    <row r="105" spans="1:8" ht="30.75">
-      <c r="A105" s="46"/>
-      <c r="B105" s="47"/>
-      <c r="C105" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D105" s="47"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="72"/>
-      <c r="G105" s="74"/>
-      <c r="H105" s="74"/>
-    </row>
-    <row r="106" spans="1:8" ht="15">
-      <c r="A106" s="9">
-        <v>10</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C106" s="65" t="s">
-        <v>132</v>
-      </c>
-      <c r="D106" s="65"/>
-      <c r="E106" s="65"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="15"/>
-    </row>
-    <row r="107" spans="1:8" ht="15">
-      <c r="A107" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E107" s="12" t="s">
+      <c r="B103" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+    </row>
+    <row r="104" spans="1:8" ht="45.75">
+      <c r="A104" s="1">
         <v>6</v>
       </c>
-      <c r="F107" s="12" t="s">
+      <c r="B104" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E104" s="4"/>
+      <c r="F104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" s="20"/>
+      <c r="H104" s="20"/>
+    </row>
+    <row r="105" spans="1:8" ht="76.5">
+      <c r="A105" s="1">
         <v>7</v>
       </c>
-      <c r="G107" s="12" t="s">
+      <c r="B105" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E105" s="4"/>
+      <c r="F105" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" s="20"/>
+      <c r="H105" s="20"/>
+    </row>
+    <row r="106" spans="1:8" ht="91.5">
+      <c r="A106" s="1">
         <v>8</v>
       </c>
-      <c r="H107" s="11" t="s">
+      <c r="B106" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E106" s="4"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="20"/>
+    </row>
+    <row r="107" spans="1:8" ht="60.75">
+      <c r="A107" s="1">
         <v>9</v>
       </c>
+      <c r="B107" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E107" s="4"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="20"/>
     </row>
     <row r="108" spans="1:8" ht="15">
       <c r="A108" s="1">
+        <v>10</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="50"/>
+      <c r="H108" s="51"/>
+    </row>
+    <row r="109" spans="1:8" ht="15" customHeight="1">
+      <c r="A109" s="52">
+        <v>11</v>
+      </c>
+      <c r="B109" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C109" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="D109" s="70"/>
+      <c r="E109" s="71"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="15"/>
+    </row>
+    <row r="110" spans="1:8" ht="15">
+      <c r="A110" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B110" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G110" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15">
+      <c r="A111" s="56">
         <v>1</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B111" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C108" s="19" t="s">
+      <c r="C111" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D111" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="E108" s="4"/>
-      <c r="F108" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-    </row>
-    <row r="109" spans="1:8" ht="60.75">
-      <c r="A109" s="1">
-        <v>2</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E109" s="4"/>
-      <c r="F109" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-    </row>
-    <row r="110" spans="1:8" ht="30.75">
-      <c r="A110" s="1">
-        <v>3</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E110" s="4"/>
-      <c r="F110" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G110" s="20"/>
-      <c r="H110" s="20"/>
-    </row>
-    <row r="111" spans="1:8" ht="76.5">
-      <c r="A111" s="1">
-        <v>4</v>
-      </c>
-      <c r="B111" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C111" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E111" s="4"/>
+      <c r="E111" s="57" t="s">
+        <v>126</v>
+      </c>
       <c r="F111" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G111" s="20"/>
       <c r="H111" s="20"/>
     </row>
-    <row r="112" spans="1:8" ht="76.5">
-      <c r="A112" s="1">
-        <v>5</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C112" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E112" s="4"/>
+    <row r="112" spans="1:8" ht="15">
+      <c r="A112" s="73">
+        <v>2</v>
+      </c>
+      <c r="B112" s="75" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D112" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112" s="57" t="s">
+        <v>126</v>
+      </c>
       <c r="F112" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113" spans="1:8" ht="45.75">
-      <c r="A113" s="1">
-        <v>6</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E113" s="4"/>
+    <row r="113" spans="1:8" ht="15">
+      <c r="A113" s="74"/>
+      <c r="B113" s="76"/>
+      <c r="C113" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D113" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="E113" s="57" t="s">
+        <v>126</v>
+      </c>
       <c r="F113" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G113" s="20"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114" spans="1:8" ht="76.5">
-      <c r="A114" s="1">
-        <v>7</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C114" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E114" s="4"/>
+    <row r="114" spans="1:8" ht="15">
+      <c r="A114" s="58">
+        <v>3</v>
+      </c>
+      <c r="B114" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="D114" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114" s="57" t="s">
+        <v>126</v>
+      </c>
       <c r="F114" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G114" s="20"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115" spans="1:8" ht="91.5">
-      <c r="A115" s="1">
-        <v>8</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E115" s="4"/>
-      <c r="F115" s="1"/>
+    <row r="115" spans="1:8" ht="30.75">
+      <c r="A115" s="58">
+        <v>4</v>
+      </c>
+      <c r="B115" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C115" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D115" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116" spans="1:8" ht="60.75">
-      <c r="A116" s="1">
-        <v>9</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C116" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E116" s="4"/>
-      <c r="F116" s="1"/>
+    <row r="116" spans="1:8" ht="15">
+      <c r="A116" s="73">
+        <v>5</v>
+      </c>
+      <c r="B116" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="C116" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D116" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E116" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
     </row>
     <row r="117" spans="1:8" ht="15">
-      <c r="A117" s="1">
-        <v>10</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C117" s="31" t="s">
+      <c r="A117" s="73"/>
+      <c r="B117" s="75"/>
+      <c r="C117" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="D117" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117" s="20"/>
+      <c r="H117" s="20"/>
+    </row>
+    <row r="118" spans="1:8" ht="15">
+      <c r="A118" s="73"/>
+      <c r="B118" s="75"/>
+      <c r="C118" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D118" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E118" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F118" s="1"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="20"/>
+    </row>
+    <row r="119" spans="1:8" ht="15">
+      <c r="A119" s="74"/>
+      <c r="B119" s="76"/>
+      <c r="C119" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="D119" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E119" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F119" s="1"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="20"/>
+    </row>
+    <row r="120" spans="1:8" ht="15">
+      <c r="A120" s="9">
+        <v>12</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C120" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E117" s="4"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="50"/>
-      <c r="H117" s="51"/>
-    </row>
-    <row r="118" spans="1:8" ht="15" customHeight="1">
-      <c r="A118" s="52">
-        <v>11</v>
-      </c>
-      <c r="B118" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="D118" s="75"/>
-      <c r="E118" s="76"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="14"/>
-      <c r="H118" s="15"/>
-    </row>
-    <row r="119" spans="1:8" ht="15">
-      <c r="A119" s="54" t="s">
+      <c r="D120" s="69"/>
+      <c r="E120" s="69"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="15"/>
+    </row>
+    <row r="121" spans="1:8" ht="15">
+      <c r="A121" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B119" s="55" t="s">
+      <c r="B121" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C119" s="55" t="s">
+      <c r="C121" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D119" s="55" t="s">
+      <c r="D121" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E119" s="55" t="s">
+      <c r="E121" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F119" s="12" t="s">
+      <c r="F121" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="G121" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H119" s="11" t="s">
+      <c r="H121" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15">
-      <c r="A120" s="56">
+    <row r="122" spans="1:8" ht="15">
+      <c r="A122" s="1">
         <v>1</v>
       </c>
-      <c r="B120" s="57" t="s">
+      <c r="B122" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C120" s="57" t="s">
+      <c r="C122" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D120" s="57" t="s">
+      <c r="D122" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E120" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
-    </row>
-    <row r="121" spans="1:8" ht="15">
-      <c r="A121" s="61">
-        <v>2</v>
-      </c>
-      <c r="B121" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="C121" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="D121" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E121" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
-    </row>
-    <row r="122" spans="1:8" ht="15">
-      <c r="A122" s="62"/>
-      <c r="B122" s="64"/>
-      <c r="C122" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="D122" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="E122" s="57" t="s">
-        <v>144</v>
-      </c>
+      <c r="E122" s="4"/>
       <c r="F122" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G122" s="20"/>
       <c r="H122" s="20"/>
     </row>
-    <row r="123" spans="1:8" ht="15">
-      <c r="A123" s="58">
-        <v>3</v>
-      </c>
-      <c r="B123" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="C123" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="D123" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E123" s="57" t="s">
-        <v>144</v>
-      </c>
+    <row r="123" spans="1:8" ht="121.5">
+      <c r="A123" s="1">
+        <v>2</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C123" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E123" s="4"/>
       <c r="F123" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124" spans="1:8" ht="30.75">
-      <c r="A124" s="58">
-        <v>4</v>
-      </c>
-      <c r="B124" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="C124" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D124" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E124" s="57" t="s">
+    <row r="124" spans="1:8" ht="106.5">
+      <c r="A124" s="1">
+        <v>3</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C124" s="19" t="s">
         <v>144</v>
       </c>
+      <c r="D124" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E124" s="4"/>
       <c r="F124" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125" spans="1:8" ht="15">
-      <c r="A125" s="61">
-        <v>5</v>
-      </c>
-      <c r="B125" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="C125" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="D125" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E125" s="57" t="s">
-        <v>144</v>
-      </c>
+    <row r="125" spans="1:8" ht="152.25">
+      <c r="A125" s="1">
+        <v>4</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C125" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E125" s="4"/>
       <c r="F125" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G125" s="20"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126" spans="1:8" ht="15">
-      <c r="A126" s="61"/>
-      <c r="B126" s="63"/>
-      <c r="C126" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="D126" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E126" s="57" t="s">
-        <v>144</v>
-      </c>
+    <row r="126" spans="1:8" ht="152.25">
+      <c r="A126" s="1">
+        <v>5</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E126" s="4"/>
       <c r="F126" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8" ht="15">
-      <c r="A127" s="61"/>
-      <c r="B127" s="63"/>
-      <c r="C127" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="D127" s="57" t="s">
+    <row r="127" spans="1:8" ht="152.25">
+      <c r="A127" s="1">
+        <v>6</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C127" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="E127" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="F127" s="1"/>
+      <c r="D127" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E127" s="4"/>
+      <c r="F127" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8" ht="15">
-      <c r="A128" s="62"/>
-      <c r="B128" s="64"/>
-      <c r="C128" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="D128" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E128" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="F128" s="1"/>
+    <row r="128" spans="1:8" ht="152.25">
+      <c r="A128" s="1">
+        <v>7</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G128" s="20"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129" spans="1:8" ht="15">
-      <c r="A129" s="9">
-        <v>12</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C129" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="D129" s="65"/>
-      <c r="E129" s="65"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="14"/>
-      <c r="H129" s="15"/>
-    </row>
-    <row r="130" spans="1:8" ht="15">
-      <c r="A130" s="11" t="s">
+    <row r="129" spans="1:8" ht="137.25">
+      <c r="A129" s="1">
+        <v>8</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="20"/>
+    </row>
+    <row r="130" spans="1:8" ht="30.75">
+      <c r="A130" s="1">
+        <v>9</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C130" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E130" s="4"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="50"/>
+      <c r="H130" s="51"/>
+    </row>
+    <row r="131" spans="1:8" ht="15">
+      <c r="A131" s="9">
+        <v>13</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C131" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="D131" s="69"/>
+      <c r="E131" s="69"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="14"/>
+      <c r="H131" s="15"/>
+    </row>
+    <row r="132" spans="1:8" ht="15">
+      <c r="A132" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B132" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C132" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D132" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E130" s="12" t="s">
+      <c r="E132" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F130" s="12" t="s">
+      <c r="F132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G130" s="12" t="s">
+      <c r="G132" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H130" s="11" t="s">
+      <c r="H132" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15">
-      <c r="A131" s="1">
+    <row r="133" spans="1:8" ht="15">
+      <c r="A133" s="1">
         <v>1</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B133" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C133" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E131" s="4"/>
-      <c r="F131" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G131" s="20"/>
-      <c r="H131" s="20"/>
-    </row>
-    <row r="132" spans="1:8" ht="121.5">
-      <c r="A132" s="1">
-        <v>2</v>
-      </c>
-      <c r="B132" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C132" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E132" s="4"/>
-      <c r="F132" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
-    </row>
-    <row r="133" spans="1:8" ht="106.5">
-      <c r="A133" s="1">
-        <v>3</v>
-      </c>
-      <c r="B133" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="1" t="s">
@@ -5298,18 +5190,18 @@
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8" ht="152.25">
+    <row r="134" spans="1:8" ht="60.75">
       <c r="A134" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B134" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="31" t="s">
-        <v>163</v>
+      <c r="C134" s="59" t="s">
+        <v>153</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="1" t="s">
@@ -5318,18 +5210,18 @@
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135" spans="1:8" ht="152.25">
+    <row r="135" spans="1:8" ht="60.75">
       <c r="A135" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B135" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="49" t="s">
-        <v>164</v>
+      <c r="C135" s="19" t="s">
+        <v>155</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="1" t="s">
@@ -5338,18 +5230,18 @@
       <c r="G135" s="20"/>
       <c r="H135" s="20"/>
     </row>
-    <row r="136" spans="1:8" ht="152.25">
+    <row r="136" spans="1:8" ht="30.75">
       <c r="A136" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B136" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C136" s="60" t="s">
-        <v>165</v>
+      <c r="C136" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="1" t="s">
@@ -5358,18 +5250,18 @@
       <c r="G136" s="20"/>
       <c r="H136" s="20"/>
     </row>
-    <row r="137" spans="1:8" ht="152.25">
+    <row r="137" spans="1:8" ht="76.5">
       <c r="A137" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B137" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C137" s="31" t="s">
-        <v>166</v>
+      <c r="C137" s="49" t="s">
+        <v>157</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="1" t="s">
@@ -5378,116 +5270,118 @@
       <c r="G137" s="20"/>
       <c r="H137" s="20"/>
     </row>
-    <row r="138" spans="1:8" ht="137.25">
+    <row r="138" spans="1:8" ht="60.75">
       <c r="A138" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B138" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C138" s="31" t="s">
-        <v>167</v>
+      <c r="C138" s="60" t="s">
+        <v>158</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E138" s="4"/>
-      <c r="F138" s="1"/>
+      <c r="F138" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G138" s="20"/>
       <c r="H138" s="20"/>
     </row>
-    <row r="139" spans="1:8" ht="30.75">
+    <row r="139" spans="1:8" ht="76.5">
       <c r="A139" s="1">
+        <v>7</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G139" s="20"/>
+      <c r="H139" s="20"/>
+    </row>
+    <row r="140" spans="1:8" ht="60.75">
+      <c r="A140" s="1">
+        <v>8</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C140" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E140" s="4"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="20"/>
+    </row>
+    <row r="141" spans="1:8" ht="15">
+      <c r="A141" s="9">
+        <v>14</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C141" s="69" t="s">
+        <v>162</v>
+      </c>
+      <c r="D141" s="69"/>
+      <c r="E141" s="69"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="14"/>
+      <c r="H141" s="15"/>
+    </row>
+    <row r="142" spans="1:8" ht="15">
+      <c r="A142" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G142" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H142" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B139" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C139" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E139" s="4"/>
-      <c r="F139" s="1"/>
-      <c r="G139" s="50"/>
-      <c r="H139" s="51"/>
-    </row>
-    <row r="140" spans="1:8" ht="15">
-      <c r="A140" s="9">
-        <v>13</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C140" s="65" t="s">
-        <v>170</v>
-      </c>
-      <c r="D140" s="65"/>
-      <c r="E140" s="65"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="14"/>
-      <c r="H140" s="15"/>
-    </row>
-    <row r="141" spans="1:8" ht="15">
-      <c r="A141" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B141" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D141" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E141" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F141" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G141" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H141" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="15">
-      <c r="A142" s="1">
+    </row>
+    <row r="143" spans="1:8" ht="15">
+      <c r="A143" s="1">
         <v>1</v>
       </c>
-      <c r="B142" s="19" t="s">
+      <c r="B143" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C142" s="19" t="s">
+      <c r="C143" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E142" s="4"/>
-      <c r="F142" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G142" s="20"/>
-      <c r="H142" s="20"/>
-    </row>
-    <row r="143" spans="1:8" ht="60.75">
-      <c r="A143" s="1">
-        <v>2</v>
-      </c>
-      <c r="B143" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C143" s="59" t="s">
-        <v>171</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="1" t="s">
@@ -5496,18 +5390,18 @@
       <c r="G143" s="20"/>
       <c r="H143" s="20"/>
     </row>
-    <row r="144" spans="1:8" ht="60.75">
+    <row r="144" spans="1:8" ht="15">
       <c r="A144" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C144" s="19" t="s">
-        <v>173</v>
+      <c r="C144" s="59" t="s">
+        <v>163</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="1" t="s">
@@ -5518,16 +5412,16 @@
     </row>
     <row r="145" spans="1:8" ht="30.75">
       <c r="A145" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B145" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C145" s="31" t="s">
-        <v>174</v>
+      <c r="C145" s="19" t="s">
+        <v>164</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="1" t="s">
@@ -5536,18 +5430,18 @@
       <c r="G145" s="20"/>
       <c r="H145" s="20"/>
     </row>
-    <row r="146" spans="1:8" ht="76.5">
+    <row r="146" spans="1:8" ht="30.75">
       <c r="A146" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B146" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C146" s="49" t="s">
-        <v>175</v>
+        <v>18</v>
+      </c>
+      <c r="C146" s="31" t="s">
+        <v>165</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="1" t="s">
@@ -5556,118 +5450,120 @@
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147" spans="1:8" ht="60.75">
-      <c r="A147" s="1">
+    <row r="147" spans="1:8" ht="15">
+      <c r="A147" s="9">
+        <v>15</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C147" s="69" t="s">
+        <v>167</v>
+      </c>
+      <c r="D147" s="69"/>
+      <c r="E147" s="69"/>
+      <c r="F147" s="9"/>
+      <c r="G147" s="14"/>
+      <c r="H147" s="15"/>
+    </row>
+    <row r="148" spans="1:8" ht="15">
+      <c r="A148" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B147" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C147" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E147" s="4"/>
-      <c r="F147" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
-    </row>
-    <row r="148" spans="1:8" ht="76.5">
-      <c r="A148" s="1">
+      <c r="F148" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B148" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C148" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E148" s="4"/>
-      <c r="F148" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
-    </row>
-    <row r="149" spans="1:8" ht="60.75">
+      <c r="G148" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H148" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="15">
       <c r="A149" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C149" s="31" t="s">
-        <v>178</v>
+        <v>18</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="E149" s="4"/>
-      <c r="F149" s="1"/>
+      <c r="F149" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G149" s="20"/>
       <c r="H149" s="20"/>
     </row>
-    <row r="150" spans="1:8" ht="15">
-      <c r="A150" s="9">
-        <v>14</v>
-      </c>
-      <c r="B150" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C150" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="D150" s="65"/>
-      <c r="E150" s="65"/>
-      <c r="F150" s="9"/>
-      <c r="G150" s="14"/>
-      <c r="H150" s="15"/>
+    <row r="150" spans="1:8" ht="60.75">
+      <c r="A150" s="1">
+        <v>2</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C150" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E150" s="4"/>
+      <c r="F150" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G150" s="20"/>
+      <c r="H150" s="20"/>
     </row>
     <row r="151" spans="1:8" ht="15">
-      <c r="A151" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B151" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C151" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D151" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F151" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G151" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H151" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="A151" s="1">
+        <v>3</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E151" s="4"/>
+      <c r="F151" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G151" s="20"/>
+      <c r="H151" s="20"/>
     </row>
     <row r="152" spans="1:8" ht="15">
       <c r="A152" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B152" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C152" s="19" t="s">
-        <v>48</v>
+      <c r="C152" s="31" t="s">
+        <v>171</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="1" t="s">
@@ -5676,18 +5572,18 @@
       <c r="G152" s="20"/>
       <c r="H152" s="20"/>
     </row>
-    <row r="153" spans="1:8" ht="15">
+    <row r="153" spans="1:8" ht="60.75">
       <c r="A153" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C153" s="59" t="s">
-        <v>181</v>
+        <v>172</v>
+      </c>
+      <c r="C153" s="31" t="s">
+        <v>173</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="1" t="s">
@@ -5696,100 +5592,100 @@
       <c r="G153" s="20"/>
       <c r="H153" s="20"/>
     </row>
-    <row r="154" spans="1:8" ht="30.75">
-      <c r="A154" s="1">
+    <row r="154" spans="1:8" ht="15">
+      <c r="A154" s="9">
+        <v>16</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C154" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="D154" s="61"/>
+      <c r="E154" s="61"/>
+      <c r="F154" s="9"/>
+      <c r="G154" s="14"/>
+      <c r="H154" s="15"/>
+    </row>
+    <row r="155" spans="1:8" ht="15">
+      <c r="A155" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F155" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="15">
+      <c r="A156" s="1">
+        <v>1</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="20"/>
+      <c r="H156" s="20"/>
+    </row>
+    <row r="157" spans="1:8" ht="76.5">
+      <c r="A157" s="1">
+        <v>2</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C157" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E157" s="4"/>
+      <c r="F157" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" s="20"/>
+      <c r="H157" s="20"/>
+    </row>
+    <row r="158" spans="1:8" ht="106.5">
+      <c r="A158" s="1">
         <v>3</v>
       </c>
-      <c r="B154" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E154" s="4"/>
-      <c r="F154" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G154" s="20"/>
-      <c r="H154" s="20"/>
-    </row>
-    <row r="155" spans="1:8" ht="30.75">
-      <c r="A155" s="1">
-        <v>4</v>
-      </c>
-      <c r="B155" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C155" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E155" s="4"/>
-      <c r="F155" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G155" s="20"/>
-      <c r="H155" s="20"/>
-    </row>
-    <row r="156" spans="1:8" ht="15">
-      <c r="A156" s="9">
-        <v>15</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C156" s="65" t="s">
-        <v>185</v>
-      </c>
-      <c r="D156" s="65"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="9"/>
-      <c r="G156" s="14"/>
-      <c r="H156" s="15"/>
-    </row>
-    <row r="157" spans="1:8" ht="15">
-      <c r="A157" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B157" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C157" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E157" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F157" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G157" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H157" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="15">
-      <c r="A158" s="1">
-        <v>1</v>
-      </c>
       <c r="B158" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C158" s="19" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="1" t="s">
@@ -5798,18 +5694,18 @@
       <c r="G158" s="20"/>
       <c r="H158" s="20"/>
     </row>
-    <row r="159" spans="1:8" ht="60.75">
+    <row r="159" spans="1:8" ht="76.5">
       <c r="A159" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B159" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C159" s="59" t="s">
-        <v>186</v>
+      <c r="C159" s="31" t="s">
+        <v>178</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="1" t="s">
@@ -5818,18 +5714,18 @@
       <c r="G159" s="20"/>
       <c r="H159" s="20"/>
     </row>
-    <row r="160" spans="1:8" ht="15">
+    <row r="160" spans="1:8" ht="60.75">
       <c r="A160" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B160" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C160" s="19" t="s">
-        <v>187</v>
+        <v>23</v>
+      </c>
+      <c r="C160" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="1" t="s">
@@ -5838,18 +5734,18 @@
       <c r="G160" s="20"/>
       <c r="H160" s="20"/>
     </row>
-    <row r="161" spans="1:8" ht="15">
+    <row r="161" spans="1:8" ht="76.5">
       <c r="A161" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B161" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C161" s="31" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="1" t="s">
@@ -5858,80 +5754,80 @@
       <c r="G161" s="20"/>
       <c r="H161" s="20"/>
     </row>
-    <row r="162" spans="1:8" ht="60.75">
-      <c r="A162" s="1">
-        <v>5</v>
-      </c>
-      <c r="B162" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C162" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E162" s="4"/>
-      <c r="F162" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G162" s="20"/>
-      <c r="H162" s="20"/>
+    <row r="162" spans="1:8" ht="15">
+      <c r="A162" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C162" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D162" s="61"/>
+      <c r="E162" s="61"/>
+      <c r="F162" s="9"/>
+      <c r="G162" s="14"/>
+      <c r="H162" s="15"/>
     </row>
     <row r="163" spans="1:8" ht="15">
-      <c r="A163" s="9">
+      <c r="A163" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B163" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C163" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="D163" s="67"/>
-      <c r="E163" s="67"/>
-      <c r="F163" s="9"/>
-      <c r="G163" s="14"/>
-      <c r="H163" s="15"/>
-    </row>
-    <row r="164" spans="1:8" ht="15">
-      <c r="A164" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B164" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C164" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D164" s="12" t="s">
+      <c r="D163" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E164" s="12" t="s">
+      <c r="E163" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F164" s="12" t="s">
+      <c r="F163" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G164" s="12" t="s">
+      <c r="G163" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H164" s="11" t="s">
+      <c r="H163" s="11" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="164" spans="1:8" ht="76.5">
+      <c r="A164" s="1">
+        <v>1</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C164" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E164" s="4"/>
+      <c r="F164" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="20"/>
+      <c r="H164" s="20"/>
     </row>
     <row r="165" spans="1:8" ht="15">
       <c r="A165" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B165" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="1" t="s">
@@ -5940,188 +5836,15 @@
       <c r="G165" s="20"/>
       <c r="H165" s="20"/>
     </row>
-    <row r="166" spans="1:8" ht="76.5">
-      <c r="A166" s="1">
-        <v>2</v>
-      </c>
-      <c r="B166" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C166" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E166" s="4"/>
-      <c r="F166" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G166" s="20"/>
-      <c r="H166" s="20"/>
-    </row>
-    <row r="167" spans="1:8" ht="106.5">
-      <c r="A167" s="1">
-        <v>3</v>
-      </c>
-      <c r="B167" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C167" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E167" s="4"/>
-      <c r="F167" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G167" s="20"/>
-      <c r="H167" s="20"/>
-    </row>
-    <row r="168" spans="1:8" ht="76.5">
-      <c r="A168" s="1">
-        <v>4</v>
-      </c>
-      <c r="B168" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C168" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E168" s="4"/>
-      <c r="F168" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G168" s="20"/>
-      <c r="H168" s="20"/>
-    </row>
-    <row r="169" spans="1:8" ht="60.75">
-      <c r="A169" s="1">
-        <v>5</v>
-      </c>
-      <c r="B169" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C169" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E169" s="4"/>
-      <c r="F169" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G169" s="20"/>
-      <c r="H169" s="20"/>
-    </row>
-    <row r="170" spans="1:8" ht="76.5">
-      <c r="A170" s="1">
-        <v>6</v>
-      </c>
-      <c r="B170" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C170" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E170" s="4"/>
-      <c r="F170" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G170" s="20"/>
-      <c r="H170" s="20"/>
-    </row>
-    <row r="171" spans="1:8" ht="15">
-      <c r="A171" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B171" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C171" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D171" s="67"/>
-      <c r="E171" s="67"/>
-      <c r="F171" s="9"/>
-      <c r="G171" s="14"/>
-      <c r="H171" s="15"/>
-    </row>
-    <row r="172" spans="1:8" ht="15">
-      <c r="A172" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B172" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C172" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D172" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E172" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F172" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G172" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H172" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" ht="76.5">
-      <c r="A173" s="1">
-        <v>1</v>
-      </c>
-      <c r="B173" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C173" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E173" s="4"/>
-      <c r="F173" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G173" s="20"/>
-      <c r="H173" s="20"/>
-    </row>
-    <row r="174" spans="1:8" ht="15">
-      <c r="A174" s="1">
-        <v>2</v>
-      </c>
-      <c r="B174" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C174" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E174" s="4"/>
-      <c r="F174" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G174" s="20"/>
-      <c r="H174" s="20"/>
-    </row>
+    <row r="166" spans="1:8" ht="15"/>
+    <row r="167" spans="1:8" ht="15"/>
+    <row r="168" spans="1:8" ht="15"/>
+    <row r="169" spans="1:8" ht="15"/>
+    <row r="170" spans="1:8" ht="15"/>
+    <row r="171" spans="1:8" ht="15"/>
+    <row r="172" spans="1:8" ht="15"/>
+    <row r="173" spans="1:8" ht="15"/>
+    <row r="174" spans="1:8" ht="15"/>
     <row r="175" spans="1:8" ht="15"/>
     <row r="176" spans="1:8" ht="15"/>
     <row r="177" ht="15"/>
@@ -6132,39 +5855,39 @@
     <row r="182" ht="15"/>
     <row r="183" ht="15"/>
   </sheetData>
-  <autoFilter ref="A3:H41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="28">
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="H100:H101"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="H104:H105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A116:A119"/>
+    <mergeCell ref="B116:B119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C62:E62"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="A125:A128"/>
-    <mergeCell ref="B125:B128"/>
-    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="F93:F94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="C147:E147"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F106:F1048576 F3:F94">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="F1 F97:F1048576 F3:F85">
     <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -6175,7 +5898,7 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F95:F100 F102 F104">
+  <conditionalFormatting sqref="F86:F91 F93 F95">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -6187,7 +5910,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F60:F70 F17:F26 F42:F53 F56:F57 F29:F39 F73:F83 F86:F94 F6:F14" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F51:F61 F17:F26 F33:F44 F47:F48 F64:F74 F77:F85 F6:F14 F29:F30" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -6208,7 +5931,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
       <c r="A1" s="77" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="77"/>
@@ -6220,26 +5943,26 @@
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6247,7 +5970,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -6260,12 +5983,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6383,13 +6103,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6397,5 +6120,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29325"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A62829-5784-4A3C-985E-75691FC15AB8}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98D4F94-559A-4DBC-A82D-31F5D864BF95}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="185">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -200,217 +200,39 @@
     <t>Abdo</t>
   </si>
   <si>
-    <t>20.12.2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm,  Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer, Seah Qiao Ling, Tristan Scheuermann,James Cherupillet</t>
-  </si>
-  <si>
-    <t>Adam: thanks for talking about the data recording. It would be great of you could show a reduced version (5 classes) of your ontology as well. Make sure that you explain well to Hamado that he can select the key 5-8 most important classes and relationships of the Ball Mill</t>
-  </si>
-  <si>
-    <t>Hans</t>
-  </si>
-  <si>
-    <t>Adjara: I liked a lot your reduced class approach. Make sure that you explain well to Adam that he can select the key 5-8 most important classes and relationships of the Music application</t>
-  </si>
-  <si>
-    <t>Alicia: I liked a lot your reduced class approach. Make sure that you explain well to Adjara that he can select the key 3-8 most important classes and relationships of the cowpea application. Greta pictures of the sensors, also hyperlink them</t>
-  </si>
-  <si>
-    <r>
-      <t>Charles:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I liked a lot your reduced classes. Make sure that you explain well to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Alicia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> that he can select the key 5-8 most important classes and relationships of the irrigation application</t>
-    </r>
-  </si>
-  <si>
-    <t>Lukas; It would be could show a reduced version (5 classes) ontology. Make sure that you explain well to Charles that he can select the key 3-8 most important classes and relationships of the Smart Dryer application</t>
-  </si>
-  <si>
-    <r>
-      <t>Boris: I liked a lot your reduced classes. Make sure that you explain well to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Lukas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> that he can select the key 5-8 most important classes and relationships of the Face recognition</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Gertrude: It would be could show a reduced version (5 classes) ontology. Make sure that you explain well to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Boris</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> that he can select the key 5-8 most important classes and relationships of weather station</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Wilfried: It would be could show a reduced version (5 classes) ontology. Make sure that you explain well to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gertrude</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> that he can select the key 5-8 most important classes and relationships of weather station</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Hamado: I liked a lot your reduced classes and how you integrated the Feedback from Abdelgafar. Make sure that you explain well to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Wilfried</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF242424"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> that he can select the key 5-8 most important classes and relationships of your picture</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>General:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>  
-We made great progress in reducing the complexity of the ontology by showing just the most important classes.
-Make sure that the reduce classes view is part of the bigger ontology
-Next time explain what she / he is doing by using the ontology and select the most important picture you think which explains his/her project. Add two new line block one with the Logo and the ontology of your partners project  
-Thanks for being shorter in the presentation and only talk about for what we see on the homepage.</t>
-    </r>
-  </si>
-  <si>
-    <t>Presentation homepage on Infineon side</t>
-  </si>
-  <si>
-    <t>QL</t>
-  </si>
-  <si>
-    <t>27.12.2024</t>
-  </si>
-  <si>
-    <t>Abdelgafar Ismail,  Diallo Fadilatou, Excellence program Students</t>
-  </si>
-  <si>
-    <t>Building a sustainable farm. 
-	²  Farm Construction: 
-	   - Build a farm 
-	   - Determine how many of your projects  could be used effectively.
-	² Output Optimization: 
-	   - Aim to increase output and reduce waste.
-	²  Idea Integration: 
-	   - Reuse your existing projects within the overall concept.
-	²  Sustainability:
-	   - Focus on building a sustainable farm.
-	²  Ontology Connections:
-	   - Link your ontologies to work together.
-	²  Process Planning:
-	   - Consider different steps in building the farm, such as preparing resources like land or a pond.</t>
+    <t>26.09.2025</t>
+  </si>
+  <si>
+    <t>Abdelgafar Ismail,  Diallo Fadilatou, Excellence program Students,Botho Schanze</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General: Please complete the excel sheet and complete the swimlane diagram </t>
+  </si>
+  <si>
+    <t>Sustainable_farm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.02.2025
+</t>
+  </si>
+  <si>
+    <t>Hans Ehm, Abdelgafar Ismail, Diallo Fadilatou, Excellence program Students , Botho Schanze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Show numbers in 6,7 instead of 6,666667;
+Farm size is 2 ha, please make sure to do calculations accordingly;
+Use full names instead of abbreviations;
+Use one color in the excel spreadsheets to make every sheet uniform;
+Ball Mill Grinder:Prices should be in €, just to be consistent; Why two lines with ----; 
+I suggest that you go for average per month and then calculate the break even;  
+Solar traking : Wy do you need 37kWh?
+No reesa: What are  see the benefit ?
+Face recognition; separate the numbers from the unit not 
+Check excel sheet for feedbacks</t>
   </si>
   <si>
     <t>03.01.2025</t>
@@ -457,7 +279,7 @@
 Think about virtual big, think about demonstrators small – doable within 4-8 weeks, plan medium what can be done in one year, two years, five years</t>
   </si>
   <si>
-    <t>Open</t>
+    <t>Hans</t>
   </si>
   <si>
     <t>10.01.2025</t>
@@ -852,7 +674,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -923,21 +745,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1445,7 +1252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1541,51 +1348,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1594,43 +1395,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1648,25 +1452,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2549,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="5" customWidth="1"/>
@@ -2561,16 +2365,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -3089,11 +2893,11 @@
       <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
@@ -3164,18 +2968,18 @@
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" ht="15">
       <c r="A31" s="9">
         <v>4</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
@@ -3206,7 +3010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="15">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -3221,12 +3025,12 @@
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G33" s="20"/>
       <c r="H33" s="20"/>
     </row>
-    <row r="34" spans="1:8" ht="57.95">
+    <row r="34" spans="1:8" ht="30.75">
       <c r="A34" s="1">
         <v>2</v>
       </c>
@@ -3234,70 +3038,74 @@
         <v>23</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="20"/>
+        <v>53</v>
+      </c>
+      <c r="G34" s="59" t="s">
+        <v>55</v>
+      </c>
       <c r="H34" s="20"/>
     </row>
-    <row r="35" spans="1:8" ht="43.5">
-      <c r="A35" s="1">
-        <v>3</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-    </row>
-    <row r="36" spans="1:8" ht="57.95">
-      <c r="A36" s="1">
-        <v>4</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="29" t="s">
+    <row r="35" spans="1:8" ht="30.75">
+      <c r="A35" s="9">
+        <v>5</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-    </row>
-    <row r="37" spans="1:8" ht="43.5">
+      <c r="C35" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>57</v>
+        <v>18</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="1" t="s">
@@ -3306,78 +3114,80 @@
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
     </row>
-    <row r="38" spans="1:8" ht="57.95">
+    <row r="38" spans="1:8" ht="213">
       <c r="A38" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="30" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
     </row>
-    <row r="39" spans="1:8" ht="43.5">
-      <c r="A39" s="1">
+    <row r="39" spans="1:8">
+      <c r="A39" s="9">
+        <v>6</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-    </row>
-    <row r="40" spans="1:8" ht="43.5">
-      <c r="A40" s="1">
+      <c r="G40" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-    </row>
-    <row r="41" spans="1:8" ht="43.5">
+      <c r="H40" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>61</v>
+        <v>18</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="1" t="s">
@@ -3386,18 +3196,18 @@
       <c r="G41" s="20"/>
       <c r="H41" s="20"/>
     </row>
-    <row r="42" spans="1:8" ht="57.95">
+    <row r="42" spans="1:8" ht="29.1">
       <c r="A42" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="31" t="s">
-        <v>62</v>
+      <c r="C42" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="1" t="s">
@@ -3406,18 +3216,18 @@
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
     </row>
-    <row r="43" spans="1:8" ht="159.6">
+    <row r="43" spans="1:8" ht="57.95">
       <c r="A43" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="33" t="s">
-        <v>63</v>
+      <c r="C43" s="29" t="s">
+        <v>62</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="1" t="s">
@@ -3426,18 +3236,18 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" ht="43.5">
       <c r="A44" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>64</v>
+        <v>23</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="1" t="s">
@@ -3446,60 +3256,58 @@
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="9">
+    <row r="45" spans="1:8" ht="72.599999999999994">
+      <c r="A45" s="1">
         <v>5</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+    </row>
+    <row r="46" spans="1:8" ht="43.5">
+      <c r="A46" s="1">
+        <v>6</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+    </row>
+    <row r="47" spans="1:8" ht="43.5">
+      <c r="A47" s="1">
+        <v>7</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="15"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="1">
-        <v>1</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="1" t="s">
@@ -3508,142 +3316,136 @@
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
     </row>
-    <row r="48" spans="1:8" ht="304.5">
+    <row r="48" spans="1:8" ht="43.5">
       <c r="A48" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>68</v>
+        <v>23</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="E48" s="4"/>
       <c r="F48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="9">
-        <v>6</v>
-      </c>
-      <c r="B49" s="10" t="s">
+    <row r="49" spans="1:8" ht="43.5">
+      <c r="A49" s="1">
+        <v>9</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" spans="1:8" ht="72.599999999999994">
+      <c r="A50" s="1">
+        <v>10</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="D50" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+    </row>
+    <row r="51" spans="1:8" ht="188.45">
+      <c r="A51" s="1">
+        <v>11</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="15"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="1">
-        <v>1</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D51" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
     </row>
-    <row r="52" spans="1:8" ht="29.1">
-      <c r="A52" s="1">
-        <v>2</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-    </row>
-    <row r="53" spans="1:8" ht="57.95">
-      <c r="A53" s="1">
-        <v>3</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" s="29" t="s">
+    <row r="52" spans="1:8">
+      <c r="A52" s="9">
+        <v>7</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-    </row>
-    <row r="54" spans="1:8" ht="43.5">
+      <c r="C52" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="15"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C54" s="29" t="s">
-        <v>73</v>
+        <v>18</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="1" t="s">
@@ -3654,16 +3456,16 @@
     </row>
     <row r="55" spans="1:8" ht="72.599999999999994">
       <c r="A55" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="31" t="s">
+      <c r="C55" s="30" t="s">
         <v>74</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="1" t="s">
@@ -3672,18 +3474,18 @@
       <c r="G55" s="20"/>
       <c r="H55" s="20"/>
     </row>
-    <row r="56" spans="1:8" ht="43.5">
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="32" t="s">
+      <c r="C56" s="29" t="s">
         <v>75</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="1" t="s">
@@ -3694,16 +3496,16 @@
     </row>
     <row r="57" spans="1:8" ht="43.5">
       <c r="A57" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="31" t="s">
-        <v>76</v>
+      <c r="C57" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="1" t="s">
@@ -3714,16 +3516,16 @@
     </row>
     <row r="58" spans="1:8" ht="43.5">
       <c r="A58" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="1" t="s">
@@ -3734,174 +3536,174 @@
     </row>
     <row r="59" spans="1:8" ht="43.5">
       <c r="A59" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C59" s="31" t="s">
-        <v>78</v>
+      <c r="C59" s="32" t="s">
+        <v>77</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E59" s="4"/>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G59" s="20"/>
       <c r="H59" s="20"/>
     </row>
-    <row r="60" spans="1:8" ht="72.599999999999994">
+    <row r="60" spans="1:8" ht="43.5">
       <c r="A60" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E60" s="4"/>
-      <c r="F60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8" ht="188.45">
+    <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C61" s="31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="1" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="9">
-        <v>7</v>
-      </c>
-      <c r="B62" s="10" t="s">
+    <row r="62" spans="1:8" ht="29.1">
+      <c r="A62" s="1">
+        <v>9</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+    </row>
+    <row r="63" spans="1:8" ht="29.1">
+      <c r="A63" s="1">
+        <v>10</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+    </row>
+    <row r="64" spans="1:8" ht="72.599999999999994">
+      <c r="A64" s="1">
+        <v>11</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="69" t="s">
-        <v>83</v>
-      </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="15"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H63" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="1">
-        <v>1</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D64" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="72.599999999999994">
-      <c r="A65" s="1">
-        <v>2</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" s="30" t="s">
+    <row r="65" spans="1:8">
+      <c r="A65" s="9">
+        <v>8</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="15"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="1">
-        <v>3</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E66" s="4"/>
-      <c r="F66" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-    </row>
-    <row r="67" spans="1:8" ht="43.5">
+      <c r="A66" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" s="29" t="s">
-        <v>73</v>
+        <v>18</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="1" t="s">
@@ -3910,18 +3712,18 @@
       <c r="G67" s="20"/>
       <c r="H67" s="20"/>
     </row>
-    <row r="68" spans="1:8" ht="43.5">
+    <row r="68" spans="1:8" ht="72.599999999999994">
       <c r="A68" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C68" s="31" t="s">
-        <v>86</v>
+      <c r="C68" s="30" t="s">
+        <v>85</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="1" t="s">
@@ -3930,18 +3732,18 @@
       <c r="G68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69" spans="1:8" ht="43.5">
+    <row r="69" spans="1:8" ht="57.95">
       <c r="A69" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="32" t="s">
-        <v>87</v>
+      <c r="C69" s="29" t="s">
+        <v>86</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="1" t="s">
@@ -3950,18 +3752,18 @@
       <c r="G69" s="20"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70" spans="1:8" ht="43.5">
+    <row r="70" spans="1:8" ht="76.5">
       <c r="A70" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="1" t="s">
@@ -3970,18 +3772,18 @@
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" ht="72.599999999999994">
       <c r="A71" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C71" s="31" t="s">
-        <v>89</v>
+      <c r="C71" s="32" t="s">
+        <v>88</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="1" t="s">
@@ -3990,1000 +3792,1000 @@
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
     </row>
-    <row r="72" spans="1:8" ht="29.1">
+    <row r="72" spans="1:8" ht="87">
       <c r="A72" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E72" s="4"/>
-      <c r="F72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
     </row>
-    <row r="73" spans="1:8" ht="29.1">
+    <row r="73" spans="1:8" ht="87">
       <c r="A73" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E73" s="4"/>
-      <c r="F73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
     </row>
-    <row r="74" spans="1:8" ht="72.599999999999994">
+    <row r="74" spans="1:8" ht="57.95">
       <c r="A74" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E74" s="4"/>
-      <c r="F74" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="F74" s="1"/>
       <c r="G74" s="20"/>
       <c r="H74" s="20"/>
     </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="9">
+    <row r="75" spans="1:8" ht="106.5">
+      <c r="A75" s="1">
+        <v>9</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+    </row>
+    <row r="76" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A76" s="33">
+        <v>9</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="62"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="15"/>
+    </row>
+    <row r="77" spans="1:8" s="35" customFormat="1" ht="15.75">
+      <c r="A77" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="15"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H76" s="11" t="s">
+      <c r="H77" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="1">
+    <row r="78" spans="1:8" ht="16.5">
+      <c r="A78" s="38">
         <v>1</v>
       </c>
-      <c r="B77" s="19" t="s">
+      <c r="B78" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C78" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D78" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E77" s="4"/>
-      <c r="F77" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-    </row>
-    <row r="78" spans="1:8" ht="72.599999999999994">
-      <c r="A78" s="1">
-        <v>2</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C78" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="4"/>
+      <c r="E78" s="40"/>
       <c r="F78" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G78" s="20"/>
       <c r="H78" s="20"/>
     </row>
-    <row r="79" spans="1:8" ht="57.95">
-      <c r="A79" s="1">
-        <v>3</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D79" s="1" t="s">
+    <row r="79" spans="1:8" ht="46.5">
+      <c r="A79" s="41">
+        <v>2</v>
+      </c>
+      <c r="B79" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E79" s="4"/>
+      <c r="E79" s="43"/>
       <c r="F79" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G79" s="20"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80" spans="1:8" ht="76.5">
-      <c r="A80" s="1">
-        <v>4</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E80" s="4"/>
+    <row r="80" spans="1:8" ht="46.5">
+      <c r="A80" s="44"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
       <c r="F80" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81" spans="1:8" ht="72.599999999999994">
-      <c r="A81" s="1">
+    <row r="81" spans="1:8" ht="46.5">
+      <c r="A81" s="41">
+        <v>3</v>
+      </c>
+      <c r="B81" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="43"/>
+      <c r="F81" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="20"/>
+      <c r="H81" s="66"/>
+    </row>
+    <row r="82" spans="1:8" ht="46.5">
+      <c r="A82" s="44"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="65"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="67"/>
+    </row>
+    <row r="83" spans="1:8" ht="30.75">
+      <c r="A83" s="41">
+        <v>4</v>
+      </c>
+      <c r="B83" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="43"/>
+      <c r="F83" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="66"/>
+      <c r="H83" s="66"/>
+    </row>
+    <row r="84" spans="1:8" ht="61.5">
+      <c r="A84" s="44"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="45"/>
+      <c r="E84" s="45"/>
+      <c r="F84" s="65"/>
+      <c r="G84" s="67"/>
+      <c r="H84" s="67"/>
+    </row>
+    <row r="85" spans="1:8" ht="30.75">
+      <c r="A85" s="41">
         <v>5</v>
       </c>
-      <c r="B81" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="B85" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E81" s="4"/>
-      <c r="F81" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-    </row>
-    <row r="82" spans="1:8" ht="87">
-      <c r="A82" s="1">
+      <c r="E85" s="43"/>
+      <c r="F85" s="64"/>
+      <c r="G85" s="66"/>
+      <c r="H85" s="66"/>
+    </row>
+    <row r="86" spans="1:8" ht="30.75">
+      <c r="A86" s="44"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" s="45"/>
+      <c r="E86" s="45"/>
+      <c r="F86" s="65"/>
+      <c r="G86" s="67"/>
+      <c r="H86" s="67"/>
+    </row>
+    <row r="87" spans="1:8" ht="15">
+      <c r="A87" s="9">
+        <v>10</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="15"/>
+    </row>
+    <row r="88" spans="1:8" ht="15">
+      <c r="A88" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B82" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C82" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E82" s="4"/>
-      <c r="F82" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G82" s="20"/>
-      <c r="H82" s="20"/>
-    </row>
-    <row r="83" spans="1:8" ht="87">
-      <c r="A83" s="1">
+      <c r="F88" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B83" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C83" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E83" s="4"/>
-      <c r="F83" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-    </row>
-    <row r="84" spans="1:8" ht="57.95">
-      <c r="A84" s="1">
+      <c r="G88" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B84" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C84" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E84" s="4"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-    </row>
-    <row r="85" spans="1:8" ht="106.5">
-      <c r="A85" s="1">
+      <c r="H88" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C85" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E85" s="4"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-    </row>
-    <row r="86" spans="1:8" s="37" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A86" s="35">
-        <v>9</v>
-      </c>
-      <c r="B86" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C86" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D86" s="63"/>
-      <c r="E86" s="64"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="15"/>
-    </row>
-    <row r="87" spans="1:8" s="37" customFormat="1" ht="15.75">
-      <c r="A87" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="D87" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G87" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H87" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="16.5">
-      <c r="A88" s="40">
+    </row>
+    <row r="89" spans="1:8" ht="15">
+      <c r="A89" s="1">
         <v>1</v>
       </c>
-      <c r="B88" s="41" t="s">
+      <c r="B89" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C88" s="41" t="s">
+      <c r="C89" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D88" s="41" t="s">
+      <c r="D89" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E88" s="42"/>
-      <c r="F88" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-    </row>
-    <row r="89" spans="1:8" ht="46.5">
-      <c r="A89" s="43">
-        <v>2</v>
-      </c>
-      <c r="B89" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D89" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E89" s="45"/>
+      <c r="E89" s="4"/>
       <c r="F89" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G89" s="20"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90" spans="1:8" ht="46.5">
-      <c r="A90" s="46"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D90" s="47"/>
-      <c r="E90" s="47"/>
+    <row r="90" spans="1:8" ht="60.75">
+      <c r="A90" s="1">
+        <v>2</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E90" s="4"/>
       <c r="F90" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91" spans="1:8" ht="46.5">
-      <c r="A91" s="43">
+    <row r="91" spans="1:8" ht="30.75">
+      <c r="A91" s="1">
         <v>3</v>
       </c>
-      <c r="B91" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" s="44" t="s">
+      <c r="B91" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+    </row>
+    <row r="92" spans="1:8" ht="76.5">
+      <c r="A92" s="1">
+        <v>4</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="D91" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91" s="45"/>
-      <c r="F91" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" s="20"/>
-      <c r="H91" s="67"/>
-    </row>
-    <row r="92" spans="1:8" ht="46.5">
-      <c r="A92" s="46"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="48" t="s">
+      <c r="D92" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+    </row>
+    <row r="93" spans="1:8" ht="76.5">
+      <c r="A93" s="1">
+        <v>5</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="D92" s="47"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="66"/>
-      <c r="G92" s="20"/>
-      <c r="H92" s="68"/>
-    </row>
-    <row r="93" spans="1:8" ht="30.75">
-      <c r="A93" s="43">
-        <v>4</v>
-      </c>
-      <c r="B93" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="44" t="s">
+      <c r="D93" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="20"/>
+      <c r="H93" s="20"/>
+    </row>
+    <row r="94" spans="1:8" ht="45.75">
+      <c r="A94" s="1">
+        <v>6</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C94" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="D93" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E93" s="45"/>
-      <c r="F93" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="G93" s="67"/>
-      <c r="H93" s="67"/>
-    </row>
-    <row r="94" spans="1:8" ht="61.5">
-      <c r="A94" s="46"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="48" t="s">
+      <c r="D94" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="20"/>
+      <c r="H94" s="20"/>
+    </row>
+    <row r="95" spans="1:8" ht="76.5">
+      <c r="A95" s="1">
+        <v>7</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="D94" s="47"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="68"/>
-      <c r="H94" s="68"/>
-    </row>
-    <row r="95" spans="1:8" ht="30.75">
-      <c r="A95" s="43">
-        <v>5</v>
-      </c>
-      <c r="B95" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" s="44" t="s">
+      <c r="D95" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="20"/>
+      <c r="H95" s="20"/>
+    </row>
+    <row r="96" spans="1:8" ht="91.5">
+      <c r="A96" s="1">
+        <v>8</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D95" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E95" s="45"/>
-      <c r="F95" s="65"/>
-      <c r="G95" s="67"/>
-      <c r="H95" s="67"/>
-    </row>
-    <row r="96" spans="1:8" ht="30.75">
-      <c r="A96" s="46"/>
-      <c r="B96" s="47"/>
-      <c r="C96" s="48" t="s">
+      <c r="D96" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="20"/>
+      <c r="H96" s="20"/>
+    </row>
+    <row r="97" spans="1:8" ht="60.75">
+      <c r="A97" s="1">
+        <v>9</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="D96" s="47"/>
-      <c r="E96" s="47"/>
-      <c r="F96" s="66"/>
-      <c r="G96" s="68"/>
-      <c r="H96" s="68"/>
-    </row>
-    <row r="97" spans="1:8" ht="15">
-      <c r="A97" s="9">
+      <c r="D97" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="20"/>
+      <c r="H97" s="20"/>
+    </row>
+    <row r="98" spans="1:8" ht="15">
+      <c r="A98" s="1">
         <v>10</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B98" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="C97" s="69" t="s">
+      <c r="D98" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="49"/>
+    </row>
+    <row r="99" spans="1:8" ht="15" customHeight="1">
+      <c r="A99" s="50">
+        <v>11</v>
+      </c>
+      <c r="B99" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="D97" s="69"/>
-      <c r="E97" s="69"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="15"/>
-    </row>
-    <row r="98" spans="1:8" ht="15">
-      <c r="A98" s="11" t="s">
+      <c r="C99" s="69" t="s">
+        <v>115</v>
+      </c>
+      <c r="D99" s="69"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="15"/>
+    </row>
+    <row r="100" spans="1:8" ht="15">
+      <c r="A100" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B100" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C98" s="11" t="s">
+      <c r="C100" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D100" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="E100" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="F98" s="12" t="s">
+      <c r="F100" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G98" s="12" t="s">
+      <c r="G100" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H98" s="11" t="s">
+      <c r="H100" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15">
-      <c r="A99" s="1">
+    <row r="101" spans="1:8" ht="15">
+      <c r="A101" s="54">
         <v>1</v>
       </c>
-      <c r="B99" s="19" t="s">
+      <c r="B101" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C101" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D101" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E99" s="4"/>
-      <c r="F99" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
-    </row>
-    <row r="100" spans="1:8" ht="60.75">
-      <c r="A100" s="1">
-        <v>2</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E100" s="4"/>
-      <c r="F100" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-    </row>
-    <row r="101" spans="1:8" ht="30.75">
-      <c r="A101" s="1">
-        <v>3</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" s="19" t="s">
+      <c r="E101" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E101" s="4"/>
       <c r="F101" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G101" s="20"/>
       <c r="H101" s="20"/>
     </row>
-    <row r="102" spans="1:8" ht="76.5">
-      <c r="A102" s="1">
-        <v>4</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102" s="31" t="s">
+    <row r="102" spans="1:8" ht="15">
+      <c r="A102" s="72">
+        <v>2</v>
+      </c>
+      <c r="B102" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E102" s="4"/>
+      <c r="C102" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D102" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E102" s="55" t="s">
+        <v>116</v>
+      </c>
       <c r="F102" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G102" s="20"/>
       <c r="H102" s="20"/>
     </row>
-    <row r="103" spans="1:8" ht="76.5">
-      <c r="A103" s="1">
-        <v>5</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C103" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E103" s="4"/>
+    <row r="103" spans="1:8" ht="15">
+      <c r="A103" s="73"/>
+      <c r="B103" s="75"/>
+      <c r="C103" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D103" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="E103" s="55" t="s">
+        <v>116</v>
+      </c>
       <c r="F103" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G103" s="20"/>
       <c r="H103" s="20"/>
     </row>
-    <row r="104" spans="1:8" ht="45.75">
-      <c r="A104" s="1">
-        <v>6</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104" s="31" t="s">
+    <row r="104" spans="1:8" ht="15">
+      <c r="A104" s="56">
+        <v>3</v>
+      </c>
+      <c r="B104" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C104" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="D104" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E104" s="4"/>
+      <c r="E104" s="55" t="s">
+        <v>116</v>
+      </c>
       <c r="F104" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G104" s="20"/>
       <c r="H104" s="20"/>
     </row>
-    <row r="105" spans="1:8" ht="76.5">
-      <c r="A105" s="1">
-        <v>7</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C105" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E105" s="4"/>
+    <row r="105" spans="1:8" ht="30.75">
+      <c r="A105" s="56">
+        <v>4</v>
+      </c>
+      <c r="B105" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D105" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E105" s="55" t="s">
+        <v>116</v>
+      </c>
       <c r="F105" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G105" s="20"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106" spans="1:8" ht="91.5">
-      <c r="A106" s="1">
-        <v>8</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C106" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E106" s="4"/>
-      <c r="F106" s="1"/>
+    <row r="106" spans="1:8" ht="15">
+      <c r="A106" s="72">
+        <v>5</v>
+      </c>
+      <c r="B106" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="C106" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D106" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E106" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G106" s="20"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107" spans="1:8" ht="60.75">
-      <c r="A107" s="1">
-        <v>9</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C107" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E107" s="4"/>
-      <c r="F107" s="1"/>
+    <row r="107" spans="1:8" ht="15">
+      <c r="A107" s="72"/>
+      <c r="B107" s="74"/>
+      <c r="C107" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D107" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E107" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G107" s="20"/>
       <c r="H107" s="20"/>
     </row>
     <row r="108" spans="1:8" ht="15">
-      <c r="A108" s="1">
-        <v>10</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C108" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E108" s="4"/>
+      <c r="A108" s="72"/>
+      <c r="B108" s="74"/>
+      <c r="C108" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D108" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E108" s="55" t="s">
+        <v>116</v>
+      </c>
       <c r="F108" s="1"/>
-      <c r="G108" s="50"/>
-      <c r="H108" s="51"/>
-    </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1">
-      <c r="A109" s="52">
-        <v>11</v>
-      </c>
-      <c r="B109" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="C109" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="D109" s="70"/>
-      <c r="E109" s="71"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="14"/>
-      <c r="H109" s="15"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+    </row>
+    <row r="109" spans="1:8" ht="15">
+      <c r="A109" s="73"/>
+      <c r="B109" s="75"/>
+      <c r="C109" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="D109" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="E109" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="F109" s="1"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="20"/>
     </row>
     <row r="110" spans="1:8" ht="15">
-      <c r="A110" s="54" t="s">
+      <c r="A110" s="9">
+        <v>12</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C110" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D110" s="68"/>
+      <c r="E110" s="68"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="15"/>
+    </row>
+    <row r="111" spans="1:8" ht="15">
+      <c r="A111" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B110" s="55" t="s">
+      <c r="B111" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C110" s="55" t="s">
+      <c r="C111" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D110" s="55" t="s">
+      <c r="D111" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E110" s="55" t="s">
+      <c r="E111" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F110" s="12" t="s">
+      <c r="F111" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G110" s="12" t="s">
+      <c r="G111" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H110" s="11" t="s">
+      <c r="H111" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15">
-      <c r="A111" s="56">
+    <row r="112" spans="1:8" ht="15">
+      <c r="A112" s="1">
         <v>1</v>
       </c>
-      <c r="B111" s="57" t="s">
+      <c r="B112" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C111" s="57" t="s">
+      <c r="C112" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D111" s="57" t="s">
+      <c r="D112" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E111" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
-    </row>
-    <row r="112" spans="1:8" ht="15">
-      <c r="A112" s="73">
-        <v>2</v>
-      </c>
-      <c r="B112" s="75" t="s">
-        <v>127</v>
-      </c>
-      <c r="C112" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="D112" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E112" s="57" t="s">
-        <v>126</v>
-      </c>
+      <c r="E112" s="4"/>
       <c r="F112" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113" spans="1:8" ht="15">
-      <c r="A113" s="74"/>
-      <c r="B113" s="76"/>
+    <row r="113" spans="1:8" ht="121.5">
+      <c r="A113" s="1">
+        <v>2</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>23</v>
+      </c>
       <c r="C113" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="D113" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="E113" s="57" t="s">
-        <v>126</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E113" s="4"/>
       <c r="F113" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G113" s="20"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114" spans="1:8" ht="15">
-      <c r="A114" s="58">
+    <row r="114" spans="1:8" ht="106.5">
+      <c r="A114" s="1">
         <v>3</v>
       </c>
-      <c r="B114" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="C114" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="D114" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E114" s="57" t="s">
-        <v>126</v>
-      </c>
+      <c r="B114" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E114" s="4"/>
       <c r="F114" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G114" s="20"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115" spans="1:8" ht="30.75">
-      <c r="A115" s="58">
+    <row r="115" spans="1:8" ht="152.25">
+      <c r="A115" s="1">
         <v>4</v>
       </c>
-      <c r="B115" s="57" t="s">
+      <c r="B115" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C115" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="D115" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E115" s="57" t="s">
-        <v>126</v>
-      </c>
+      <c r="E115" s="4"/>
       <c r="F115" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116" spans="1:8" ht="15">
-      <c r="A116" s="73">
+    <row r="116" spans="1:8" ht="152.25">
+      <c r="A116" s="1">
         <v>5</v>
       </c>
-      <c r="B116" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="C116" s="57" t="s">
+      <c r="B116" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C116" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="D116" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E116" s="57" t="s">
-        <v>126</v>
-      </c>
+      <c r="D116" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E116" s="4"/>
       <c r="F116" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117" spans="1:8" ht="15">
-      <c r="A117" s="73"/>
-      <c r="B117" s="75"/>
-      <c r="C117" s="57" t="s">
+    <row r="117" spans="1:8" ht="152.25">
+      <c r="A117" s="1">
+        <v>6</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C117" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="D117" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E117" s="57" t="s">
-        <v>126</v>
-      </c>
+      <c r="D117" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E117" s="4"/>
       <c r="F117" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118" spans="1:8" ht="15">
-      <c r="A118" s="73"/>
-      <c r="B118" s="75"/>
-      <c r="C118" s="57" t="s">
+    <row r="118" spans="1:8" ht="152.25">
+      <c r="A118" s="1">
+        <v>7</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="D118" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E118" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="F118" s="1"/>
+      <c r="D118" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119" spans="1:8" ht="15">
-      <c r="A119" s="74"/>
-      <c r="B119" s="76"/>
-      <c r="C119" s="57" t="s">
+    <row r="119" spans="1:8" ht="137.25">
+      <c r="A119" s="1">
+        <v>8</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D119" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E119" s="57" t="s">
-        <v>126</v>
-      </c>
+      <c r="D119" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E119" s="4"/>
       <c r="F119" s="1"/>
       <c r="G119" s="20"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120" spans="1:8" ht="15">
-      <c r="A120" s="9">
-        <v>12</v>
-      </c>
-      <c r="B120" s="10" t="s">
+    <row r="120" spans="1:8" ht="30.75">
+      <c r="A120" s="1">
+        <v>9</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="C120" s="69" t="s">
+      <c r="D120" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="48"/>
+      <c r="H120" s="49"/>
+    </row>
+    <row r="121" spans="1:8" ht="15">
+      <c r="A121" s="9">
+        <v>13</v>
+      </c>
+      <c r="B121" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D120" s="69"/>
-      <c r="E120" s="69"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="14"/>
-      <c r="H120" s="15"/>
-    </row>
-    <row r="121" spans="1:8" ht="15">
-      <c r="A121" s="11" t="s">
+      <c r="C121" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D121" s="68"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="15"/>
+    </row>
+    <row r="122" spans="1:8" ht="15">
+      <c r="A122" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B122" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C122" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D122" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E122" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F121" s="12" t="s">
+      <c r="F122" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G121" s="12" t="s">
+      <c r="G122" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H121" s="11" t="s">
+      <c r="H122" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15">
-      <c r="A122" s="1">
+    <row r="123" spans="1:8" ht="15">
+      <c r="A123" s="1">
         <v>1</v>
       </c>
-      <c r="B122" s="19" t="s">
+      <c r="B123" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C122" s="19" t="s">
+      <c r="C123" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E122" s="4"/>
-      <c r="F122" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-    </row>
-    <row r="123" spans="1:8" ht="121.5">
-      <c r="A123" s="1">
-        <v>2</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C123" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="1" t="s">
@@ -4992,18 +4794,18 @@
       <c r="G123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124" spans="1:8" ht="106.5">
+    <row r="124" spans="1:8" ht="60.75">
       <c r="A124" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B124" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C124" s="19" t="s">
+      <c r="C124" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="1" t="s">
@@ -5012,18 +4814,18 @@
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125" spans="1:8" ht="152.25">
+    <row r="125" spans="1:8" ht="60.75">
       <c r="A125" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B125" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C125" s="31" t="s">
+      <c r="C125" s="19" t="s">
         <v>145</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="1" t="s">
@@ -5032,18 +4834,18 @@
       <c r="G125" s="20"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126" spans="1:8" ht="152.25">
+    <row r="126" spans="1:8" ht="30.75">
       <c r="A126" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B126" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C126" s="49" t="s">
+      <c r="C126" s="31" t="s">
         <v>146</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="1" t="s">
@@ -5052,18 +4854,18 @@
       <c r="G126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8" ht="152.25">
+    <row r="127" spans="1:8" ht="76.5">
       <c r="A127" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B127" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C127" s="60" t="s">
+      <c r="C127" s="47" t="s">
         <v>147</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="1" t="s">
@@ -5072,18 +4874,18 @@
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8" ht="152.25">
+    <row r="128" spans="1:8" ht="60.75">
       <c r="A128" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B128" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C128" s="31" t="s">
+      <c r="C128" s="58" t="s">
         <v>148</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="1" t="s">
@@ -5092,9 +4894,9 @@
       <c r="G128" s="20"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129" spans="1:8" ht="137.25">
+    <row r="129" spans="1:8" ht="76.5">
       <c r="A129" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B129" s="19" t="s">
         <v>23</v>
@@ -5103,16 +4905,18 @@
         <v>149</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E129" s="4"/>
-      <c r="F129" s="1"/>
+      <c r="F129" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G129" s="20"/>
       <c r="H129" s="20"/>
     </row>
-    <row r="130" spans="1:8" ht="30.75">
+    <row r="130" spans="1:8" ht="60.75">
       <c r="A130" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B130" s="19" t="s">
         <v>23</v>
@@ -5121,25 +4925,25 @@
         <v>150</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="1"/>
-      <c r="G130" s="50"/>
-      <c r="H130" s="51"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="20"/>
     </row>
     <row r="131" spans="1:8" ht="15">
       <c r="A131" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C131" s="69" t="s">
+      <c r="C131" s="68" t="s">
         <v>152</v>
       </c>
-      <c r="D131" s="69"/>
-      <c r="E131" s="69"/>
+      <c r="D131" s="68"/>
+      <c r="E131" s="68"/>
       <c r="F131" s="9"/>
       <c r="G131" s="14"/>
       <c r="H131" s="15"/>
@@ -5190,18 +4994,18 @@
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8" ht="60.75">
+    <row r="134" spans="1:8" ht="15">
       <c r="A134" s="1">
         <v>2</v>
       </c>
       <c r="B134" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="59" t="s">
+      <c r="C134" s="57" t="s">
         <v>153</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="1" t="s">
@@ -5210,7 +5014,7 @@
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135" spans="1:8" ht="60.75">
+    <row r="135" spans="1:8" ht="30.75">
       <c r="A135" s="1">
         <v>3</v>
       </c>
@@ -5218,10 +5022,10 @@
         <v>23</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="1" t="s">
@@ -5235,13 +5039,13 @@
         <v>4</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C136" s="31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="1" t="s">
@@ -5250,58 +5054,60 @@
       <c r="G136" s="20"/>
       <c r="H136" s="20"/>
     </row>
-    <row r="137" spans="1:8" ht="76.5">
-      <c r="A137" s="1">
-        <v>5</v>
-      </c>
-      <c r="B137" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C137" s="49" t="s">
+    <row r="137" spans="1:8" ht="15">
+      <c r="A137" s="9">
+        <v>15</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C137" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E137" s="4"/>
-      <c r="F137" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G137" s="20"/>
-      <c r="H137" s="20"/>
-    </row>
-    <row r="138" spans="1:8" ht="60.75">
-      <c r="A138" s="1">
+      <c r="D137" s="68"/>
+      <c r="E137" s="68"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="15"/>
+    </row>
+    <row r="138" spans="1:8" ht="15">
+      <c r="A138" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B138" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C138" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E138" s="4"/>
-      <c r="F138" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G138" s="20"/>
-      <c r="H138" s="20"/>
-    </row>
-    <row r="139" spans="1:8" ht="76.5">
+      <c r="F138" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G138" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="15">
       <c r="A139" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C139" s="31" t="s">
-        <v>159</v>
+        <v>18</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="1" t="s">
@@ -5312,76 +5118,76 @@
     </row>
     <row r="140" spans="1:8" ht="60.75">
       <c r="A140" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B140" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C140" s="31" t="s">
-        <v>160</v>
+      <c r="C140" s="57" t="s">
+        <v>158</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="E140" s="4"/>
-      <c r="F140" s="1"/>
+      <c r="F140" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
     </row>
     <row r="141" spans="1:8" ht="15">
-      <c r="A141" s="9">
-        <v>14</v>
-      </c>
-      <c r="B141" s="10" t="s">
+      <c r="A141" s="1">
+        <v>3</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E141" s="4"/>
+      <c r="F141" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20"/>
+    </row>
+    <row r="142" spans="1:8" ht="15">
+      <c r="A142" s="1">
+        <v>4</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C142" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="C141" s="69" t="s">
+      <c r="D142" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142" s="20"/>
+      <c r="H142" s="20"/>
+    </row>
+    <row r="143" spans="1:8" ht="60.75">
+      <c r="A143" s="1">
+        <v>5</v>
+      </c>
+      <c r="B143" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D141" s="69"/>
-      <c r="E141" s="69"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="14"/>
-      <c r="H141" s="15"/>
-    </row>
-    <row r="142" spans="1:8" ht="15">
-      <c r="A142" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D142" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E142" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F142" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G142" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H142" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="15">
-      <c r="A143" s="1">
-        <v>1</v>
-      </c>
-      <c r="B143" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>48</v>
+      <c r="C143" s="31" t="s">
+        <v>163</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="1" t="s">
@@ -5391,57 +5197,59 @@
       <c r="H143" s="20"/>
     </row>
     <row r="144" spans="1:8" ht="15">
-      <c r="A144" s="1">
-        <v>2</v>
-      </c>
-      <c r="B144" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C144" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E144" s="4"/>
-      <c r="F144" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
-    </row>
-    <row r="145" spans="1:8" ht="30.75">
-      <c r="A145" s="1">
-        <v>3</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C145" s="19" t="s">
+      <c r="A144" s="9">
+        <v>16</v>
+      </c>
+      <c r="B144" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D145" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E145" s="4"/>
-      <c r="F145" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
-    </row>
-    <row r="146" spans="1:8" ht="30.75">
+      <c r="C144" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="D144" s="60"/>
+      <c r="E144" s="60"/>
+      <c r="F144" s="9"/>
+      <c r="G144" s="14"/>
+      <c r="H144" s="15"/>
+    </row>
+    <row r="145" spans="1:8" ht="15">
+      <c r="A145" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G145" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="15">
       <c r="A146" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B146" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C146" s="31" t="s">
-        <v>165</v>
+      <c r="C146" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="1" t="s">
@@ -5450,60 +5258,58 @@
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147" spans="1:8" ht="15">
-      <c r="A147" s="9">
-        <v>15</v>
-      </c>
-      <c r="B147" s="10" t="s">
+    <row r="147" spans="1:8" ht="76.5">
+      <c r="A147" s="1">
+        <v>2</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="C147" s="69" t="s">
+      <c r="D147" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E147" s="4"/>
+      <c r="F147" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147" s="20"/>
+      <c r="H147" s="20"/>
+    </row>
+    <row r="148" spans="1:8" ht="106.5">
+      <c r="A148" s="1">
+        <v>3</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C148" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D147" s="69"/>
-      <c r="E147" s="69"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="14"/>
-      <c r="H147" s="15"/>
-    </row>
-    <row r="148" spans="1:8" ht="15">
-      <c r="A148" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B148" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C148" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D148" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E148" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F148" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G148" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H148" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="15">
+      <c r="D148" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E148" s="4"/>
+      <c r="F148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
+    </row>
+    <row r="149" spans="1:8" ht="76.5">
       <c r="A149" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C149" s="31" t="s">
+        <v>168</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="1" t="s">
@@ -5514,16 +5320,16 @@
     </row>
     <row r="150" spans="1:8" ht="60.75">
       <c r="A150" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B150" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C150" s="59" t="s">
-        <v>168</v>
+      <c r="C150" s="31" t="s">
+        <v>169</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="1" t="s">
@@ -5532,18 +5338,18 @@
       <c r="G150" s="20"/>
       <c r="H150" s="20"/>
     </row>
-    <row r="151" spans="1:8" ht="15">
+    <row r="151" spans="1:8" ht="76.5">
       <c r="A151" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C151" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C151" s="31" t="s">
         <v>170</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="1" t="s">
@@ -5553,341 +5359,145 @@
       <c r="H151" s="20"/>
     </row>
     <row r="152" spans="1:8" ht="15">
-      <c r="A152" s="1">
-        <v>4</v>
-      </c>
-      <c r="B152" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C152" s="31" t="s">
+      <c r="A152" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E152" s="4"/>
-      <c r="F152" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G152" s="20"/>
-      <c r="H152" s="20"/>
-    </row>
-    <row r="153" spans="1:8" ht="60.75">
-      <c r="A153" s="1">
-        <v>5</v>
-      </c>
-      <c r="B153" s="19" t="s">
+      <c r="B152" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C153" s="31" t="s">
+      <c r="C152" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E153" s="4"/>
-      <c r="F153" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G153" s="20"/>
-      <c r="H153" s="20"/>
-    </row>
-    <row r="154" spans="1:8" ht="15">
-      <c r="A154" s="9">
+      <c r="D152" s="60"/>
+      <c r="E152" s="60"/>
+      <c r="F152" s="9"/>
+      <c r="G152" s="14"/>
+      <c r="H152" s="15"/>
+    </row>
+    <row r="153" spans="1:8" ht="15">
+      <c r="A153" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="D153" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G153" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="76.5">
+      <c r="A154" s="1">
+        <v>1</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C154" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="C154" s="61" t="s">
+      <c r="D154" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D154" s="61"/>
-      <c r="E154" s="61"/>
-      <c r="F154" s="9"/>
-      <c r="G154" s="14"/>
-      <c r="H154" s="15"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G154" s="20"/>
+      <c r="H154" s="20"/>
     </row>
     <row r="155" spans="1:8" ht="15">
-      <c r="A155" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B155" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C155" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D155" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E155" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F155" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G155" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H155" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="15">
-      <c r="A156" s="1">
-        <v>1</v>
-      </c>
-      <c r="B156" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C156" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E156" s="4"/>
-      <c r="F156" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G156" s="20"/>
-      <c r="H156" s="20"/>
-    </row>
-    <row r="157" spans="1:8" ht="76.5">
-      <c r="A157" s="1">
+      <c r="A155" s="1">
         <v>2</v>
       </c>
-      <c r="B157" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C157" s="59" t="s">
+      <c r="B155" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C155" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E157" s="4"/>
-      <c r="F157" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G157" s="20"/>
-      <c r="H157" s="20"/>
-    </row>
-    <row r="158" spans="1:8" ht="106.5">
-      <c r="A158" s="1">
-        <v>3</v>
-      </c>
-      <c r="B158" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C158" s="19" t="s">
+      <c r="D155" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E158" s="4"/>
-      <c r="F158" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G158" s="20"/>
-      <c r="H158" s="20"/>
-    </row>
-    <row r="159" spans="1:8" ht="76.5">
-      <c r="A159" s="1">
-        <v>4</v>
-      </c>
-      <c r="B159" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C159" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E159" s="4"/>
-      <c r="F159" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G159" s="20"/>
-      <c r="H159" s="20"/>
-    </row>
-    <row r="160" spans="1:8" ht="60.75">
-      <c r="A160" s="1">
-        <v>5</v>
-      </c>
-      <c r="B160" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C160" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E160" s="4"/>
-      <c r="F160" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G160" s="20"/>
-      <c r="H160" s="20"/>
-    </row>
-    <row r="161" spans="1:8" ht="76.5">
-      <c r="A161" s="1">
-        <v>6</v>
-      </c>
-      <c r="B161" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C161" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E161" s="4"/>
-      <c r="F161" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G161" s="20"/>
-      <c r="H161" s="20"/>
-    </row>
-    <row r="162" spans="1:8" ht="15">
-      <c r="A162" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B162" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C162" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="D162" s="61"/>
-      <c r="E162" s="61"/>
-      <c r="F162" s="9"/>
-      <c r="G162" s="14"/>
-      <c r="H162" s="15"/>
-    </row>
-    <row r="163" spans="1:8" ht="15">
-      <c r="A163" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C163" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E163" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F163" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G163" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H163" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="76.5">
-      <c r="A164" s="1">
-        <v>1</v>
-      </c>
-      <c r="B164" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C164" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E164" s="4"/>
-      <c r="F164" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G164" s="20"/>
-      <c r="H164" s="20"/>
-    </row>
-    <row r="165" spans="1:8" ht="15">
-      <c r="A165" s="1">
-        <v>2</v>
-      </c>
-      <c r="B165" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C165" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E165" s="4"/>
-      <c r="F165" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G165" s="20"/>
-      <c r="H165" s="20"/>
-    </row>
-    <row r="166" spans="1:8" ht="15"/>
-    <row r="167" spans="1:8" ht="15"/>
-    <row r="168" spans="1:8" ht="15"/>
-    <row r="169" spans="1:8" ht="15"/>
-    <row r="170" spans="1:8" ht="15"/>
-    <row r="171" spans="1:8" ht="15"/>
-    <row r="172" spans="1:8" ht="15"/>
-    <row r="173" spans="1:8" ht="15"/>
-    <row r="174" spans="1:8" ht="15"/>
-    <row r="175" spans="1:8" ht="15"/>
-    <row r="176" spans="1:8" ht="15"/>
-    <row r="177" ht="15"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" s="20"/>
+      <c r="H155" s="20"/>
+    </row>
+    <row r="156" spans="1:8" ht="15"/>
+    <row r="157" spans="1:8" ht="15"/>
+    <row r="158" spans="1:8" ht="15"/>
+    <row r="159" spans="1:8" ht="15"/>
+    <row r="160" spans="1:8" ht="15"/>
+    <row r="161" ht="15"/>
+    <row r="162" ht="15"/>
+    <row r="163" ht="15"/>
+    <row r="164" ht="15"/>
+    <row r="165" ht="15"/>
+    <row r="166" ht="15"/>
+    <row r="167" ht="15"/>
+    <row r="168" ht="15"/>
+    <row r="169" ht="15"/>
+    <row r="170" ht="15"/>
+    <row r="171" ht="15"/>
+    <row r="172" ht="15"/>
+    <row r="173" ht="15"/>
+    <row r="174" ht="15"/>
+    <row r="175" ht="15"/>
+    <row r="176" ht="15"/>
     <row r="178" ht="15"/>
-    <row r="179" ht="15"/>
     <row r="180" ht="15"/>
-    <row r="181" ht="15"/>
     <row r="182" ht="15"/>
-    <row r="183" ht="15"/>
   </sheetData>
   <autoFilter ref="A3:H32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="28">
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A116:A119"/>
-    <mergeCell ref="B116:B119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C52:E52"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="F93:F94"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C121:E121"/>
     <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C137:E137"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F97:F1048576 F3:F85">
+  <conditionalFormatting sqref="F1 F87:F1048576 F3:F75">
     <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5898,7 +5508,7 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F86:F91 F93 F95">
+  <conditionalFormatting sqref="F76:F81 F83 F85">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5910,13 +5520,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F51:F61 F17:F26 F33:F44 F47:F48 F64:F74 F77:F85 F6:F14 F29:F30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41:F51 F17:F26 F37:F38 F54:F64 F67:F75 F6:F14 F29:F30 F33:F34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G34" r:id="rId1" xr:uid="{70A08BB7-D84B-4BDB-8CBE-3536286FFE9C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -5930,39 +5543,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="77" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
+      <c r="A1" s="76" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5970,7 +5583,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -5983,12 +5596,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D22D72570E156D4F9C34B893E183F0BF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ec9c283aea1b7e9b2a2bfe7317a7796f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -6102,23 +5724,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29406"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98D4F94-559A-4DBC-A82D-31F5D864BF95}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09040B4-E99D-4725-908B-A8F73CCC5ED2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="178">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -215,7 +215,7 @@
     <t>Sustainable_farm</t>
   </si>
   <si>
-    <t xml:space="preserve">10.02.2025
+    <t xml:space="preserve">02.10.2025
 </t>
   </si>
   <si>
@@ -235,51 +235,19 @@
 Check excel sheet for feedbacks</t>
   </si>
   <si>
-    <t>03.01.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm,Abdelgafar ismail,  Diallo Fadilatou, Excellence program Students</t>
-  </si>
-  <si>
-    <t>Adams: great idea to use the ball mill in the sustainable farm à did you consider the process previous to you to communicate e.g. understand</t>
-  </si>
-  <si>
-    <t>Adjara: great idea to use the music app in the marketing of sustainable farm products à could think of using the music during the rest of the farming phases e.g. chants during harvesting e.g. playlist for harvesting, ..etc. – watch this video of ancient tradition in Sudan</t>
-  </si>
-  <si>
-    <t>Alicia: great idea to use the cowpea thresher in the sustainable farm à do you think the thresher could be customized for other products from the farm other than cowpea</t>
-  </si>
-  <si>
-    <t>Charles: great idea to use the automatic irrigation in the sustainable farm à did you think of including water counting techniques to calculate how much water is consumed/saved by each irrigating style, could also help raising awareness of farming about fresh water saving techniques ..etc.</t>
-  </si>
-  <si>
-    <t>Lucas: great idea to use the smart dryer in the sustainable farm à Could you consider communication with the following process e.g. packaging of dried products e.g. dried Mango</t>
-  </si>
-  <si>
-    <t>Boris: great idea to use the facial recognition system in the sustainable farm à would it be possible to tailor/customize the recognition of plants species e.g. herbs and unwanted plants</t>
-  </si>
-  <si>
-    <t>Gertrude: great idea to use the solar power plant in the sustainable farm à the sun doesn’t shine all the time, did you think of including storage/battery</t>
-  </si>
-  <si>
-    <t>Wilfried: great idea to use the solar tracking system in the sustainable farm à did you consider communicating with Gertrude to improve the solar power plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamado:  great idea to use the translation to local languages in the sustainable farm à could you consider other applications e.g. raising awareness of farmers and visitors about the different plants in the sustainable farms
-</t>
-  </si>
-  <si>
-    <t>General: 
-I really like the idea of a sustainable farm via ontology collaboration
-Let us think about the Goal of the farm in economic and ecological and societal Goal
-Let us think about the stages and time frames of the farm
-Let us think about demonstrators for the farm – your individual project
-Let us think how your individual project and demonstrator supports the overall goal
-Let us think how Infineon semiconductors can serve the farm
-Think about virtual big, think about demonstrators small – doable within 4-8 weeks, plan medium what can be done in one year, two years, five years</t>
-  </si>
-  <si>
-    <t>Hans</t>
+    <t xml:space="preserve"> Abdelgafar ismail,  Diallo Fadilatou, Excellence program Students</t>
+  </si>
+  <si>
+    <t>Fill PPT template with information bachelor thesis topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add name of each students the cheat they are working on.  Change name of the Ball mill grinder to Processing Machines on the Excel spreadsheet. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin feedback during JF: Plants and irrigation =&gt; Abdo                                           Processing Machines and Smart dryer =&gt; Hans                                                Solar PV and Solar Tracking =&gt; Fadila                                                              No Reesa and Facial Recognition =&gt; Botho/Vanessa              </t>
   </si>
   <si>
     <t>10.01.2025</t>
@@ -292,7 +260,13 @@
 Always good if you check the homepage upfront</t>
   </si>
   <si>
+    <t>Hans</t>
+  </si>
+  <si>
     <t>Adjara: Maybe we can all look at your ontology</t>
+  </si>
+  <si>
+    <t>Alicia: great idea to use the cowpea thresher in the sustainable farm à do you think the thresher could be customized for other products from the farm other than cowpea</t>
   </si>
   <si>
     <t>Charles: thanks for integrating the irrigation into the sustainable farm would be good if you can give some figures in an .xls. use class names for the column headlines</t>
@@ -585,9 +559,6 @@
   </si>
   <si>
     <t>Review PPT file about the sustainable farm and Feedack:                                        -Add Hyperlink                                                                                                      -Add Litterarure review                                                                                       -Add Picture related to BF</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Info</t>
   </si>
   <si>
     <t>More Informaton about possible Internship</t>
@@ -1425,6 +1396,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1449,28 +1438,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2353,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="5" customWidth="1"/>
@@ -2365,16 +2336,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -2893,11 +2864,11 @@
       <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
@@ -2975,11 +2946,11 @@
       <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
@@ -3059,11 +3030,11 @@
       <c r="B35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
       <c r="F35" s="9"/>
       <c r="G35" s="14"/>
       <c r="H35" s="15"/>
@@ -3134,18 +3105,18 @@
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" ht="15">
       <c r="A39" s="9">
         <v>6</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="10">
+        <v>45943</v>
+      </c>
+      <c r="C39" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
       <c r="F39" s="9"/>
       <c r="G39" s="14"/>
       <c r="H39" s="15"/>
@@ -3196,15 +3167,15 @@
       <c r="G41" s="20"/>
       <c r="H41" s="20"/>
     </row>
-    <row r="42" spans="1:8" ht="29.1">
+    <row r="42" spans="1:8" ht="15">
       <c r="A42" s="1">
         <v>2</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>50</v>
@@ -3216,15 +3187,15 @@
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
     </row>
-    <row r="43" spans="1:8" ht="57.95">
+    <row r="43" spans="1:8" ht="45.75">
       <c r="A43" s="1">
         <v>3</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>50</v>
@@ -3236,12 +3207,12 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
     </row>
-    <row r="44" spans="1:8" ht="43.5">
+    <row r="44" spans="1:8" ht="60.75">
       <c r="A44" s="1">
         <v>4</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C44" s="29" t="s">
         <v>63</v>
@@ -3256,58 +3227,60 @@
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
     </row>
-    <row r="45" spans="1:8" ht="72.599999999999994">
-      <c r="A45" s="1">
-        <v>5</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="31" t="s">
+    <row r="45" spans="1:8">
+      <c r="A45" s="9">
+        <v>7</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" ht="43.5">
-      <c r="A46" s="1">
+      <c r="C45" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="15"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-    </row>
-    <row r="47" spans="1:8" ht="43.5">
+      <c r="F46" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="31" t="s">
-        <v>66</v>
+        <v>18</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="1" t="s">
@@ -3316,18 +3289,18 @@
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
     </row>
-    <row r="48" spans="1:8" ht="43.5">
+    <row r="48" spans="1:8" ht="72.599999999999994">
       <c r="A48" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="31" t="s">
+      <c r="C48" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="1" t="s">
@@ -3336,45 +3309,49 @@
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
     </row>
-    <row r="49" spans="1:8" ht="43.5">
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="29" t="s">
         <v>68</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G49" s="20"/>
       <c r="H49" s="20"/>
     </row>
-    <row r="50" spans="1:8" ht="72.599999999999994">
+    <row r="50" spans="1:8" ht="43.5">
       <c r="A50" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="29" t="s">
         <v>69</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="F50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
     </row>
-    <row r="51" spans="1:8" ht="188.45">
+    <row r="51" spans="1:8" ht="43.5">
       <c r="A51" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>23</v>
@@ -3383,69 +3360,67 @@
         <v>70</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="9">
+    <row r="52" spans="1:8" ht="43.5">
+      <c r="A52" s="1">
+        <v>6</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+    </row>
+    <row r="53" spans="1:8" ht="43.5">
+      <c r="A53" s="1">
         <v>7</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B53" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="C52" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="15"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="D53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>73</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="1" t="s">
@@ -3454,118 +3429,116 @@
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
     </row>
-    <row r="55" spans="1:8" ht="72.599999999999994">
+    <row r="55" spans="1:8" ht="29.1">
       <c r="A55" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="31" t="s">
         <v>74</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E55" s="4"/>
-      <c r="F55" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="20"/>
       <c r="H55" s="20"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" ht="29.1">
       <c r="A56" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="31" t="s">
         <v>75</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E56" s="4"/>
-      <c r="F56" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F56" s="1"/>
       <c r="G56" s="20"/>
       <c r="H56" s="20"/>
     </row>
-    <row r="57" spans="1:8" ht="43.5">
+    <row r="57" spans="1:8" ht="72.599999999999994">
       <c r="A57" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="29" t="s">
-        <v>63</v>
+      <c r="C57" s="31" t="s">
+        <v>76</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="20"/>
     </row>
-    <row r="58" spans="1:8" ht="43.5">
-      <c r="A58" s="1">
-        <v>5</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-    </row>
-    <row r="59" spans="1:8" ht="43.5">
-      <c r="A59" s="1">
+    <row r="58" spans="1:8">
+      <c r="A58" s="9">
+        <v>8</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="15"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-    </row>
-    <row r="60" spans="1:8" ht="43.5">
+      <c r="F59" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="31" t="s">
-        <v>78</v>
+        <v>18</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="1" t="s">
@@ -3574,18 +3547,18 @@
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" ht="72.599999999999994">
       <c r="A61" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="31" t="s">
+      <c r="C61" s="30" t="s">
         <v>79</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="1" t="s">
@@ -3594,27 +3567,29 @@
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8" ht="29.1">
+    <row r="62" spans="1:8" ht="57.95">
       <c r="A62" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="31" t="s">
+      <c r="C62" s="29" t="s">
         <v>80</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E62" s="4"/>
-      <c r="F62" s="1"/>
+      <c r="F62" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63" spans="1:8" ht="29.1">
+    <row r="63" spans="1:8" ht="76.5">
       <c r="A63" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>23</v>
@@ -3623,1031 +3598,1029 @@
         <v>81</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E63" s="4"/>
-      <c r="F63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
     </row>
     <row r="64" spans="1:8" ht="72.599999999999994">
       <c r="A64" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="32" t="s">
         <v>82</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="9">
+    <row r="65" spans="1:8" ht="87">
+      <c r="A65" s="1">
+        <v>6</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+    </row>
+    <row r="66" spans="1:8" ht="87">
+      <c r="A66" s="1">
+        <v>7</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+    </row>
+    <row r="67" spans="1:8" ht="57.95">
+      <c r="A67" s="1">
         <v>8</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="68" t="s">
-        <v>84</v>
-      </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="15"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="1">
-        <v>1</v>
-      </c>
       <c r="B67" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C67" s="31" t="s">
+        <v>85</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E67" s="4"/>
-      <c r="F67" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F67" s="1"/>
       <c r="G67" s="20"/>
       <c r="H67" s="20"/>
     </row>
-    <row r="68" spans="1:8" ht="72.599999999999994">
+    <row r="68" spans="1:8" ht="106.5">
       <c r="A68" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C68" s="30" t="s">
-        <v>85</v>
+      <c r="C68" s="31" t="s">
+        <v>86</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E68" s="4"/>
-      <c r="F68" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F68" s="1"/>
       <c r="G68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69" spans="1:8" ht="57.95">
-      <c r="A69" s="1">
-        <v>3</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-    </row>
-    <row r="70" spans="1:8" ht="76.5">
-      <c r="A70" s="1">
-        <v>4</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" s="31" t="s">
+    <row r="69" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A69" s="33">
+        <v>9</v>
+      </c>
+      <c r="B69" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-    </row>
-    <row r="71" spans="1:8" ht="72.599999999999994">
-      <c r="A71" s="1">
-        <v>5</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="32" t="s">
+      <c r="C69" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="4"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="69"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="15"/>
+    </row>
+    <row r="70" spans="1:8" s="35" customFormat="1" ht="15.75">
+      <c r="A70" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="16.5">
+      <c r="A71" s="38">
+        <v>1</v>
+      </c>
+      <c r="B71" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="40"/>
       <c r="F71" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
     </row>
-    <row r="72" spans="1:8" ht="87">
-      <c r="A72" s="1">
-        <v>6</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="31" t="s">
+    <row r="72" spans="1:8" ht="46.5">
+      <c r="A72" s="41">
+        <v>2</v>
+      </c>
+      <c r="B72" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E72" s="4"/>
+      <c r="E72" s="43"/>
       <c r="F72" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
     </row>
-    <row r="73" spans="1:8" ht="87">
-      <c r="A73" s="1">
-        <v>7</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="31" t="s">
+    <row r="73" spans="1:8" ht="46.5">
+      <c r="A73" s="44"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="4"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
       <c r="F73" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
     </row>
-    <row r="74" spans="1:8" ht="57.95">
-      <c r="A74" s="1">
+    <row r="74" spans="1:8" ht="46.5">
+      <c r="A74" s="41">
+        <v>3</v>
+      </c>
+      <c r="B74" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="43"/>
+      <c r="F74" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="20"/>
+      <c r="H74" s="72"/>
+    </row>
+    <row r="75" spans="1:8" ht="46.5">
+      <c r="A75" s="44"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="73"/>
+    </row>
+    <row r="76" spans="1:8" ht="30.75">
+      <c r="A76" s="41">
+        <v>4</v>
+      </c>
+      <c r="B76" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="43"/>
+      <c r="F76" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="72"/>
+      <c r="H76" s="72"/>
+    </row>
+    <row r="77" spans="1:8" ht="61.5">
+      <c r="A77" s="44"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D77" s="45"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="71"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="73"/>
+    </row>
+    <row r="78" spans="1:8" ht="30.75">
+      <c r="A78" s="41">
+        <v>5</v>
+      </c>
+      <c r="B78" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="43"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="72"/>
+      <c r="H78" s="72"/>
+    </row>
+    <row r="79" spans="1:8" ht="30.75">
+      <c r="A79" s="44"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="71"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="73"/>
+    </row>
+    <row r="80" spans="1:8" ht="15">
+      <c r="A80" s="9">
+        <v>10</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C80" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="15"/>
+    </row>
+    <row r="81" spans="1:8" ht="15">
+      <c r="A81" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G81" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B74" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="4"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-    </row>
-    <row r="75" spans="1:8" ht="106.5">
-      <c r="A75" s="1">
+      <c r="H81" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B75" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="4"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-    </row>
-    <row r="76" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A76" s="33">
-        <v>9</v>
-      </c>
-      <c r="B76" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="D76" s="62"/>
-      <c r="E76" s="63"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="15"/>
-    </row>
-    <row r="77" spans="1:8" s="35" customFormat="1" ht="15.75">
-      <c r="A77" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E77" s="37" t="s">
+    </row>
+    <row r="82" spans="1:8" ht="15">
+      <c r="A82" s="1">
+        <v>1</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+    </row>
+    <row r="83" spans="1:8" ht="60.75">
+      <c r="A83" s="1">
+        <v>2</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+    </row>
+    <row r="84" spans="1:8" ht="30.75">
+      <c r="A84" s="1">
+        <v>3</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+    </row>
+    <row r="85" spans="1:8" ht="76.5">
+      <c r="A85" s="1">
+        <v>4</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+    </row>
+    <row r="86" spans="1:8" ht="76.5">
+      <c r="A86" s="1">
+        <v>5</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+    </row>
+    <row r="87" spans="1:8" ht="45.75">
+      <c r="A87" s="1">
         <v>6</v>
       </c>
-      <c r="F77" s="12" t="s">
+      <c r="B87" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+    </row>
+    <row r="88" spans="1:8" ht="76.5">
+      <c r="A88" s="1">
         <v>7</v>
       </c>
-      <c r="G77" s="12" t="s">
+      <c r="B88" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+    </row>
+    <row r="89" spans="1:8" ht="91.5">
+      <c r="A89" s="1">
         <v>8</v>
       </c>
-      <c r="H77" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="16.5">
-      <c r="A78" s="38">
-        <v>1</v>
-      </c>
-      <c r="B78" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D78" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="40"/>
-      <c r="F78" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-    </row>
-    <row r="79" spans="1:8" ht="46.5">
-      <c r="A79" s="41">
-        <v>2</v>
-      </c>
-      <c r="B79" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D79" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-    </row>
-    <row r="80" spans="1:8" ht="46.5">
-      <c r="A80" s="44"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D80" s="45"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-    </row>
-    <row r="81" spans="1:8" ht="46.5">
-      <c r="A81" s="41">
-        <v>3</v>
-      </c>
-      <c r="B81" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="D81" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E81" s="43"/>
-      <c r="F81" s="64" t="s">
-        <v>22</v>
-      </c>
-      <c r="G81" s="20"/>
-      <c r="H81" s="66"/>
-    </row>
-    <row r="82" spans="1:8" ht="46.5">
-      <c r="A82" s="44"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="D82" s="45"/>
-      <c r="E82" s="45"/>
-      <c r="F82" s="65"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="67"/>
-    </row>
-    <row r="83" spans="1:8" ht="30.75">
-      <c r="A83" s="41">
-        <v>4</v>
-      </c>
-      <c r="B83" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C83" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D83" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E83" s="43"/>
-      <c r="F83" s="64" t="s">
-        <v>22</v>
-      </c>
-      <c r="G83" s="66"/>
-      <c r="H83" s="66"/>
-    </row>
-    <row r="84" spans="1:8" ht="61.5">
-      <c r="A84" s="44"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D84" s="45"/>
-      <c r="E84" s="45"/>
-      <c r="F84" s="65"/>
-      <c r="G84" s="67"/>
-      <c r="H84" s="67"/>
-    </row>
-    <row r="85" spans="1:8" ht="30.75">
-      <c r="A85" s="41">
-        <v>5</v>
-      </c>
-      <c r="B85" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C85" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D85" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E85" s="43"/>
-      <c r="F85" s="64"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="66"/>
-    </row>
-    <row r="86" spans="1:8" ht="30.75">
-      <c r="A86" s="44"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D86" s="45"/>
-      <c r="E86" s="45"/>
-      <c r="F86" s="65"/>
-      <c r="G86" s="67"/>
-      <c r="H86" s="67"/>
-    </row>
-    <row r="87" spans="1:8" ht="15">
-      <c r="A87" s="9">
-        <v>10</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C87" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="15"/>
-    </row>
-    <row r="88" spans="1:8" ht="15">
-      <c r="A88" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G88" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H88" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="15">
-      <c r="A89" s="1">
-        <v>1</v>
-      </c>
       <c r="B89" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C89" s="31" t="s">
+        <v>105</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E89" s="4"/>
-      <c r="F89" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F89" s="1"/>
       <c r="G89" s="20"/>
       <c r="H89" s="20"/>
     </row>
     <row r="90" spans="1:8" ht="60.75">
       <c r="A90" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B90" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C90" s="5" t="s">
-        <v>105</v>
+      <c r="C90" s="31" t="s">
+        <v>106</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E90" s="4"/>
-      <c r="F90" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F90" s="1"/>
       <c r="G90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91" spans="1:8" ht="30.75">
+    <row r="91" spans="1:8" ht="15">
       <c r="A91" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B91" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C91" s="19" t="s">
-        <v>106</v>
+      <c r="C91" s="31" t="s">
+        <v>107</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E91" s="4"/>
-      <c r="F91" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" s="20"/>
-      <c r="H91" s="20"/>
-    </row>
-    <row r="92" spans="1:8" ht="76.5">
-      <c r="A92" s="1">
-        <v>4</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E92" s="4"/>
-      <c r="F92" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-    </row>
-    <row r="93" spans="1:8" ht="76.5">
-      <c r="A93" s="1">
-        <v>5</v>
-      </c>
-      <c r="B93" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="47" t="s">
+      <c r="F91" s="1"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="49"/>
+    </row>
+    <row r="92" spans="1:8" ht="15" customHeight="1">
+      <c r="A92" s="50">
+        <v>11</v>
+      </c>
+      <c r="B92" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E93" s="4"/>
-      <c r="F93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-    </row>
-    <row r="94" spans="1:8" ht="45.75">
-      <c r="A94" s="1">
+      <c r="C92" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="D92" s="74"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="15"/>
+    </row>
+    <row r="93" spans="1:8" ht="15">
+      <c r="A93" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B94" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E94" s="4"/>
+      <c r="F93" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15">
+      <c r="A94" s="54">
+        <v>1</v>
+      </c>
+      <c r="B94" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D94" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="55" t="s">
+        <v>110</v>
+      </c>
       <c r="F94" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G94" s="20"/>
       <c r="H94" s="20"/>
     </row>
-    <row r="95" spans="1:8" ht="76.5">
-      <c r="A95" s="1">
-        <v>7</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" s="31" t="s">
+    <row r="95" spans="1:8" ht="15">
+      <c r="A95" s="60">
+        <v>2</v>
+      </c>
+      <c r="B95" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="C95" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E95" s="4"/>
       <c r="F95" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G95" s="20"/>
       <c r="H95" s="20"/>
     </row>
-    <row r="96" spans="1:8" ht="91.5">
-      <c r="A96" s="1">
-        <v>8</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E96" s="4"/>
-      <c r="F96" s="1"/>
+    <row r="96" spans="1:8" ht="15">
+      <c r="A96" s="61"/>
+      <c r="B96" s="63"/>
+      <c r="C96" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G96" s="20"/>
       <c r="H96" s="20"/>
     </row>
-    <row r="97" spans="1:8" ht="60.75">
-      <c r="A97" s="1">
-        <v>9</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C97" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E97" s="4"/>
-      <c r="F97" s="1"/>
+    <row r="97" spans="1:8" ht="15">
+      <c r="A97" s="56">
+        <v>3</v>
+      </c>
+      <c r="B97" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D97" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G97" s="20"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98" spans="1:8" ht="15">
-      <c r="A98" s="1">
-        <v>10</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" s="31" t="s">
+    <row r="98" spans="1:8" ht="30.75">
+      <c r="A98" s="56">
+        <v>4</v>
+      </c>
+      <c r="B98" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D98" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E98" s="4"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="49"/>
-    </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1">
-      <c r="A99" s="50">
-        <v>11</v>
-      </c>
-      <c r="B99" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="C99" s="69" t="s">
-        <v>115</v>
-      </c>
-      <c r="D99" s="69"/>
-      <c r="E99" s="70"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="14"/>
-      <c r="H99" s="15"/>
+      <c r="E98" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="20"/>
+      <c r="H98" s="20"/>
+    </row>
+    <row r="99" spans="1:8" ht="15">
+      <c r="A99" s="60">
+        <v>5</v>
+      </c>
+      <c r="B99" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="20"/>
+      <c r="H99" s="20"/>
     </row>
     <row r="100" spans="1:8" ht="15">
-      <c r="A100" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B100" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="C100" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D100" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="E100" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G100" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="A100" s="60"/>
+      <c r="B100" s="62"/>
+      <c r="C100" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D100" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="20"/>
+      <c r="H100" s="20"/>
     </row>
     <row r="101" spans="1:8" ht="15">
-      <c r="A101" s="54">
-        <v>1</v>
-      </c>
-      <c r="B101" s="55" t="s">
-        <v>18</v>
-      </c>
+      <c r="A101" s="60"/>
+      <c r="B101" s="62"/>
       <c r="C101" s="55" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="E101" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F101" s="1"/>
       <c r="G101" s="20"/>
       <c r="H101" s="20"/>
     </row>
     <row r="102" spans="1:8" ht="15">
-      <c r="A102" s="72">
-        <v>2</v>
-      </c>
-      <c r="B102" s="74" t="s">
-        <v>117</v>
-      </c>
+      <c r="A102" s="61"/>
+      <c r="B102" s="63"/>
       <c r="C102" s="55" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E102" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F102" s="1"/>
       <c r="G102" s="20"/>
       <c r="H102" s="20"/>
     </row>
     <row r="103" spans="1:8" ht="15">
-      <c r="A103" s="73"/>
-      <c r="B103" s="75"/>
-      <c r="C103" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="D103" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E103" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
+      <c r="A103" s="9">
+        <v>12</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C103" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="D103" s="64"/>
+      <c r="E103" s="64"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="15"/>
     </row>
     <row r="104" spans="1:8" ht="15">
-      <c r="A104" s="56">
-        <v>3</v>
-      </c>
-      <c r="B104" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="C104" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E104" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G104" s="20"/>
-      <c r="H104" s="20"/>
-    </row>
-    <row r="105" spans="1:8" ht="30.75">
-      <c r="A105" s="56">
-        <v>4</v>
-      </c>
-      <c r="B105" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C105" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="D105" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E105" s="55" t="s">
-        <v>116</v>
-      </c>
+      <c r="A104" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15">
+      <c r="A105" s="1">
+        <v>1</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="4"/>
       <c r="F105" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G105" s="20"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106" spans="1:8" ht="15">
-      <c r="A106" s="72">
-        <v>5</v>
-      </c>
-      <c r="B106" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="C106" s="55" t="s">
+    <row r="106" spans="1:8" ht="121.5">
+      <c r="A106" s="1">
+        <v>2</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="D106" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E106" s="55" t="s">
-        <v>116</v>
-      </c>
+      <c r="D106" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E106" s="4"/>
       <c r="F106" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G106" s="20"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107" spans="1:8" ht="15">
-      <c r="A107" s="72"/>
-      <c r="B107" s="74"/>
-      <c r="C107" s="55" t="s">
+    <row r="107" spans="1:8" ht="106.5">
+      <c r="A107" s="1">
+        <v>3</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D107" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E107" s="55" t="s">
-        <v>116</v>
-      </c>
+      <c r="E107" s="4"/>
       <c r="F107" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G107" s="20"/>
       <c r="H107" s="20"/>
     </row>
-    <row r="108" spans="1:8" ht="15">
-      <c r="A108" s="72"/>
-      <c r="B108" s="74"/>
-      <c r="C108" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D108" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E108" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="F108" s="1"/>
+    <row r="108" spans="1:8" ht="152.25">
+      <c r="A108" s="1">
+        <v>4</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G108" s="20"/>
       <c r="H108" s="20"/>
     </row>
-    <row r="109" spans="1:8" ht="15">
-      <c r="A109" s="73"/>
-      <c r="B109" s="75"/>
-      <c r="C109" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="D109" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E109" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="F109" s="1"/>
+    <row r="109" spans="1:8" ht="152.25">
+      <c r="A109" s="1">
+        <v>5</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110" spans="1:8" ht="15">
-      <c r="A110" s="9">
-        <v>12</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C110" s="68" t="s">
+    <row r="110" spans="1:8" ht="152.25">
+      <c r="A110" s="1">
+        <v>6</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="D110" s="68"/>
-      <c r="E110" s="68"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="14"/>
-      <c r="H110" s="15"/>
-    </row>
-    <row r="111" spans="1:8" ht="15">
-      <c r="A111" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E111" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" s="12" t="s">
+      <c r="D110" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="20"/>
+      <c r="H110" s="20"/>
+    </row>
+    <row r="111" spans="1:8" ht="152.25">
+      <c r="A111" s="1">
         <v>7</v>
       </c>
-      <c r="G111" s="12" t="s">
+      <c r="B111" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="20"/>
+      <c r="H111" s="20"/>
+    </row>
+    <row r="112" spans="1:8" ht="137.25">
+      <c r="A112" s="1">
         <v>8</v>
       </c>
-      <c r="H111" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="15">
-      <c r="A112" s="1">
-        <v>1</v>
-      </c>
       <c r="B112" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C112" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C112" s="31" t="s">
+        <v>133</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="E112" s="4"/>
-      <c r="F112" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F112" s="1"/>
       <c r="G112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113" spans="1:8" ht="121.5">
+    <row r="113" spans="1:8" ht="30.75">
       <c r="A113" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B113" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="57" t="s">
-        <v>132</v>
+      <c r="C113" s="31" t="s">
+        <v>134</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="E113" s="4"/>
-      <c r="F113" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-    </row>
-    <row r="114" spans="1:8" ht="106.5">
-      <c r="A114" s="1">
-        <v>3</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E114" s="4"/>
-      <c r="F114" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G114" s="20"/>
-      <c r="H114" s="20"/>
-    </row>
-    <row r="115" spans="1:8" ht="152.25">
-      <c r="A115" s="1">
-        <v>4</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" s="31" t="s">
+      <c r="F113" s="1"/>
+      <c r="G113" s="48"/>
+      <c r="H113" s="49"/>
+    </row>
+    <row r="114" spans="1:8" ht="15">
+      <c r="A114" s="9">
+        <v>13</v>
+      </c>
+      <c r="B114" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E115" s="4"/>
-      <c r="F115" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G115" s="20"/>
-      <c r="H115" s="20"/>
-    </row>
-    <row r="116" spans="1:8" ht="152.25">
+      <c r="C114" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="D114" s="64"/>
+      <c r="E114" s="64"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="15"/>
+    </row>
+    <row r="115" spans="1:8" ht="15">
+      <c r="A115" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="15">
       <c r="A116" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C116" s="47" t="s">
-        <v>136</v>
+        <v>18</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="1" t="s">
@@ -4656,18 +4629,18 @@
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117" spans="1:8" ht="152.25">
+    <row r="117" spans="1:8" ht="60.75">
       <c r="A117" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C117" s="58" t="s">
+      <c r="C117" s="57" t="s">
         <v>137</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="1" t="s">
@@ -4676,18 +4649,18 @@
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118" spans="1:8" ht="152.25">
+    <row r="118" spans="1:8" ht="60.75">
       <c r="A118" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C118" s="31" t="s">
+      <c r="C118" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="1" t="s">
@@ -4696,156 +4669,158 @@
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119" spans="1:8" ht="137.25">
+    <row r="119" spans="1:8" ht="30.75">
       <c r="A119" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B119" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C119" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E119" s="4"/>
-      <c r="F119" s="1"/>
+      <c r="F119" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G119" s="20"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120" spans="1:8" ht="30.75">
+    <row r="120" spans="1:8" ht="76.5">
       <c r="A120" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B120" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C120" s="31" t="s">
-        <v>140</v>
+      <c r="C120" s="47" t="s">
+        <v>141</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="E120" s="4"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="49"/>
-    </row>
-    <row r="121" spans="1:8" ht="15">
-      <c r="A121" s="9">
-        <v>13</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C121" s="68" t="s">
+      <c r="F120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
+    </row>
+    <row r="121" spans="1:8" ht="60.75">
+      <c r="A121" s="1">
+        <v>6</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C121" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="D121" s="68"/>
-      <c r="E121" s="68"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="15"/>
-    </row>
-    <row r="122" spans="1:8" ht="15">
-      <c r="A122" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B122" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E122" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F122" s="12" t="s">
+      <c r="D121" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121" s="20"/>
+      <c r="H121" s="20"/>
+    </row>
+    <row r="122" spans="1:8" ht="76.5">
+      <c r="A122" s="1">
         <v>7</v>
       </c>
-      <c r="G122" s="12" t="s">
+      <c r="B122" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C122" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" s="20"/>
+      <c r="H122" s="20"/>
+    </row>
+    <row r="123" spans="1:8" ht="60.75">
+      <c r="A123" s="1">
         <v>8</v>
       </c>
-      <c r="H122" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="15">
-      <c r="A123" s="1">
-        <v>1</v>
-      </c>
       <c r="B123" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>144</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="E123" s="4"/>
-      <c r="F123" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F123" s="1"/>
       <c r="G123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124" spans="1:8" ht="60.75">
-      <c r="A124" s="1">
-        <v>2</v>
-      </c>
-      <c r="B124" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C124" s="57" t="s">
-        <v>143</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E124" s="4"/>
-      <c r="F124" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-    </row>
-    <row r="125" spans="1:8" ht="60.75">
-      <c r="A125" s="1">
-        <v>3</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C125" s="19" t="s">
+    <row r="124" spans="1:8" ht="15">
+      <c r="A124" s="9">
+        <v>14</v>
+      </c>
+      <c r="B124" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E125" s="4"/>
-      <c r="F125" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
-    </row>
-    <row r="126" spans="1:8" ht="30.75">
+      <c r="C124" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="D124" s="64"/>
+      <c r="E124" s="64"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="14"/>
+      <c r="H124" s="15"/>
+    </row>
+    <row r="125" spans="1:8" ht="15">
+      <c r="A125" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G125" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="15">
       <c r="A126" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C126" s="31" t="s">
-        <v>146</v>
+        <v>18</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="1" t="s">
@@ -4854,18 +4829,18 @@
       <c r="G126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8" ht="76.5">
+    <row r="127" spans="1:8" ht="15">
       <c r="A127" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B127" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C127" s="47" t="s">
+      <c r="C127" s="57" t="s">
         <v>147</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="1" t="s">
@@ -4874,18 +4849,18 @@
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8" ht="60.75">
+    <row r="128" spans="1:8" ht="30.75">
       <c r="A128" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B128" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C128" s="58" t="s">
+      <c r="C128" s="19" t="s">
         <v>148</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="1" t="s">
@@ -4894,18 +4869,18 @@
       <c r="G128" s="20"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129" spans="1:8" ht="76.5">
+    <row r="129" spans="1:8" ht="30.75">
       <c r="A129" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C129" s="31" t="s">
         <v>149</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="1" t="s">
@@ -4914,78 +4889,80 @@
       <c r="G129" s="20"/>
       <c r="H129" s="20"/>
     </row>
-    <row r="130" spans="1:8" ht="60.75">
-      <c r="A130" s="1">
+    <row r="130" spans="1:8" ht="15">
+      <c r="A130" s="9">
+        <v>15</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C130" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D130" s="64"/>
+      <c r="E130" s="64"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="14"/>
+      <c r="H130" s="15"/>
+    </row>
+    <row r="131" spans="1:8" ht="15">
+      <c r="A131" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G131" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B130" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C130" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E130" s="4"/>
-      <c r="F130" s="1"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="20"/>
-    </row>
-    <row r="131" spans="1:8" ht="15">
-      <c r="A131" s="9">
-        <v>14</v>
-      </c>
-      <c r="B131" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C131" s="68" t="s">
+      <c r="H131" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="15">
+      <c r="A132" s="1">
+        <v>1</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="4"/>
+      <c r="F132" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
+    </row>
+    <row r="133" spans="1:8" ht="60.75">
+      <c r="A133" s="1">
+        <v>2</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="D131" s="68"/>
-      <c r="E131" s="68"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="14"/>
-      <c r="H131" s="15"/>
-    </row>
-    <row r="132" spans="1:8" ht="15">
-      <c r="A132" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E132" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F132" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G132" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H132" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="15">
-      <c r="A133" s="1">
-        <v>1</v>
-      </c>
-      <c r="B133" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D133" s="1" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="1" t="s">
@@ -4996,16 +4973,16 @@
     </row>
     <row r="134" spans="1:8" ht="15">
       <c r="A134" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C134" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C134" s="19" t="s">
         <v>153</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="1" t="s">
@@ -5014,18 +4991,18 @@
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135" spans="1:8" ht="30.75">
+    <row r="135" spans="1:8" ht="15">
       <c r="A135" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C135" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="31" t="s">
         <v>154</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="1" t="s">
@@ -5034,18 +5011,18 @@
       <c r="G135" s="20"/>
       <c r="H135" s="20"/>
     </row>
-    <row r="136" spans="1:8" ht="30.75">
+    <row r="136" spans="1:8" ht="60.75">
       <c r="A136" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="C136" s="31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="1" t="s">
@@ -5056,16 +5033,16 @@
     </row>
     <row r="137" spans="1:8" ht="15">
       <c r="A137" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C137" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="D137" s="68"/>
-      <c r="E137" s="68"/>
+      <c r="C137" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="D137" s="66"/>
+      <c r="E137" s="66"/>
       <c r="F137" s="9"/>
       <c r="G137" s="14"/>
       <c r="H137" s="15"/>
@@ -5116,7 +5093,7 @@
       <c r="G139" s="20"/>
       <c r="H139" s="20"/>
     </row>
-    <row r="140" spans="1:8" ht="60.75">
+    <row r="140" spans="1:8" ht="76.5">
       <c r="A140" s="1">
         <v>2</v>
       </c>
@@ -5124,10 +5101,10 @@
         <v>23</v>
       </c>
       <c r="C140" s="57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="1" t="s">
@@ -5136,18 +5113,18 @@
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141" spans="1:8" ht="15">
+    <row r="141" spans="1:8" ht="106.5">
       <c r="A141" s="1">
         <v>3</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="C141" s="19" t="s">
         <v>160</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="1" t="s">
@@ -5156,18 +5133,18 @@
       <c r="G141" s="20"/>
       <c r="H141" s="20"/>
     </row>
-    <row r="142" spans="1:8" ht="15">
+    <row r="142" spans="1:8" ht="76.5">
       <c r="A142" s="1">
         <v>4</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C142" s="31" t="s">
         <v>161</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="1" t="s">
@@ -5181,13 +5158,13 @@
         <v>5</v>
       </c>
       <c r="B143" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="C143" s="31" t="s">
-        <v>163</v>
-      </c>
       <c r="D143" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="1" t="s">
@@ -5196,80 +5173,80 @@
       <c r="G143" s="20"/>
       <c r="H143" s="20"/>
     </row>
-    <row r="144" spans="1:8" ht="15">
-      <c r="A144" s="9">
+    <row r="144" spans="1:8" ht="76.5">
+      <c r="A144" s="1">
+        <v>6</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" s="20"/>
+      <c r="H144" s="20"/>
+    </row>
+    <row r="145" spans="1:8" ht="15">
+      <c r="A145" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C145" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="D145" s="66"/>
+      <c r="E145" s="66"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="14"/>
+      <c r="H145" s="15"/>
+    </row>
+    <row r="146" spans="1:8" ht="15">
+      <c r="A146" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B144" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C144" s="60" t="s">
-        <v>165</v>
-      </c>
-      <c r="D144" s="60"/>
-      <c r="E144" s="60"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="14"/>
-      <c r="H144" s="15"/>
-    </row>
-    <row r="145" spans="1:8" ht="15">
-      <c r="A145" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B145" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D145" s="12" t="s">
+      <c r="D146" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E145" s="12" t="s">
+      <c r="E146" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F145" s="12" t="s">
+      <c r="F146" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G145" s="12" t="s">
+      <c r="G146" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H145" s="11" t="s">
+      <c r="H146" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" ht="15">
-      <c r="A146" s="1">
-        <v>1</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E146" s="4"/>
-      <c r="F146" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
     </row>
     <row r="147" spans="1:8" ht="76.5">
       <c r="A147" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B147" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C147" s="57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="1" t="s">
@@ -5278,18 +5255,18 @@
       <c r="G147" s="20"/>
       <c r="H147" s="20"/>
     </row>
-    <row r="148" spans="1:8" ht="106.5">
+    <row r="148" spans="1:8" ht="15">
       <c r="A148" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B148" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="1" t="s">
@@ -5298,148 +5275,13 @@
       <c r="G148" s="20"/>
       <c r="H148" s="20"/>
     </row>
-    <row r="149" spans="1:8" ht="76.5">
-      <c r="A149" s="1">
-        <v>4</v>
-      </c>
-      <c r="B149" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C149" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E149" s="4"/>
-      <c r="F149" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G149" s="20"/>
-      <c r="H149" s="20"/>
-    </row>
-    <row r="150" spans="1:8" ht="60.75">
-      <c r="A150" s="1">
-        <v>5</v>
-      </c>
-      <c r="B150" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C150" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E150" s="4"/>
-      <c r="F150" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
-    </row>
-    <row r="151" spans="1:8" ht="76.5">
-      <c r="A151" s="1">
-        <v>6</v>
-      </c>
-      <c r="B151" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C151" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E151" s="4"/>
-      <c r="F151" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G151" s="20"/>
-      <c r="H151" s="20"/>
-    </row>
-    <row r="152" spans="1:8" ht="15">
-      <c r="A152" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B152" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C152" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="D152" s="60"/>
-      <c r="E152" s="60"/>
-      <c r="F152" s="9"/>
-      <c r="G152" s="14"/>
-      <c r="H152" s="15"/>
-    </row>
-    <row r="153" spans="1:8" ht="15">
-      <c r="A153" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B153" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D153" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E153" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F153" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G153" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H153" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="76.5">
-      <c r="A154" s="1">
-        <v>1</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C154" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E154" s="4"/>
-      <c r="F154" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G154" s="20"/>
-      <c r="H154" s="20"/>
-    </row>
-    <row r="155" spans="1:8" ht="15">
-      <c r="A155" s="1">
-        <v>2</v>
-      </c>
-      <c r="B155" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E155" s="4"/>
-      <c r="F155" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G155" s="20"/>
-      <c r="H155" s="20"/>
-    </row>
+    <row r="149" spans="1:8" ht="15"/>
+    <row r="150" spans="1:8" ht="15"/>
+    <row r="151" spans="1:8" ht="15"/>
+    <row r="152" spans="1:8" ht="15"/>
+    <row r="153" spans="1:8" ht="15"/>
+    <row r="154" spans="1:8" ht="15"/>
+    <row r="155" spans="1:8" ht="15"/>
     <row r="156" spans="1:8" ht="15"/>
     <row r="157" spans="1:8" ht="15"/>
     <row r="158" spans="1:8" ht="15"/>
@@ -5454,50 +5296,43 @@
     <row r="167" ht="15"/>
     <row r="168" ht="15"/>
     <row r="169" ht="15"/>
-    <row r="170" ht="15"/>
     <row r="171" ht="15"/>
-    <row r="172" ht="15"/>
     <row r="173" ht="15"/>
-    <row r="174" ht="15"/>
     <row r="175" ht="15"/>
-    <row r="176" ht="15"/>
-    <row r="178" ht="15"/>
-    <row r="180" ht="15"/>
-    <row r="182" ht="15"/>
   </sheetData>
   <autoFilter ref="A3:H32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="28">
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C45:E45"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C152:E152"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="C103:E103"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F87:F1048576 F3:F75">
+  <conditionalFormatting sqref="F1 F80:F1048576 F3:F68">
     <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5508,7 +5343,7 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F76:F81 F83 F85">
+  <conditionalFormatting sqref="F69:F74 F76 F78">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5520,7 +5355,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41:F51 F17:F26 F37:F38 F54:F64 F67:F75 F6:F14 F29:F30 F33:F34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F26 F37:F38 F47:F57 F60:F68 F6:F14 F29:F30 F33:F34 F41:F44" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5544,7 +5379,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
       <c r="A1" s="76" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -5556,10 +5391,10 @@
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5567,15 +5402,15 @@
         <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5583,7 +5418,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5596,21 +5431,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D22D72570E156D4F9C34B893E183F0BF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ec9c283aea1b7e9b2a2bfe7317a7796f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -5724,8 +5544,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5733,5 +5568,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29415"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09040B4-E99D-4725-908B-A8F73CCC5ED2}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD52902-7349-4483-A037-CECC8566A209}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="176">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -235,62 +235,64 @@
 Check excel sheet for feedbacks</t>
   </si>
   <si>
-    <t xml:space="preserve"> Abdelgafar ismail,  Diallo Fadilatou, Excellence program Students</t>
+    <t xml:space="preserve"> Abdelgafar Ismail,  Diallo Fadilatou, Excellence program Students</t>
   </si>
   <si>
     <t>Fill PPT template with information bachelor thesis topic</t>
   </si>
   <si>
-    <t xml:space="preserve">Add name of each students the cheat they are working on.  Change name of the Ball mill grinder to Processing Machines on the Excel spreadsheet. </t>
+    <t xml:space="preserve">Add name of each students the sheet they are working on.  Change name of the Ball mill grinder to Processing Machines on the Excel spreadsheet. </t>
   </si>
   <si>
     <t xml:space="preserve"> Info</t>
   </si>
   <si>
-    <t xml:space="preserve">Admin feedback during JF: Plants and irrigation =&gt; Abdo                                           Processing Machines and Smart dryer =&gt; Hans                                                Solar PV and Solar Tracking =&gt; Fadila                                                              No Reesa and Facial Recognition =&gt; Botho/Vanessa              </t>
-  </si>
-  <si>
-    <t>10.01.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm, Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer, Seah Qiao Ling, JamesDevassia Cherupillet</t>
-  </si>
-  <si>
-    <t>Adams: thanks for integrating ball mill into the sustainable farm would be good if you can give some figures in an .xls. use class names for the column headlines
-Always good if you check the homepage upfront</t>
+    <t xml:space="preserve">feedback during JF on excel spreadsheet: Plants and irrigation =&gt; Abdo                                           Processing Machines and Smart dryer =&gt; Hans                                                Solar PV and Solar Tracking =&gt; Fadila                                                              No Reesa and Facial Recognition =&gt; Botho/Vanessa              </t>
+  </si>
+  <si>
+    <t>17.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hans Ehm, Abdelgafar Ismail,Diallo Fadilatou, Excellence program Students</t>
+  </si>
+  <si>
+    <t>Salowe: Maybe you can talk about how to use face recognition in the sustainable farm.
+ very good presentation! did you test the system? What was the accuracy?</t>
+  </si>
+  <si>
+    <t>Ange: Maybe also useful to clean or keep the solar panels cold – Maybe use one in the sustainable farm.
+very good presentation! Did you also build a prototype?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Arcus: can we use the same setup for the sustainable farm, how would you further improve.
+how much energy output you got? and how much is the cost of the 1kw of energy using your approach?</t>
+  </si>
+  <si>
+    <t>Yannick: I guess the capacity is 50 MWh and not MW, right? What can be used for the sustainable farm? What Peak Power and how much capacity.
+were you able to reduce the energy import from 60%? How much is the cost of the battery system?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Afia: well understood. Can we have a mobile app for the sustainable farm?
+what were the benefits of the app in terms of cost and revenue?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Mare: What crop should you propose for the sustainable farm to use your harvesting machine: Onion, carrot or lettuce?
+you mentioned the reduction in the labor? Is there any numerical value for the reduction? E.g. 10% …etc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Poda: How and where could your smart Meter be integrated into the sustainable farm. 
+also is there any numerical value for the reduction? E.g. 10% …etc.</t>
+  </si>
+  <si>
+    <t>General: 
+Maybe Link your thesis paper on your homepages</t>
   </si>
   <si>
     <t>Hans</t>
-  </si>
-  <si>
-    <t>Adjara: Maybe we can all look at your ontology</t>
-  </si>
-  <si>
-    <t>Alicia: great idea to use the cowpea thresher in the sustainable farm à do you think the thresher could be customized for other products from the farm other than cowpea</t>
-  </si>
-  <si>
-    <t>Charles: thanks for integrating the irrigation into the sustainable farm would be good if you can give some figures in an .xls. use class names for the column headlines</t>
-  </si>
-  <si>
-    <t>Lucas:  thanks for integrating the smart dryer into the sustainable farm would be good if you can give some figures in an .xls. use class names for the column headlines</t>
-  </si>
-  <si>
-    <t>Boris: think about how to integrate Face recognition into the sustainable farm. I like the way of detecting beneficial and non beneficial plants. Maybe also access rights for the farms</t>
-  </si>
-  <si>
-    <t>Gertrude: Think about the size of the solar system</t>
-  </si>
-  <si>
-    <t>Wilfried: Solar tracking system to increase output of solar panels. Think about the size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamado:   language is important I agree
-</t>
-  </si>
-  <si>
-    <t>General: 
-All let us think about the size for simulation, for small and medium prototype.
-Maybe we work together on building the farm .xls</t>
   </si>
   <si>
     <t>17.01.2025</t>
@@ -1396,6 +1398,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1406,42 +1444,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2336,16 +2338,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -2864,11 +2866,11 @@
       <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
@@ -2946,11 +2948,11 @@
       <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="64" t="s">
+      <c r="C31" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
@@ -3030,11 +3032,11 @@
       <c r="B35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
       <c r="F35" s="9"/>
       <c r="G35" s="14"/>
       <c r="H35" s="15"/>
@@ -3112,11 +3114,11 @@
       <c r="B39" s="10">
         <v>45943</v>
       </c>
-      <c r="C39" s="64" t="s">
+      <c r="C39" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
       <c r="F39" s="9"/>
       <c r="G39" s="14"/>
       <c r="H39" s="15"/>
@@ -3207,7 +3209,7 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
     </row>
-    <row r="44" spans="1:8" ht="60.75">
+    <row r="44" spans="1:8" ht="76.5">
       <c r="A44" s="1">
         <v>4</v>
       </c>
@@ -3227,18 +3229,18 @@
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" ht="15">
       <c r="A45" s="9">
         <v>7</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
       <c r="F45" s="9"/>
       <c r="G45" s="14"/>
       <c r="H45" s="15"/>
@@ -3289,7 +3291,7 @@
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
     </row>
-    <row r="48" spans="1:8" ht="72.599999999999994">
+    <row r="48" spans="1:8" ht="60.75">
       <c r="A48" s="1">
         <v>2</v>
       </c>
@@ -3300,7 +3302,7 @@
         <v>66</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="1" t="s">
@@ -3309,7 +3311,7 @@
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="45.75">
       <c r="A49" s="1">
         <v>3</v>
       </c>
@@ -3317,10 +3319,10 @@
         <v>23</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="1" t="s">
@@ -3329,7 +3331,7 @@
       <c r="G49" s="20"/>
       <c r="H49" s="20"/>
     </row>
-    <row r="50" spans="1:8" ht="43.5">
+    <row r="50" spans="1:8" ht="76.5">
       <c r="A50" s="1">
         <v>4</v>
       </c>
@@ -3337,10 +3339,10 @@
         <v>23</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="1" t="s">
@@ -3349,7 +3351,7 @@
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
     </row>
-    <row r="51" spans="1:8" ht="43.5">
+    <row r="51" spans="1:8" ht="76.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -3357,10 +3359,10 @@
         <v>23</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="1" t="s">
@@ -3369,7 +3371,7 @@
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
     </row>
-    <row r="52" spans="1:8" ht="43.5">
+    <row r="52" spans="1:8" ht="60.75">
       <c r="A52" s="1">
         <v>6</v>
       </c>
@@ -3377,10 +3379,10 @@
         <v>23</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="1" t="s">
@@ -3389,7 +3391,7 @@
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
     </row>
-    <row r="53" spans="1:8" ht="43.5">
+    <row r="53" spans="1:8" ht="76.5">
       <c r="A53" s="1">
         <v>7</v>
       </c>
@@ -3397,10 +3399,10 @@
         <v>23</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="1" t="s">
@@ -3409,7 +3411,7 @@
       <c r="G53" s="20"/>
       <c r="H53" s="20"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" ht="60.75">
       <c r="A54" s="1">
         <v>8</v>
       </c>
@@ -3417,19 +3419,17 @@
         <v>23</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E54" s="4"/>
-      <c r="F54" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
     </row>
-    <row r="55" spans="1:8" ht="29.1">
+    <row r="55" spans="1:8" ht="30.75">
       <c r="A55" s="1">
         <v>9</v>
       </c>
@@ -3437,108 +3437,112 @@
         <v>23</v>
       </c>
       <c r="C55" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="E55" s="4"/>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="G55" s="20"/>
       <c r="H55" s="20"/>
     </row>
-    <row r="56" spans="1:8" ht="29.1">
-      <c r="A56" s="1">
-        <v>10</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="31" t="s">
+    <row r="56" spans="1:8">
+      <c r="A56" s="9">
+        <v>8</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-    </row>
-    <row r="57" spans="1:8" ht="72.599999999999994">
-      <c r="A57" s="1">
-        <v>11</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" s="31" t="s">
+      <c r="C56" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="15"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="9">
-        <v>8</v>
-      </c>
-      <c r="B58" s="10" t="s">
+      <c r="A58" s="1">
+        <v>1</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+    </row>
+    <row r="59" spans="1:8" ht="72.599999999999994">
+      <c r="A59" s="1">
+        <v>2</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C58" s="64" t="s">
+      <c r="D59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+    </row>
+    <row r="60" spans="1:8" ht="57.95">
+      <c r="A60" s="1">
+        <v>3</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="15"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="1">
-        <v>1</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D60" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="1" t="s">
@@ -3547,14 +3551,14 @@
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8" ht="72.599999999999994">
+    <row r="61" spans="1:8" ht="76.5">
       <c r="A61" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="31" t="s">
         <v>79</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -3567,14 +3571,14 @@
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8" ht="57.95">
+    <row r="62" spans="1:8" ht="72.599999999999994">
       <c r="A62" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="32" t="s">
         <v>80</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -3587,9 +3591,9 @@
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63" spans="1:8" ht="76.5">
+    <row r="63" spans="1:8" ht="87">
       <c r="A63" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>23</v>
@@ -3607,14 +3611,14 @@
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64" spans="1:8" ht="72.599999999999994">
+    <row r="64" spans="1:8" ht="87">
       <c r="A64" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C64" s="32" t="s">
+      <c r="C64" s="31" t="s">
         <v>82</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -3627,9 +3631,9 @@
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="87">
+    <row r="65" spans="1:8" ht="57.95">
       <c r="A65" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>23</v>
@@ -3641,15 +3645,13 @@
         <v>25</v>
       </c>
       <c r="E65" s="4"/>
-      <c r="F65" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F65" s="1"/>
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66" spans="1:8" ht="87">
+    <row r="66" spans="1:8" ht="106.5">
       <c r="A66" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>23</v>
@@ -3661,104 +3663,100 @@
         <v>25</v>
       </c>
       <c r="E66" s="4"/>
-      <c r="F66" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F66" s="1"/>
       <c r="G66" s="20"/>
       <c r="H66" s="20"/>
     </row>
-    <row r="67" spans="1:8" ht="57.95">
-      <c r="A67" s="1">
+    <row r="67" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A67" s="33">
+        <v>9</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="D67" s="62"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="15"/>
+    </row>
+    <row r="68" spans="1:8" s="35" customFormat="1" ht="15.75">
+      <c r="A68" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="H68" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="16.5">
+      <c r="A69" s="38">
+        <v>1</v>
+      </c>
+      <c r="B69" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="40"/>
+      <c r="F69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+    </row>
+    <row r="70" spans="1:8" ht="46.5">
+      <c r="A70" s="41">
+        <v>2</v>
+      </c>
+      <c r="B70" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-    </row>
-    <row r="68" spans="1:8" ht="106.5">
-      <c r="A68" s="1">
-        <v>9</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C68" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="4"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-    </row>
-    <row r="69" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A69" s="33">
-        <v>9</v>
-      </c>
-      <c r="B69" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="67" t="s">
+      <c r="E70" s="43"/>
+      <c r="F70" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+    </row>
+    <row r="71" spans="1:8" ht="46.5">
+      <c r="A71" s="44"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="69"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="15"/>
-    </row>
-    <row r="70" spans="1:8" s="35" customFormat="1" ht="15.75">
-      <c r="A70" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B70" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H70" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="16.5">
-      <c r="A71" s="38">
-        <v>1</v>
-      </c>
-      <c r="B71" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D71" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="40"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
       <c r="F71" s="1" t="s">
         <v>22</v>
       </c>
@@ -3767,7 +3765,7 @@
     </row>
     <row r="72" spans="1:8" ht="46.5">
       <c r="A72" s="41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" s="42" t="s">
         <v>23</v>
@@ -3779,11 +3777,11 @@
         <v>25</v>
       </c>
       <c r="E72" s="43"/>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="64" t="s">
         <v>22</v>
       </c>
       <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
+      <c r="H72" s="66"/>
     </row>
     <row r="73" spans="1:8" ht="46.5">
       <c r="A73" s="44"/>
@@ -3793,15 +3791,13 @@
       </c>
       <c r="D73" s="45"/>
       <c r="E73" s="45"/>
-      <c r="F73" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F73" s="65"/>
       <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-    </row>
-    <row r="74" spans="1:8" ht="46.5">
+      <c r="H73" s="67"/>
+    </row>
+    <row r="74" spans="1:8" ht="30.75">
       <c r="A74" s="41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B74" s="42" t="s">
         <v>23</v>
@@ -3813,13 +3809,13 @@
         <v>25</v>
       </c>
       <c r="E74" s="43"/>
-      <c r="F74" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="20"/>
-      <c r="H74" s="72"/>
-    </row>
-    <row r="75" spans="1:8" ht="46.5">
+      <c r="F74" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="66"/>
+      <c r="H74" s="66"/>
+    </row>
+    <row r="75" spans="1:8" ht="61.5">
       <c r="A75" s="44"/>
       <c r="B75" s="45"/>
       <c r="C75" s="46" t="s">
@@ -3827,13 +3823,13 @@
       </c>
       <c r="D75" s="45"/>
       <c r="E75" s="45"/>
-      <c r="F75" s="71"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="73"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="67"/>
+      <c r="H75" s="67"/>
     </row>
     <row r="76" spans="1:8" ht="30.75">
       <c r="A76" s="41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B76" s="42" t="s">
         <v>23</v>
@@ -3845,13 +3841,11 @@
         <v>25</v>
       </c>
       <c r="E76" s="43"/>
-      <c r="F76" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="72"/>
-      <c r="H76" s="72"/>
-    </row>
-    <row r="77" spans="1:8" ht="61.5">
+      <c r="F76" s="64"/>
+      <c r="G76" s="66"/>
+      <c r="H76" s="66"/>
+    </row>
+    <row r="77" spans="1:8" ht="30.75">
       <c r="A77" s="44"/>
       <c r="B77" s="45"/>
       <c r="C77" s="46" t="s">
@@ -3859,94 +3853,104 @@
       </c>
       <c r="D77" s="45"/>
       <c r="E77" s="45"/>
-      <c r="F77" s="71"/>
-      <c r="G77" s="73"/>
-      <c r="H77" s="73"/>
-    </row>
-    <row r="78" spans="1:8" ht="30.75">
-      <c r="A78" s="41">
-        <v>5</v>
-      </c>
-      <c r="B78" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C78" s="42" t="s">
+      <c r="F77" s="65"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+    </row>
+    <row r="78" spans="1:8" ht="15">
+      <c r="A78" s="9">
+        <v>10</v>
+      </c>
+      <c r="B78" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D78" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="43"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="72"/>
-      <c r="H78" s="72"/>
-    </row>
-    <row r="79" spans="1:8" ht="30.75">
-      <c r="A79" s="44"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="46" t="s">
+      <c r="C78" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D79" s="45"/>
-      <c r="E79" s="45"/>
-      <c r="F79" s="71"/>
-      <c r="G79" s="73"/>
-      <c r="H79" s="73"/>
+      <c r="D78" s="68"/>
+      <c r="E78" s="68"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="15"/>
+    </row>
+    <row r="79" spans="1:8" ht="15">
+      <c r="A79" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="80" spans="1:8" ht="15">
-      <c r="A80" s="9">
-        <v>10</v>
-      </c>
-      <c r="B80" s="10" t="s">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" ht="60.75">
+      <c r="A81" s="1">
+        <v>2</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C80" s="64" t="s">
+      <c r="D81" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+    </row>
+    <row r="82" spans="1:8" ht="30.75">
+      <c r="A82" s="1">
+        <v>3</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="15"/>
-    </row>
-    <row r="81" spans="1:8" ht="15">
-      <c r="A81" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G81" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="15">
-      <c r="A82" s="1">
-        <v>1</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D82" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="1" t="s">
@@ -3955,14 +3959,14 @@
       <c r="G82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" ht="60.75">
+    <row r="83" spans="1:8" ht="76.5">
       <c r="A83" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="31" t="s">
         <v>99</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3975,14 +3979,14 @@
       <c r="G83" s="20"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84" spans="1:8" ht="30.75">
+    <row r="84" spans="1:8" ht="76.5">
       <c r="A84" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C84" s="47" t="s">
         <v>100</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3995,9 +3999,9 @@
       <c r="G84" s="20"/>
       <c r="H84" s="20"/>
     </row>
-    <row r="85" spans="1:8" ht="76.5">
+    <row r="85" spans="1:8" ht="45.75">
       <c r="A85" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B85" s="19" t="s">
         <v>23</v>
@@ -4017,12 +4021,12 @@
     </row>
     <row r="86" spans="1:8" ht="76.5">
       <c r="A86" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C86" s="47" t="s">
+      <c r="C86" s="31" t="s">
         <v>102</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -4035,9 +4039,9 @@
       <c r="G86" s="20"/>
       <c r="H86" s="20"/>
     </row>
-    <row r="87" spans="1:8" ht="45.75">
+    <row r="87" spans="1:8" ht="91.5">
       <c r="A87" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>23</v>
@@ -4049,15 +4053,13 @@
         <v>50</v>
       </c>
       <c r="E87" s="4"/>
-      <c r="F87" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F87" s="1"/>
       <c r="G87" s="20"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88" spans="1:8" ht="76.5">
+    <row r="88" spans="1:8" ht="60.75">
       <c r="A88" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>23</v>
@@ -4069,15 +4071,13 @@
         <v>50</v>
       </c>
       <c r="E88" s="4"/>
-      <c r="F88" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F88" s="1"/>
       <c r="G88" s="20"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89" spans="1:8" ht="91.5">
+    <row r="89" spans="1:8" ht="15">
       <c r="A89" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>23</v>
@@ -4086,106 +4086,110 @@
         <v>105</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="1"/>
-      <c r="G89" s="20"/>
-      <c r="H89" s="20"/>
-    </row>
-    <row r="90" spans="1:8" ht="60.75">
-      <c r="A90" s="1">
+      <c r="G89" s="48"/>
+      <c r="H89" s="49"/>
+    </row>
+    <row r="90" spans="1:8" ht="15" customHeight="1">
+      <c r="A90" s="50">
+        <v>11</v>
+      </c>
+      <c r="B90" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D90" s="69"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="15"/>
+    </row>
+    <row r="91" spans="1:8" ht="15">
+      <c r="A91" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B90" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E90" s="4"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-    </row>
-    <row r="91" spans="1:8" ht="15">
-      <c r="A91" s="1">
-        <v>10</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E91" s="4"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="49"/>
-    </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1">
-      <c r="A92" s="50">
-        <v>11</v>
-      </c>
-      <c r="B92" s="51" t="s">
+    </row>
+    <row r="92" spans="1:8" ht="15">
+      <c r="A92" s="54">
+        <v>1</v>
+      </c>
+      <c r="B92" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D92" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C92" s="74" t="s">
+      <c r="F92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+    </row>
+    <row r="93" spans="1:8" ht="15">
+      <c r="A93" s="72">
+        <v>2</v>
+      </c>
+      <c r="B93" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="75"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="15"/>
-    </row>
-    <row r="93" spans="1:8" ht="15">
-      <c r="A93" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="C93" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D93" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G93" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H93" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="C93" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D93" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="20"/>
+      <c r="H93" s="20"/>
     </row>
     <row r="94" spans="1:8" ht="15">
-      <c r="A94" s="54">
-        <v>1</v>
-      </c>
-      <c r="B94" s="55" t="s">
-        <v>18</v>
-      </c>
+      <c r="A94" s="73"/>
+      <c r="B94" s="75"/>
       <c r="C94" s="55" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E94" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>22</v>
@@ -4194,20 +4198,20 @@
       <c r="H94" s="20"/>
     </row>
     <row r="95" spans="1:8" ht="15">
-      <c r="A95" s="60">
-        <v>2</v>
-      </c>
-      <c r="B95" s="62" t="s">
+      <c r="A95" s="56">
+        <v>3</v>
+      </c>
+      <c r="B95" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="C95" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="D95" s="55" t="s">
-        <v>113</v>
-      </c>
       <c r="E95" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>22</v>
@@ -4215,17 +4219,21 @@
       <c r="G95" s="20"/>
       <c r="H95" s="20"/>
     </row>
-    <row r="96" spans="1:8" ht="15">
-      <c r="A96" s="61"/>
-      <c r="B96" s="63"/>
+    <row r="96" spans="1:8" ht="30.75">
+      <c r="A96" s="56">
+        <v>4</v>
+      </c>
+      <c r="B96" s="55" t="s">
+        <v>115</v>
+      </c>
       <c r="C96" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E96" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>22</v>
@@ -4234,20 +4242,20 @@
       <c r="H96" s="20"/>
     </row>
     <row r="97" spans="1:8" ht="15">
-      <c r="A97" s="56">
-        <v>3</v>
-      </c>
-      <c r="B97" s="55" t="s">
-        <v>115</v>
+      <c r="A97" s="72">
+        <v>5</v>
+      </c>
+      <c r="B97" s="74" t="s">
+        <v>117</v>
       </c>
       <c r="C97" s="55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E97" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>22</v>
@@ -4255,21 +4263,17 @@
       <c r="G97" s="20"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98" spans="1:8" ht="30.75">
-      <c r="A98" s="56">
-        <v>4</v>
-      </c>
-      <c r="B98" s="55" t="s">
-        <v>117</v>
-      </c>
+    <row r="98" spans="1:8" ht="15">
+      <c r="A98" s="72"/>
+      <c r="B98" s="74"/>
       <c r="C98" s="55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E98" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>22</v>
@@ -4278,131 +4282,131 @@
       <c r="H98" s="20"/>
     </row>
     <row r="99" spans="1:8" ht="15">
-      <c r="A99" s="60">
-        <v>5</v>
-      </c>
-      <c r="B99" s="62" t="s">
-        <v>119</v>
-      </c>
+      <c r="A99" s="72"/>
+      <c r="B99" s="74"/>
       <c r="C99" s="55" t="s">
         <v>120</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E99" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F99" s="1"/>
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
     </row>
     <row r="100" spans="1:8" ht="15">
-      <c r="A100" s="60"/>
-      <c r="B100" s="62"/>
+      <c r="A100" s="73"/>
+      <c r="B100" s="75"/>
       <c r="C100" s="55" t="s">
         <v>121</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E100" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F100" s="1"/>
       <c r="G100" s="20"/>
       <c r="H100" s="20"/>
     </row>
     <row r="101" spans="1:8" ht="15">
-      <c r="A101" s="60"/>
-      <c r="B101" s="62"/>
-      <c r="C101" s="55" t="s">
+      <c r="A101" s="9">
+        <v>12</v>
+      </c>
+      <c r="B101" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D101" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="E101" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="F101" s="1"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
+      <c r="C101" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="D101" s="68"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="15"/>
     </row>
     <row r="102" spans="1:8" ht="15">
-      <c r="A102" s="61"/>
-      <c r="B102" s="63"/>
-      <c r="C102" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="D102" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="E102" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="F102" s="1"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
+      <c r="A102" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="103" spans="1:8" ht="15">
-      <c r="A103" s="9">
-        <v>12</v>
-      </c>
-      <c r="B103" s="10" t="s">
+      <c r="A103" s="1">
+        <v>1</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+    </row>
+    <row r="104" spans="1:8" ht="121.5">
+      <c r="A104" s="1">
+        <v>2</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="C103" s="64" t="s">
+      <c r="D104" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D103" s="64"/>
-      <c r="E103" s="64"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="14"/>
-      <c r="H103" s="15"/>
-    </row>
-    <row r="104" spans="1:8" ht="15">
-      <c r="A104" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F104" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G104" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="15">
+      <c r="E104" s="4"/>
+      <c r="F104" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" s="20"/>
+      <c r="H104" s="20"/>
+    </row>
+    <row r="105" spans="1:8" ht="106.5">
       <c r="A105" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="1" t="s">
@@ -4411,18 +4415,18 @@
       <c r="G105" s="20"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106" spans="1:8" ht="121.5">
+    <row r="106" spans="1:8" ht="152.25">
       <c r="A106" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B106" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C106" s="57" t="s">
-        <v>126</v>
+      <c r="C106" s="31" t="s">
+        <v>127</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="1" t="s">
@@ -4431,18 +4435,18 @@
       <c r="G106" s="20"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107" spans="1:8" ht="106.5">
+    <row r="107" spans="1:8" ht="152.25">
       <c r="A107" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B107" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C107" s="19" t="s">
+      <c r="C107" s="47" t="s">
         <v>128</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="1" t="s">
@@ -4453,16 +4457,16 @@
     </row>
     <row r="108" spans="1:8" ht="152.25">
       <c r="A108" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B108" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C108" s="31" t="s">
+      <c r="C108" s="58" t="s">
         <v>129</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="1" t="s">
@@ -4473,16 +4477,16 @@
     </row>
     <row r="109" spans="1:8" ht="152.25">
       <c r="A109" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="47" t="s">
+      <c r="C109" s="31" t="s">
         <v>130</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="1" t="s">
@@ -4491,29 +4495,27 @@
       <c r="G109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110" spans="1:8" ht="152.25">
+    <row r="110" spans="1:8" ht="137.25">
       <c r="A110" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B110" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="58" t="s">
+      <c r="C110" s="31" t="s">
         <v>131</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E110" s="4"/>
-      <c r="F110" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F110" s="1"/>
       <c r="G110" s="20"/>
       <c r="H110" s="20"/>
     </row>
-    <row r="111" spans="1:8" ht="152.25">
+    <row r="111" spans="1:8" ht="30.75">
       <c r="A111" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>23</v>
@@ -4522,105 +4524,107 @@
         <v>132</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="E111" s="4"/>
-      <c r="F111" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
-    </row>
-    <row r="112" spans="1:8" ht="137.25">
-      <c r="A112" s="1">
+      <c r="F111" s="1"/>
+      <c r="G111" s="48"/>
+      <c r="H111" s="49"/>
+    </row>
+    <row r="112" spans="1:8" ht="15">
+      <c r="A112" s="9">
+        <v>13</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C112" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="D112" s="68"/>
+      <c r="E112" s="68"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="15"/>
+    </row>
+    <row r="113" spans="1:8" ht="15">
+      <c r="A113" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B112" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C112" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E112" s="4"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-    </row>
-    <row r="113" spans="1:8" ht="30.75">
-      <c r="A113" s="1">
+      <c r="H113" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E113" s="4"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="48"/>
-      <c r="H113" s="49"/>
     </row>
     <row r="114" spans="1:8" ht="15">
-      <c r="A114" s="9">
-        <v>13</v>
-      </c>
-      <c r="B114" s="10" t="s">
+      <c r="A114" s="1">
+        <v>1</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="20"/>
+      <c r="H114" s="20"/>
+    </row>
+    <row r="115" spans="1:8" ht="60.75">
+      <c r="A115" s="1">
+        <v>2</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="C114" s="64" t="s">
+      <c r="D115" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D114" s="64"/>
-      <c r="E114" s="64"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="14"/>
-      <c r="H114" s="15"/>
-    </row>
-    <row r="115" spans="1:8" ht="15">
-      <c r="A115" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E115" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G115" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H115" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="15">
+      <c r="E115" s="4"/>
+      <c r="F115" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G115" s="20"/>
+      <c r="H115" s="20"/>
+    </row>
+    <row r="116" spans="1:8" ht="60.75">
       <c r="A116" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="1" t="s">
@@ -4629,18 +4633,18 @@
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117" spans="1:8" ht="60.75">
+    <row r="117" spans="1:8" ht="30.75">
       <c r="A117" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C117" s="57" t="s">
-        <v>137</v>
+      <c r="C117" s="31" t="s">
+        <v>138</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="1" t="s">
@@ -4649,18 +4653,18 @@
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118" spans="1:8" ht="60.75">
+    <row r="118" spans="1:8" ht="76.5">
       <c r="A118" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C118" s="19" t="s">
+      <c r="C118" s="47" t="s">
         <v>139</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="1" t="s">
@@ -4669,18 +4673,18 @@
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119" spans="1:8" ht="30.75">
+    <row r="119" spans="1:8" ht="60.75">
       <c r="A119" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B119" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C119" s="31" t="s">
+      <c r="C119" s="58" t="s">
         <v>140</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="1" t="s">
@@ -4691,16 +4695,16 @@
     </row>
     <row r="120" spans="1:8" ht="76.5">
       <c r="A120" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B120" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C120" s="47" t="s">
+      <c r="C120" s="31" t="s">
         <v>141</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="1" t="s">
@@ -4711,116 +4715,116 @@
     </row>
     <row r="121" spans="1:8" ht="60.75">
       <c r="A121" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B121" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C121" s="58" t="s">
+      <c r="C121" s="31" t="s">
         <v>142</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E121" s="4"/>
-      <c r="F121" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F121" s="1"/>
       <c r="G121" s="20"/>
       <c r="H121" s="20"/>
     </row>
-    <row r="122" spans="1:8" ht="76.5">
-      <c r="A122" s="1">
+    <row r="122" spans="1:8" ht="15">
+      <c r="A122" s="9">
+        <v>14</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C122" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="D122" s="68"/>
+      <c r="E122" s="68"/>
+      <c r="F122" s="9"/>
+      <c r="G122" s="14"/>
+      <c r="H122" s="15"/>
+    </row>
+    <row r="123" spans="1:8" ht="15">
+      <c r="A123" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B122" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C122" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E122" s="4"/>
-      <c r="F122" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-    </row>
-    <row r="123" spans="1:8" ht="60.75">
-      <c r="A123" s="1">
+      <c r="G123" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B123" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C123" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E123" s="4"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
+      <c r="H123" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="124" spans="1:8" ht="15">
-      <c r="A124" s="9">
-        <v>14</v>
-      </c>
-      <c r="B124" s="10" t="s">
+      <c r="A124" s="1">
+        <v>1</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
+    </row>
+    <row r="125" spans="1:8" ht="15">
+      <c r="A125" s="1">
+        <v>2</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C125" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="C124" s="64" t="s">
+      <c r="D125" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="20"/>
+      <c r="H125" s="20"/>
+    </row>
+    <row r="126" spans="1:8" ht="30.75">
+      <c r="A126" s="1">
+        <v>3</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D124" s="64"/>
-      <c r="E124" s="64"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="15"/>
-    </row>
-    <row r="125" spans="1:8" ht="15">
-      <c r="A125" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B125" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C125" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E125" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F125" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G125" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H125" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="15">
-      <c r="A126" s="1">
-        <v>1</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="1" t="s">
@@ -4829,18 +4833,18 @@
       <c r="G126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8" ht="15">
+    <row r="127" spans="1:8" ht="30.75">
       <c r="A127" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C127" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" s="31" t="s">
         <v>147</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="1" t="s">
@@ -4849,100 +4853,100 @@
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8" ht="30.75">
-      <c r="A128" s="1">
-        <v>3</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C128" s="19" t="s">
+    <row r="128" spans="1:8" ht="15">
+      <c r="A128" s="9">
+        <v>15</v>
+      </c>
+      <c r="B128" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E128" s="4"/>
-      <c r="F128" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
-    </row>
-    <row r="129" spans="1:8" ht="30.75">
-      <c r="A129" s="1">
-        <v>4</v>
-      </c>
-      <c r="B129" s="19" t="s">
+      <c r="C128" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="D128" s="68"/>
+      <c r="E128" s="68"/>
+      <c r="F128" s="9"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="15"/>
+    </row>
+    <row r="129" spans="1:8" ht="15">
+      <c r="A129" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15">
+      <c r="A130" s="1">
+        <v>1</v>
+      </c>
+      <c r="B130" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C129" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E129" s="4"/>
-      <c r="F129" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-    </row>
-    <row r="130" spans="1:8" ht="15">
-      <c r="A130" s="9">
-        <v>15</v>
-      </c>
-      <c r="B130" s="10" t="s">
+      <c r="C130" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="4"/>
+      <c r="F130" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="20"/>
+      <c r="H130" s="20"/>
+    </row>
+    <row r="131" spans="1:8" ht="60.75">
+      <c r="A131" s="1">
+        <v>2</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C131" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="C130" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="D130" s="64"/>
-      <c r="E130" s="64"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="15"/>
-    </row>
-    <row r="131" spans="1:8" ht="15">
-      <c r="A131" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E131" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G131" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H131" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="D131" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="20"/>
+      <c r="H131" s="20"/>
     </row>
     <row r="132" spans="1:8" ht="15">
       <c r="A132" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="1" t="s">
@@ -4951,18 +4955,18 @@
       <c r="G132" s="20"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133" spans="1:8" ht="60.75">
+    <row r="133" spans="1:8" ht="15">
       <c r="A133" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C133" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C133" s="31" t="s">
         <v>152</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="1" t="s">
@@ -4971,18 +4975,18 @@
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8" ht="15">
+    <row r="134" spans="1:8" ht="60.75">
       <c r="A134" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C134" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="C134" s="31" t="s">
+        <v>154</v>
+      </c>
       <c r="D134" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="1" t="s">
@@ -4992,99 +4996,99 @@
       <c r="H134" s="20"/>
     </row>
     <row r="135" spans="1:8" ht="15">
-      <c r="A135" s="1">
-        <v>4</v>
-      </c>
-      <c r="B135" s="19" t="s">
+      <c r="A135" s="9">
+        <v>16</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C135" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="D135" s="60"/>
+      <c r="E135" s="60"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="14"/>
+      <c r="H135" s="15"/>
+    </row>
+    <row r="136" spans="1:8" ht="15">
+      <c r="A136" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G136" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="15">
+      <c r="A137" s="1">
+        <v>1</v>
+      </c>
+      <c r="B137" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C135" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E135" s="4"/>
-      <c r="F135" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G135" s="20"/>
-      <c r="H135" s="20"/>
-    </row>
-    <row r="136" spans="1:8" ht="60.75">
-      <c r="A136" s="1">
-        <v>5</v>
-      </c>
-      <c r="B136" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="C136" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E136" s="4"/>
-      <c r="F136" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
-    </row>
-    <row r="137" spans="1:8" ht="15">
-      <c r="A137" s="9">
-        <v>16</v>
-      </c>
-      <c r="B137" s="10" t="s">
+      <c r="C137" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="20"/>
+      <c r="H137" s="20"/>
+    </row>
+    <row r="138" spans="1:8" ht="76.5">
+      <c r="A138" s="1">
+        <v>2</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C138" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="C137" s="66" t="s">
+      <c r="D138" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G138" s="20"/>
+      <c r="H138" s="20"/>
+    </row>
+    <row r="139" spans="1:8" ht="106.5">
+      <c r="A139" s="1">
+        <v>3</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="D137" s="66"/>
-      <c r="E137" s="66"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="14"/>
-      <c r="H137" s="15"/>
-    </row>
-    <row r="138" spans="1:8" ht="15">
-      <c r="A138" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D138" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E138" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F138" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G138" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H138" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" ht="15">
-      <c r="A139" s="1">
-        <v>1</v>
-      </c>
-      <c r="B139" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="D139" s="1" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="1" t="s">
@@ -5095,16 +5099,16 @@
     </row>
     <row r="140" spans="1:8" ht="76.5">
       <c r="A140" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B140" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C140" s="57" t="s">
+      <c r="C140" s="31" t="s">
         <v>159</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="1" t="s">
@@ -5113,18 +5117,18 @@
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141" spans="1:8" ht="106.5">
+    <row r="141" spans="1:8" ht="60.75">
       <c r="A141" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B141" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C141" s="19" t="s">
+      <c r="C141" s="31" t="s">
         <v>160</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="1" t="s">
@@ -5135,7 +5139,7 @@
     </row>
     <row r="142" spans="1:8" ht="76.5">
       <c r="A142" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B142" s="19" t="s">
         <v>23</v>
@@ -5144,7 +5148,7 @@
         <v>161</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="1" t="s">
@@ -5153,128 +5157,90 @@
       <c r="G142" s="20"/>
       <c r="H142" s="20"/>
     </row>
-    <row r="143" spans="1:8" ht="60.75">
-      <c r="A143" s="1">
-        <v>5</v>
-      </c>
-      <c r="B143" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C143" s="31" t="s">
+    <row r="143" spans="1:8" ht="15">
+      <c r="A143" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E143" s="4"/>
-      <c r="F143" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
-    </row>
-    <row r="144" spans="1:8" ht="76.5">
-      <c r="A144" s="1">
+      <c r="B143" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C143" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D143" s="60"/>
+      <c r="E143" s="60"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="14"/>
+      <c r="H143" s="15"/>
+    </row>
+    <row r="144" spans="1:8" ht="15">
+      <c r="A144" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B144" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C144" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E144" s="4"/>
-      <c r="F144" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
-    </row>
-    <row r="145" spans="1:8" ht="15">
-      <c r="A145" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B145" s="10" t="s">
+      <c r="F144" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G144" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="76.5">
+      <c r="A145" s="1">
+        <v>1</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C145" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="C145" s="66" t="s">
+      <c r="D145" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D145" s="66"/>
-      <c r="E145" s="66"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="14"/>
-      <c r="H145" s="15"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="20"/>
+      <c r="H145" s="20"/>
     </row>
     <row r="146" spans="1:8" ht="15">
-      <c r="A146" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B146" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E146" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F146" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G146" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H146" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="76.5">
-      <c r="A147" s="1">
-        <v>1</v>
-      </c>
-      <c r="B147" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C147" s="57" t="s">
+      <c r="A146" s="1">
+        <v>2</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C146" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E147" s="4"/>
-      <c r="F147" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
-    </row>
-    <row r="148" spans="1:8" ht="15">
-      <c r="A148" s="1">
-        <v>2</v>
-      </c>
-      <c r="B148" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C148" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E148" s="4"/>
-      <c r="F148" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
-    </row>
+      <c r="E146" s="4"/>
+      <c r="F146" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="20"/>
+      <c r="H146" s="20"/>
+    </row>
+    <row r="147" spans="1:8" ht="15"/>
+    <row r="148" spans="1:8" ht="15"/>
     <row r="149" spans="1:8" ht="15"/>
     <row r="150" spans="1:8" ht="15"/>
     <row r="151" spans="1:8" ht="15"/>
@@ -5294,45 +5260,45 @@
     <row r="165" ht="15"/>
     <row r="166" ht="15"/>
     <row r="167" ht="15"/>
-    <row r="168" ht="15"/>
     <row r="169" ht="15"/>
     <row r="171" ht="15"/>
     <row r="173" ht="15"/>
+    <row r="174" ht="15"/>
     <row r="175" ht="15"/>
   </sheetData>
   <autoFilter ref="A3:H32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="28">
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="C124:E124"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C56:E56"/>
     <mergeCell ref="C45:E45"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C128:E128"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F80:F1048576 F3:F68">
+  <conditionalFormatting sqref="F1 F78:F1048576 F3:F66">
     <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5343,7 +5309,7 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F69:F74 F76 F78">
+  <conditionalFormatting sqref="F67:F72 F74 F76">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5355,7 +5321,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F26 F37:F38 F47:F57 F60:F68 F6:F14 F29:F30 F33:F34 F41:F44" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F26 F37:F38 F58:F66 F6:F14 F29:F30 F33:F34 F41:F44 F47:F55" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5379,7 +5345,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
       <c r="A1" s="76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -5391,10 +5357,10 @@
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5402,15 +5368,15 @@
         <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5418,7 +5384,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -5545,12 +5511,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5559,14 +5519,20 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
 </file>
--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29421"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD52902-7349-4483-A037-CECC8566A209}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB276564-659A-4753-A11E-5CF1E603B3A8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="171">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -295,36 +295,19 @@
     <t>Hans</t>
   </si>
   <si>
-    <t>17.01.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hans Ehm,Abdelgafar Ismail, Diallo Fadilatou, Excellence program Students,Marie Rahlmeyer</t>
-  </si>
-  <si>
-    <t>Adams: can you show next time your .xls – the Ball Mill being part of the overall farm                                                                                                          Very interesting point of view you made by looking at three impacts, it’s it would be interesting to conduct a SWOT analysis about the economic, societal and environmental impacts of the sustainable farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adjara: really interested on the time planning in .xls                                                                                                                                                                                     
-Nice to see the stages of the farm, could you perform a risk analysis of each stage e.g. during growing stage drought could be a risk, or floods …etc</t>
-  </si>
-  <si>
-    <t>Charles: really interested on your .xls file on the amount of irrigation – aligned with Charles and Alcia’s – earlier idea                                                                 automatic irrigation system is a very interesting idea, it would be interesting to conduct a SWOT analysis about automatic vs tradition irrigation systems</t>
-  </si>
-  <si>
-    <t>Lucas: really interested on your .xls file – what fruits do you want to grow, harvest and dry                                                                                      it is very interesting to see how simulation could help assess long term impact, it would be interesting to conduct a SWOT analysis about the long term impact of the sustainable farm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boris:really interested on your .xls and how it is connected with the irrigation, solar, fruit and irrigation                                                          Using Infineon sensors in the sustainable is a great idea, it would be interesting to conduct a SWOT analysis for smart sustainable farm which is using sensors from Infineon vs traditional sustainable farm which is not using smart solutions                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gertrude: really interested on the .xls, the size of the input: energy, water,… and the output: fruits, dried fruits, …. And needed resources for the scenario as discussed (and the column names linked to the classes in the individual and overall ontology)                                                           solar energy is an nice idea because it is clean energy, it would be interesting to conduct a SWOT analysis about the PV solar system  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilfried: really interested in the demonstrators and how they look                        I am glad that we have a lot of demonstrators we can show from the sustainable farm, could you list all demonstrators and what is the expected improvement from each one e.g. 10% water saving                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamado:   language is important I agree                                                     To make sure the farm is “sustainable” medium and long term planning is important, therefore excellent work you did Hamada, could you include a performance baseline to assess planned progress vs actual progress e.g. you plan in one year that the sustainable is up and running, but what happens in actual life                                                           
-</t>
+    <t>27.10.2025</t>
+  </si>
+  <si>
+    <t>Botho Schanze, Diallo Fadilatou, Excellence program Students,Hartinger Niklas Markus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General:  Good Presentation </t>
+  </si>
+  <si>
+    <t>Botho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel spreadsheets Feedback:  Botho will folllow up with Hans </t>
   </si>
   <si>
     <t>24/1/2025</t>
@@ -1398,6 +1381,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1422,28 +1423,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2338,16 +2321,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -2866,11 +2849,11 @@
       <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
@@ -2948,11 +2931,11 @@
       <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
@@ -3032,11 +3015,11 @@
       <c r="B35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
       <c r="F35" s="9"/>
       <c r="G35" s="14"/>
       <c r="H35" s="15"/>
@@ -3114,11 +3097,11 @@
       <c r="B39" s="10">
         <v>45943</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
       <c r="F39" s="9"/>
       <c r="G39" s="14"/>
       <c r="H39" s="15"/>
@@ -3236,11 +3219,11 @@
       <c r="B45" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
       <c r="F45" s="9"/>
       <c r="G45" s="14"/>
       <c r="H45" s="15"/>
@@ -3449,18 +3432,18 @@
       <c r="G55" s="20"/>
       <c r="H55" s="20"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" ht="15">
       <c r="A56" s="9">
         <v>8</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="68"/>
-      <c r="E56" s="68"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
       <c r="F56" s="9"/>
       <c r="G56" s="14"/>
       <c r="H56" s="15"/>
@@ -3511,7 +3494,7 @@
       <c r="G58" s="20"/>
       <c r="H58" s="20"/>
     </row>
-    <row r="59" spans="1:8" ht="72.599999999999994">
+    <row r="59" spans="1:8" ht="15">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -3522,7 +3505,7 @@
         <v>77</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="1" t="s">
@@ -3531,18 +3514,18 @@
       <c r="G59" s="20"/>
       <c r="H59" s="20"/>
     </row>
-    <row r="60" spans="1:8" ht="57.95">
+    <row r="60" spans="1:8" ht="15">
       <c r="A60" s="1">
         <v>3</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C60" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="1" t="s">
@@ -3551,366 +3534,370 @@
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
     </row>
-    <row r="61" spans="1:8" ht="76.5">
-      <c r="A61" s="1">
-        <v>4</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-    </row>
-    <row r="62" spans="1:8" ht="72.599999999999994">
-      <c r="A62" s="1">
-        <v>5</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="32" t="s">
+    <row r="61" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A61" s="33">
+        <v>9</v>
+      </c>
+      <c r="B61" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-    </row>
-    <row r="63" spans="1:8" ht="87">
-      <c r="A63" s="1">
+      <c r="C61" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" s="68"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="15"/>
+    </row>
+    <row r="62" spans="1:8" s="35" customFormat="1" ht="15.75">
+      <c r="A62" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="4"/>
+      <c r="F62" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="16.5">
+      <c r="A63" s="38">
+        <v>1</v>
+      </c>
+      <c r="B63" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="40"/>
       <c r="F63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64" spans="1:8" ht="87">
-      <c r="A64" s="1">
-        <v>7</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" s="31" t="s">
+    <row r="64" spans="1:8" ht="46.5">
+      <c r="A64" s="41">
+        <v>2</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E64" s="4"/>
+      <c r="E64" s="43"/>
       <c r="F64" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="57.95">
-      <c r="A65" s="1">
-        <v>8</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" s="31" t="s">
+    <row r="65" spans="1:8" ht="46.5">
+      <c r="A65" s="44"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="1"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66" spans="1:8" ht="106.5">
-      <c r="A66" s="1">
-        <v>9</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" s="31" t="s">
+    <row r="66" spans="1:8" ht="46.5">
+      <c r="A66" s="41">
+        <v>3</v>
+      </c>
+      <c r="B66" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E66" s="4"/>
-      <c r="F66" s="1"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="70" t="s">
+        <v>22</v>
+      </c>
       <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-    </row>
-    <row r="67" spans="1:8" s="35" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A67" s="33">
-        <v>9</v>
-      </c>
-      <c r="B67" s="34" t="s">
+      <c r="H66" s="72"/>
+    </row>
+    <row r="67" spans="1:8" ht="46.5">
+      <c r="A67" s="44"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="61" t="s">
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="73"/>
+    </row>
+    <row r="68" spans="1:8" ht="30.75">
+      <c r="A68" s="41">
+        <v>4</v>
+      </c>
+      <c r="B68" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D67" s="62"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="15"/>
-    </row>
-    <row r="68" spans="1:8" s="35" customFormat="1" ht="15.75">
-      <c r="A68" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B68" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="16.5">
-      <c r="A69" s="38">
-        <v>1</v>
-      </c>
-      <c r="B69" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D69" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="40"/>
-      <c r="F69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-    </row>
-    <row r="70" spans="1:8" ht="46.5">
+      <c r="D68" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="43"/>
+      <c r="F68" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="72"/>
+      <c r="H68" s="72"/>
+    </row>
+    <row r="69" spans="1:8" ht="61.5">
+      <c r="A69" s="44"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="73"/>
+      <c r="H69" s="73"/>
+    </row>
+    <row r="70" spans="1:8" ht="30.75">
       <c r="A70" s="41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B70" s="42" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D70" s="42" t="s">
         <v>25</v>
       </c>
       <c r="E70" s="43"/>
-      <c r="F70" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-    </row>
-    <row r="71" spans="1:8" ht="46.5">
+      <c r="F70" s="70"/>
+      <c r="G70" s="72"/>
+      <c r="H70" s="72"/>
+    </row>
+    <row r="71" spans="1:8" ht="30.75">
       <c r="A71" s="44"/>
       <c r="B71" s="45"/>
       <c r="C71" s="46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D71" s="45"/>
       <c r="E71" s="45"/>
-      <c r="F71" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-    </row>
-    <row r="72" spans="1:8" ht="46.5">
-      <c r="A72" s="41">
+      <c r="F71" s="71"/>
+      <c r="G71" s="73"/>
+      <c r="H71" s="73"/>
+    </row>
+    <row r="72" spans="1:8" ht="15">
+      <c r="A72" s="9">
+        <v>10</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D72" s="64"/>
+      <c r="E72" s="64"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="15"/>
+    </row>
+    <row r="73" spans="1:8" ht="15">
+      <c r="A73" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15">
+      <c r="A74" s="1">
+        <v>1</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+    </row>
+    <row r="75" spans="1:8" ht="60.75">
+      <c r="A75" s="1">
+        <v>2</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+    </row>
+    <row r="76" spans="1:8" ht="30.75">
+      <c r="A76" s="1">
         <v>3</v>
       </c>
-      <c r="B72" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="D72" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="43"/>
-      <c r="F72" s="64" t="s">
-        <v>22</v>
-      </c>
-      <c r="G72" s="20"/>
-      <c r="H72" s="66"/>
-    </row>
-    <row r="73" spans="1:8" ht="46.5">
-      <c r="A73" s="44"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="65"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="67"/>
-    </row>
-    <row r="74" spans="1:8" ht="30.75">
-      <c r="A74" s="41">
+      <c r="B76" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+    </row>
+    <row r="77" spans="1:8" ht="76.5">
+      <c r="A77" s="1">
         <v>4</v>
       </c>
-      <c r="B74" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D74" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="43"/>
-      <c r="F74" s="64" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="66"/>
-      <c r="H74" s="66"/>
-    </row>
-    <row r="75" spans="1:8" ht="61.5">
-      <c r="A75" s="44"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="65"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-    </row>
-    <row r="76" spans="1:8" ht="30.75">
-      <c r="A76" s="41">
+      <c r="B77" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+    </row>
+    <row r="78" spans="1:8" ht="76.5">
+      <c r="A78" s="1">
         <v>5</v>
       </c>
-      <c r="B76" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="D76" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="43"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="66"/>
-      <c r="H76" s="66"/>
-    </row>
-    <row r="77" spans="1:8" ht="30.75">
-      <c r="A77" s="44"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-      <c r="F77" s="65"/>
-      <c r="G77" s="67"/>
-      <c r="H77" s="67"/>
-    </row>
-    <row r="78" spans="1:8" ht="15">
-      <c r="A78" s="9">
-        <v>10</v>
-      </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="C78" s="68" t="s">
+      <c r="D78" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+    </row>
+    <row r="79" spans="1:8" ht="45.75">
+      <c r="A79" s="1">
+        <v>6</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="15"/>
-    </row>
-    <row r="79" spans="1:8" ht="15">
-      <c r="A79" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" s="12" t="s">
+      <c r="D79" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+    </row>
+    <row r="80" spans="1:8" ht="76.5">
+      <c r="A80" s="1">
         <v>7</v>
       </c>
-      <c r="G79" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H79" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="15">
-      <c r="A80" s="1">
-        <v>1</v>
-      </c>
       <c r="B80" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>97</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="1" t="s">
@@ -3919,237 +3906,241 @@
       <c r="G80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81" spans="1:8" ht="60.75">
+    <row r="81" spans="1:8" ht="91.5">
       <c r="A81" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>97</v>
+      <c r="C81" s="31" t="s">
+        <v>98</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E81" s="4"/>
-      <c r="F81" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F81" s="1"/>
       <c r="G81" s="20"/>
       <c r="H81" s="20"/>
     </row>
-    <row r="82" spans="1:8" ht="30.75">
+    <row r="82" spans="1:8" ht="60.75">
       <c r="A82" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C82" s="19" t="s">
-        <v>98</v>
+      <c r="C82" s="31" t="s">
+        <v>99</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E82" s="4"/>
-      <c r="F82" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F82" s="1"/>
       <c r="G82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" ht="76.5">
+    <row r="83" spans="1:8" ht="15">
       <c r="A83" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E83" s="4"/>
-      <c r="F83" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-    </row>
-    <row r="84" spans="1:8" ht="76.5">
-      <c r="A84" s="1">
-        <v>5</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C84" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E84" s="4"/>
-      <c r="F84" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-    </row>
-    <row r="85" spans="1:8" ht="45.75">
-      <c r="A85" s="1">
+      <c r="F83" s="1"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="49"/>
+    </row>
+    <row r="84" spans="1:8" ht="15" customHeight="1">
+      <c r="A84" s="50">
+        <v>11</v>
+      </c>
+      <c r="B84" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C84" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" s="74"/>
+      <c r="E84" s="75"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="15"/>
+    </row>
+    <row r="85" spans="1:8" ht="15">
+      <c r="A85" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C85" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E85" s="4"/>
-      <c r="F85" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-    </row>
-    <row r="86" spans="1:8" ht="76.5">
-      <c r="A86" s="1">
+      <c r="F85" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B86" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C86" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E86" s="4"/>
+      <c r="G85" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15">
+      <c r="A86" s="54">
+        <v>1</v>
+      </c>
+      <c r="B86" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="55" t="s">
+        <v>103</v>
+      </c>
       <c r="F86" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G86" s="20"/>
       <c r="H86" s="20"/>
     </row>
-    <row r="87" spans="1:8" ht="91.5">
-      <c r="A87" s="1">
-        <v>8</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" s="31" t="s">
+    <row r="87" spans="1:8" ht="15">
+      <c r="A87" s="60">
+        <v>2</v>
+      </c>
+      <c r="B87" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D87" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="E87" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E87" s="4"/>
-      <c r="F87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G87" s="20"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88" spans="1:8" ht="60.75">
-      <c r="A88" s="1">
-        <v>9</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E88" s="4"/>
-      <c r="F88" s="1"/>
+    <row r="88" spans="1:8" ht="15">
+      <c r="A88" s="61"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="D88" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E88" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G88" s="20"/>
       <c r="H88" s="20"/>
     </row>
     <row r="89" spans="1:8" ht="15">
-      <c r="A89" s="1">
-        <v>10</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E89" s="4"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="48"/>
-      <c r="H89" s="49"/>
-    </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1">
-      <c r="A90" s="50">
-        <v>11</v>
-      </c>
-      <c r="B90" s="51" t="s">
+      <c r="A89" s="56">
+        <v>3</v>
+      </c>
+      <c r="B89" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D89" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="C90" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="D90" s="69"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="15"/>
+      <c r="E89" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+    </row>
+    <row r="90" spans="1:8" ht="30.75">
+      <c r="A90" s="56">
+        <v>4</v>
+      </c>
+      <c r="B90" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="E90" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
     </row>
     <row r="91" spans="1:8" ht="15">
-      <c r="A91" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B91" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G91" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="A91" s="60">
+        <v>5</v>
+      </c>
+      <c r="B91" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="C91" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D91" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="E91" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
     </row>
     <row r="92" spans="1:8" ht="15">
-      <c r="A92" s="54">
-        <v>1</v>
-      </c>
-      <c r="B92" s="55" t="s">
-        <v>18</v>
-      </c>
+      <c r="A92" s="60"/>
+      <c r="B92" s="62"/>
       <c r="C92" s="55" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="D92" s="55" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="E92" s="55" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>22</v>
@@ -4158,215 +4149,211 @@
       <c r="H92" s="20"/>
     </row>
     <row r="93" spans="1:8" ht="15">
-      <c r="A93" s="72">
-        <v>2</v>
-      </c>
-      <c r="B93" s="74" t="s">
-        <v>109</v>
-      </c>
+      <c r="A93" s="60"/>
+      <c r="B93" s="62"/>
       <c r="C93" s="55" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D93" s="55" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E93" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="F93" s="1"/>
       <c r="G93" s="20"/>
       <c r="H93" s="20"/>
     </row>
     <row r="94" spans="1:8" ht="15">
-      <c r="A94" s="73"/>
-      <c r="B94" s="75"/>
+      <c r="A94" s="61"/>
+      <c r="B94" s="63"/>
       <c r="C94" s="55" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E94" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="F94" s="1"/>
       <c r="G94" s="20"/>
       <c r="H94" s="20"/>
     </row>
     <row r="95" spans="1:8" ht="15">
-      <c r="A95" s="56">
-        <v>3</v>
-      </c>
-      <c r="B95" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="C95" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D95" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E95" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
-    </row>
-    <row r="96" spans="1:8" ht="30.75">
-      <c r="A96" s="56">
-        <v>4</v>
-      </c>
-      <c r="B96" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="C96" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E96" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G96" s="20"/>
-      <c r="H96" s="20"/>
+      <c r="A95" s="9">
+        <v>12</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C95" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D95" s="64"/>
+      <c r="E95" s="64"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="15"/>
+    </row>
+    <row r="96" spans="1:8" ht="15">
+      <c r="A96" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="97" spans="1:8" ht="15">
-      <c r="A97" s="72">
-        <v>5</v>
-      </c>
-      <c r="B97" s="74" t="s">
-        <v>117</v>
-      </c>
-      <c r="C97" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E97" s="55" t="s">
-        <v>108</v>
-      </c>
+      <c r="A97" s="1">
+        <v>1</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="4"/>
       <c r="F97" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G97" s="20"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98" spans="1:8" ht="15">
-      <c r="A98" s="72"/>
-      <c r="B98" s="74"/>
-      <c r="C98" s="55" t="s">
+    <row r="98" spans="1:8" ht="121.5">
+      <c r="A98" s="1">
+        <v>2</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="D98" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E98" s="55" t="s">
-        <v>108</v>
-      </c>
+      <c r="D98" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E98" s="4"/>
       <c r="F98" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G98" s="20"/>
       <c r="H98" s="20"/>
     </row>
-    <row r="99" spans="1:8" ht="15">
-      <c r="A99" s="72"/>
-      <c r="B99" s="74"/>
-      <c r="C99" s="55" t="s">
+    <row r="99" spans="1:8" ht="106.5">
+      <c r="A99" s="1">
+        <v>3</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D99" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E99" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F99" s="1"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
     </row>
-    <row r="100" spans="1:8" ht="15">
-      <c r="A100" s="73"/>
-      <c r="B100" s="75"/>
-      <c r="C100" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="D100" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E100" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F100" s="1"/>
+    <row r="100" spans="1:8" ht="152.25">
+      <c r="A100" s="1">
+        <v>4</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G100" s="20"/>
       <c r="H100" s="20"/>
     </row>
-    <row r="101" spans="1:8" ht="15">
-      <c r="A101" s="9">
-        <v>12</v>
-      </c>
-      <c r="B101" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C101" s="68" t="s">
+    <row r="101" spans="1:8" ht="152.25">
+      <c r="A101" s="1">
+        <v>5</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="D101" s="68"/>
-      <c r="E101" s="68"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="15"/>
-    </row>
-    <row r="102" spans="1:8" ht="15">
-      <c r="A102" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E102" s="12" t="s">
+      <c r="D101" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="20"/>
+      <c r="H101" s="20"/>
+    </row>
+    <row r="102" spans="1:8" ht="152.25">
+      <c r="A102" s="1">
         <v>6</v>
       </c>
-      <c r="F102" s="12" t="s">
+      <c r="B102" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="20"/>
+      <c r="H102" s="20"/>
+    </row>
+    <row r="103" spans="1:8" ht="152.25">
+      <c r="A103" s="1">
         <v>7</v>
       </c>
-      <c r="G102" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H102" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="15">
-      <c r="A103" s="1">
-        <v>1</v>
-      </c>
       <c r="B103" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C103" s="31" t="s">
+        <v>125</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="1" t="s">
@@ -4375,98 +4362,96 @@
       <c r="G103" s="20"/>
       <c r="H103" s="20"/>
     </row>
-    <row r="104" spans="1:8" ht="121.5">
+    <row r="104" spans="1:8" ht="137.25">
       <c r="A104" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B104" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C104" s="57" t="s">
-        <v>124</v>
+      <c r="C104" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E104" s="4"/>
-      <c r="F104" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F104" s="1"/>
       <c r="G104" s="20"/>
       <c r="H104" s="20"/>
     </row>
-    <row r="105" spans="1:8" ht="106.5">
+    <row r="105" spans="1:8" ht="30.75">
       <c r="A105" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B105" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C105" s="19" t="s">
-        <v>126</v>
+      <c r="C105" s="31" t="s">
+        <v>127</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="E105" s="4"/>
-      <c r="F105" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G105" s="20"/>
-      <c r="H105" s="20"/>
-    </row>
-    <row r="106" spans="1:8" ht="152.25">
-      <c r="A106" s="1">
-        <v>4</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C106" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E106" s="4"/>
-      <c r="F106" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G106" s="20"/>
-      <c r="H106" s="20"/>
-    </row>
-    <row r="107" spans="1:8" ht="152.25">
-      <c r="A107" s="1">
-        <v>5</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C107" s="47" t="s">
+      <c r="F105" s="1"/>
+      <c r="G105" s="48"/>
+      <c r="H105" s="49"/>
+    </row>
+    <row r="106" spans="1:8" ht="15">
+      <c r="A106" s="9">
+        <v>13</v>
+      </c>
+      <c r="B106" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E107" s="4"/>
-      <c r="F107" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-    </row>
-    <row r="108" spans="1:8" ht="152.25">
+      <c r="C106" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="D106" s="64"/>
+      <c r="E106" s="64"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="15"/>
+    </row>
+    <row r="107" spans="1:8" ht="15">
+      <c r="A107" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15">
       <c r="A108" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C108" s="58" t="s">
-        <v>129</v>
+        <v>18</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="1" t="s">
@@ -4475,18 +4460,18 @@
       <c r="G108" s="20"/>
       <c r="H108" s="20"/>
     </row>
-    <row r="109" spans="1:8" ht="152.25">
+    <row r="109" spans="1:8" ht="60.75">
       <c r="A109" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="31" t="s">
+      <c r="C109" s="57" t="s">
         <v>130</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="1" t="s">
@@ -4495,96 +4480,98 @@
       <c r="G109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110" spans="1:8" ht="137.25">
+    <row r="110" spans="1:8" ht="60.75">
       <c r="A110" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B110" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="31" t="s">
+      <c r="C110" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="E110" s="4"/>
-      <c r="F110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G110" s="20"/>
       <c r="H110" s="20"/>
     </row>
     <row r="111" spans="1:8" ht="30.75">
       <c r="A111" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C111" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="E111" s="4"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="48"/>
-      <c r="H111" s="49"/>
-    </row>
-    <row r="112" spans="1:8" ht="15">
-      <c r="A112" s="9">
-        <v>13</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C112" s="68" t="s">
+      <c r="F111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="20"/>
+      <c r="H111" s="20"/>
+    </row>
+    <row r="112" spans="1:8" ht="76.5">
+      <c r="A112" s="1">
+        <v>5</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C112" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="D112" s="68"/>
-      <c r="E112" s="68"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="14"/>
-      <c r="H112" s="15"/>
-    </row>
-    <row r="113" spans="1:8" ht="15">
-      <c r="A113" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D113" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E113" s="12" t="s">
+      <c r="D112" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E112" s="4"/>
+      <c r="F112" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="20"/>
+      <c r="H112" s="20"/>
+    </row>
+    <row r="113" spans="1:8" ht="60.75">
+      <c r="A113" s="1">
         <v>6</v>
       </c>
-      <c r="F113" s="12" t="s">
+      <c r="B113" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E113" s="4"/>
+      <c r="F113" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
+    </row>
+    <row r="114" spans="1:8" ht="76.5">
+      <c r="A114" s="1">
         <v>7</v>
       </c>
-      <c r="G113" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="15">
-      <c r="A114" s="1">
-        <v>1</v>
-      </c>
       <c r="B114" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C114" s="31" t="s">
+        <v>136</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="1" t="s">
@@ -4595,76 +4582,76 @@
     </row>
     <row r="115" spans="1:8" ht="60.75">
       <c r="A115" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B115" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C115" s="57" t="s">
-        <v>135</v>
+      <c r="C115" s="31" t="s">
+        <v>137</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E115" s="4"/>
-      <c r="F115" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F115" s="1"/>
       <c r="G115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116" spans="1:8" ht="60.75">
-      <c r="A116" s="1">
-        <v>3</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E116" s="4"/>
-      <c r="F116" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
-    </row>
-    <row r="117" spans="1:8" ht="30.75">
-      <c r="A117" s="1">
-        <v>4</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C117" s="31" t="s">
+    <row r="116" spans="1:8" ht="15">
+      <c r="A116" s="9">
+        <v>14</v>
+      </c>
+      <c r="B116" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E117" s="4"/>
-      <c r="F117" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-    </row>
-    <row r="118" spans="1:8" ht="76.5">
+      <c r="C116" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="D116" s="64"/>
+      <c r="E116" s="64"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="15"/>
+    </row>
+    <row r="117" spans="1:8" ht="15">
+      <c r="A117" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H117" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="15">
       <c r="A118" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C118" s="47" t="s">
-        <v>139</v>
+        <v>18</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="1" t="s">
@@ -4673,18 +4660,18 @@
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119" spans="1:8" ht="60.75">
+    <row r="119" spans="1:8" ht="15">
       <c r="A119" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B119" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C119" s="58" t="s">
+      <c r="C119" s="57" t="s">
         <v>140</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="1" t="s">
@@ -4693,18 +4680,18 @@
       <c r="G119" s="20"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120" spans="1:8" ht="76.5">
+    <row r="120" spans="1:8" ht="30.75">
       <c r="A120" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B120" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C120" s="31" t="s">
+      <c r="C120" s="19" t="s">
         <v>141</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="1" t="s">
@@ -4713,36 +4700,38 @@
       <c r="G120" s="20"/>
       <c r="H120" s="20"/>
     </row>
-    <row r="121" spans="1:8" ht="60.75">
+    <row r="121" spans="1:8" ht="30.75">
       <c r="A121" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C121" s="31" t="s">
         <v>142</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E121" s="4"/>
-      <c r="F121" s="1"/>
+      <c r="F121" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G121" s="20"/>
       <c r="H121" s="20"/>
     </row>
     <row r="122" spans="1:8" ht="15">
       <c r="A122" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C122" s="68" t="s">
+      <c r="C122" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="D122" s="68"/>
-      <c r="E122" s="68"/>
+      <c r="D122" s="64"/>
+      <c r="E122" s="64"/>
       <c r="F122" s="9"/>
       <c r="G122" s="14"/>
       <c r="H122" s="15"/>
@@ -4793,7 +4782,7 @@
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125" spans="1:8" ht="15">
+    <row r="125" spans="1:8" ht="60.75">
       <c r="A125" s="1">
         <v>2</v>
       </c>
@@ -4813,12 +4802,12 @@
       <c r="G125" s="20"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126" spans="1:8" ht="30.75">
+    <row r="126" spans="1:8" ht="15">
       <c r="A126" s="1">
         <v>3</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C126" s="19" t="s">
         <v>146</v>
@@ -4833,7 +4822,7 @@
       <c r="G126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8" ht="30.75">
+    <row r="127" spans="1:8" ht="15">
       <c r="A127" s="1">
         <v>4</v>
       </c>
@@ -4853,80 +4842,80 @@
       <c r="G127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8" ht="15">
-      <c r="A128" s="9">
+    <row r="128" spans="1:8" ht="60.75">
+      <c r="A128" s="1">
+        <v>5</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="20"/>
+      <c r="H128" s="20"/>
+    </row>
+    <row r="129" spans="1:8" ht="15">
+      <c r="A129" s="9">
+        <v>16</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C129" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D129" s="66"/>
+      <c r="E129" s="66"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="14"/>
+      <c r="H129" s="15"/>
+    </row>
+    <row r="130" spans="1:8" ht="15">
+      <c r="A130" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B128" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C128" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="D128" s="68"/>
-      <c r="E128" s="68"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="14"/>
-      <c r="H128" s="15"/>
-    </row>
-    <row r="129" spans="1:8" ht="15">
-      <c r="A129" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B129" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C129" s="11" t="s">
+      <c r="C130" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D130" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E129" s="12" t="s">
+      <c r="E130" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F129" s="12" t="s">
+      <c r="F130" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G129" s="12" t="s">
+      <c r="G130" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H129" s="11" t="s">
+      <c r="H130" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15">
-      <c r="A130" s="1">
+    <row r="131" spans="1:8" ht="15">
+      <c r="A131" s="1">
         <v>1</v>
       </c>
-      <c r="B130" s="19" t="s">
+      <c r="B131" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C130" s="19" t="s">
+      <c r="C131" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E130" s="4"/>
-      <c r="F130" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G130" s="20"/>
-      <c r="H130" s="20"/>
-    </row>
-    <row r="131" spans="1:8" ht="60.75">
-      <c r="A131" s="1">
-        <v>2</v>
-      </c>
-      <c r="B131" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C131" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="1" t="s">
@@ -4935,15 +4924,15 @@
       <c r="G131" s="20"/>
       <c r="H131" s="20"/>
     </row>
-    <row r="132" spans="1:8" ht="15">
+    <row r="132" spans="1:8" ht="76.5">
       <c r="A132" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C132" s="19" t="s">
-        <v>151</v>
+        <v>23</v>
+      </c>
+      <c r="C132" s="57" t="s">
+        <v>152</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>74</v>
@@ -4955,15 +4944,15 @@
       <c r="G132" s="20"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133" spans="1:8" ht="15">
+    <row r="133" spans="1:8" ht="106.5">
       <c r="A133" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C133" s="31" t="s">
-        <v>152</v>
+        <v>23</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>153</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>74</v>
@@ -4975,12 +4964,12 @@
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8" ht="60.75">
+    <row r="134" spans="1:8" ht="76.5">
       <c r="A134" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="C134" s="31" t="s">
         <v>154</v>
@@ -4995,100 +4984,100 @@
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135" spans="1:8" ht="15">
-      <c r="A135" s="9">
+    <row r="135" spans="1:8" ht="60.75">
+      <c r="A135" s="1">
+        <v>5</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135" s="20"/>
+      <c r="H135" s="20"/>
+    </row>
+    <row r="136" spans="1:8" ht="76.5">
+      <c r="A136" s="1">
+        <v>6</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136" s="20"/>
+      <c r="H136" s="20"/>
+    </row>
+    <row r="137" spans="1:8" ht="15">
+      <c r="A137" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C137" s="66" t="s">
+        <v>159</v>
+      </c>
+      <c r="D137" s="66"/>
+      <c r="E137" s="66"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="15"/>
+    </row>
+    <row r="138" spans="1:8" ht="15">
+      <c r="A138" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B135" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C135" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="D135" s="60"/>
-      <c r="E135" s="60"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="15"/>
-    </row>
-    <row r="136" spans="1:8" ht="15">
-      <c r="A136" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C136" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D136" s="12" t="s">
+      <c r="D138" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E136" s="12" t="s">
+      <c r="E138" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F136" s="12" t="s">
+      <c r="F138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G136" s="12" t="s">
+      <c r="G138" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H136" s="11" t="s">
+      <c r="H138" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15">
-      <c r="A137" s="1">
+    <row r="139" spans="1:8" ht="76.5">
+      <c r="A139" s="1">
         <v>1</v>
       </c>
-      <c r="B137" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C137" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E137" s="4"/>
-      <c r="F137" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G137" s="20"/>
-      <c r="H137" s="20"/>
-    </row>
-    <row r="138" spans="1:8" ht="76.5">
-      <c r="A138" s="1">
-        <v>2</v>
-      </c>
-      <c r="B138" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C138" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E138" s="4"/>
-      <c r="F138" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G138" s="20"/>
-      <c r="H138" s="20"/>
-    </row>
-    <row r="139" spans="1:8" ht="106.5">
-      <c r="A139" s="1">
-        <v>3</v>
-      </c>
       <c r="B139" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C139" s="19" t="s">
-        <v>158</v>
+      <c r="C139" s="57" t="s">
+        <v>160</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="1" t="s">
@@ -5097,18 +5086,18 @@
       <c r="G139" s="20"/>
       <c r="H139" s="20"/>
     </row>
-    <row r="140" spans="1:8" ht="76.5">
+    <row r="140" spans="1:8" ht="15">
       <c r="A140" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B140" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C140" s="31" t="s">
-        <v>159</v>
+      <c r="C140" s="19" t="s">
+        <v>162</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="1" t="s">
@@ -5117,162 +5106,57 @@
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141" spans="1:8" ht="60.75">
-      <c r="A141" s="1">
-        <v>5</v>
-      </c>
-      <c r="B141" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C141" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E141" s="4"/>
-      <c r="F141" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
-    </row>
-    <row r="142" spans="1:8" ht="76.5">
-      <c r="A142" s="1">
-        <v>6</v>
-      </c>
-      <c r="B142" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C142" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E142" s="4"/>
-      <c r="F142" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G142" s="20"/>
-      <c r="H142" s="20"/>
-    </row>
-    <row r="143" spans="1:8" ht="15">
-      <c r="A143" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B143" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C143" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="D143" s="60"/>
-      <c r="E143" s="60"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="14"/>
-      <c r="H143" s="15"/>
-    </row>
-    <row r="144" spans="1:8" ht="15">
-      <c r="A144" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B144" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D144" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E144" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F144" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G144" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H144" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="76.5">
-      <c r="A145" s="1">
-        <v>1</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C145" s="57" t="s">
-        <v>165</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E145" s="4"/>
-      <c r="F145" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
-    </row>
-    <row r="146" spans="1:8" ht="15">
-      <c r="A146" s="1">
-        <v>2</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E146" s="4"/>
-      <c r="F146" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
-    </row>
-    <row r="147" spans="1:8" ht="15"/>
-    <row r="148" spans="1:8" ht="15"/>
-    <row r="149" spans="1:8" ht="15"/>
-    <row r="150" spans="1:8" ht="15"/>
-    <row r="151" spans="1:8" ht="15"/>
-    <row r="152" spans="1:8" ht="15"/>
-    <row r="153" spans="1:8" ht="15"/>
-    <row r="154" spans="1:8" ht="15"/>
-    <row r="155" spans="1:8" ht="15"/>
-    <row r="156" spans="1:8" ht="15"/>
-    <row r="157" spans="1:8" ht="15"/>
-    <row r="158" spans="1:8" ht="15"/>
-    <row r="159" spans="1:8" ht="15"/>
-    <row r="160" spans="1:8" ht="15"/>
+    <row r="141" spans="1:8" ht="15"/>
+    <row r="142" spans="1:8" ht="15"/>
+    <row r="143" spans="1:8" ht="15"/>
+    <row r="144" spans="1:8" ht="15"/>
+    <row r="145" ht="15"/>
+    <row r="146" ht="15"/>
+    <row r="147" ht="15"/>
+    <row r="148" ht="15"/>
+    <row r="149" ht="15"/>
+    <row r="150" ht="15"/>
+    <row r="151" ht="15"/>
+    <row r="152" ht="15"/>
+    <row r="153" ht="15"/>
+    <row r="154" ht="15"/>
+    <row r="155" ht="15"/>
+    <row r="156" ht="15"/>
+    <row r="157" ht="15"/>
+    <row r="158" ht="15"/>
+    <row r="159" ht="15"/>
+    <row r="160" ht="15"/>
     <row r="161" ht="15"/>
-    <row r="162" ht="15"/>
     <row r="163" ht="15"/>
-    <row r="164" ht="15"/>
     <row r="165" ht="15"/>
-    <row r="166" ht="15"/>
     <row r="167" ht="15"/>
+    <row r="168" ht="15"/>
     <row r="169" ht="15"/>
+    <row r="170" ht="15"/>
     <row r="171" ht="15"/>
+    <row r="172" ht="15"/>
     <row r="173" ht="15"/>
     <row r="174" ht="15"/>
     <row r="175" ht="15"/>
   </sheetData>
   <autoFilter ref="A3:H32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="28">
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C122:E122"/>
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="C45:E45"/>
     <mergeCell ref="C27:E27"/>
@@ -5280,25 +5164,14 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="C95:E95"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F78:F1048576 F3:F66">
+  <conditionalFormatting sqref="F1 F72:F1048576 F3:F60">
     <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5309,7 +5182,7 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F67:F72 F74 F76">
+  <conditionalFormatting sqref="F61:F66 F68 F70">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
@@ -5321,7 +5194,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F26 F37:F38 F58:F66 F6:F14 F29:F30 F33:F34 F41:F44 F47:F55" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F26 F37:F38 F6:F14 F29:F30 F33:F34 F41:F44 F47:F55 F58:F60" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5345,7 +5218,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
       <c r="A1" s="76" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -5357,10 +5230,10 @@
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5368,15 +5241,15 @@
         <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5384,7 +5257,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -5511,6 +5384,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5519,20 +5398,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
--- a/MoM_Excellence_program2025.xlsx
+++ b/MoM_Excellence_program2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbceec1c4b8718ad/Documents/GitHub/Excellence-Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB276564-659A-4753-A11E-5CF1E603B3A8}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="13_ncr:1_{22FD50FF-7022-42AF-BDFC-94CFFD8376F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E85A37E-579D-401D-866D-02A86BA8015D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="171">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -295,7 +295,7 @@
     <t>Hans</t>
   </si>
   <si>
-    <t>27.10.2025</t>
+    <t>24.10.2025</t>
   </si>
   <si>
     <t>Botho Schanze, Diallo Fadilatou, Excellence program Students,Hartinger Niklas Markus</t>
@@ -310,35 +310,37 @@
     <t xml:space="preserve">Excel spreadsheets Feedback:  Botho will folllow up with Hans </t>
   </si>
   <si>
-    <t>24/1/2025</t>
-  </si>
-  <si>
-    <t>Hans Ehm,Abdelgafar Ismail, Diallo Fadilatou, Excellence program Students, Seah Qiao Ling, JamesDevassia Cherupillet,</t>
-  </si>
-  <si>
-    <t>Adams:SWOT analysis is fine, but we also need to think how the Ball Mill is making money on the  farm; show the ball mill next Friday there will be time </t>
-  </si>
-  <si>
-    <t> - Very good to develop a SWOT, one suggestion is to look at the weakness and threats and try to think of mitigation measures</t>
-  </si>
-  <si>
-    <t>Adjara: I think you should play for 3 minutes the favorite music in the break out session and for one minute in the general assembly later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- Very good analysis of risks, could you think of risk mitigations</t>
-  </si>
-  <si>
-    <t>Wilfried: really interested in the demonstrators and how they look - Very good benefits analysis from demonstrators</t>
-  </si>
-  <si>
-    <t> – is it possible to think of alternative analysis to increase the benefits e.g. say current yield expected is 80%, if we add fertilization we could increase yield by 10% but could would increase by say 2% or 3%</t>
-  </si>
-  <si>
-    <t>Hamado: I need to look in detail at your .xls file. I think you should start with the overall picture in the creative hour </t>
-  </si>
-  <si>
-    <t> - Excellent presentation – is it ok to widen your planned vs schedule to scope, schedule and cost</t>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>Hans Ehm,Diallo Fadilatou, Excellence program Students, Vanessa Bleil, Isabella Lippert, Gertrude Bazongo, Wilfried Yameogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mare Zalka: add some citation where the data comes from; depreciate land by 30 years and machinery by 5 years. 
+Bring all to cost per year for a 2 ha and cost per Mango. </t>
+  </si>
+  <si>
+    <t>Arcus: Distance better 8 instead of 8*8 .</t>
+  </si>
+  <si>
+    <t>Ange Marie: In cells strictly distinguish between numbers and non number cells, where you have numbers don't do a range. 
+If you want to have alternatives use two lines. Better do not mix explanation into the .xls use ppt for that.</t>
+  </si>
+  <si>
+    <t>Cedric: Change all to 2ha.</t>
+  </si>
+  <si>
+    <t>Narcisse: Separate the value from the unit; if you have in the headline %total you  do not need 46% but just 46.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afia: Business Model canvas is good - But this should be in the ppt, not in the .xls.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yannick: Do not leave column A and B empty start at the left.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All: use Paramter, Metric, value and comment. Have the data to left and best no empty cells in between use a frts base; 
+use always the same naming  data sheet with 2 has the exchange rate the crop = Mango etc.; all use the same font and size and do not merge cells - it makes it diffcult for calculating.  </t>
   </si>
   <si>
     <t>07.02.2025</t>
@@ -813,7 +815,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -959,36 +961,6 @@
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1007,45 +979,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -1055,19 +988,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1203,12 +1123,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1313,161 +1244,121 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color auto="1"/>
@@ -2309,7 +2200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="5" customWidth="1"/>
@@ -2321,16 +2212,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1">
       <c r="A2" s="6"/>
@@ -2849,11 +2740,11 @@
       <c r="B27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
@@ -2931,11 +2822,11 @@
       <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="64" t="s">
+      <c r="C31" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
@@ -3003,7 +2894,7 @@
       <c r="F34" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="59" t="s">
+      <c r="G34" s="48" t="s">
         <v>55</v>
       </c>
       <c r="H34" s="20"/>
@@ -3015,11 +2906,11 @@
       <c r="B35" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
       <c r="F35" s="9"/>
       <c r="G35" s="14"/>
       <c r="H35" s="15"/>
@@ -3097,11 +2988,11 @@
       <c r="B39" s="10">
         <v>45943</v>
       </c>
-      <c r="C39" s="64" t="s">
+      <c r="C39" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
       <c r="F39" s="9"/>
       <c r="G39" s="14"/>
       <c r="H39" s="15"/>
@@ -3219,11 +3110,11 @@
       <c r="B45" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
       <c r="F45" s="9"/>
       <c r="G45" s="14"/>
       <c r="H45" s="15"/>
@@ -3439,11 +3330,11 @@
       <c r="B56" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="64" t="s">
+      <c r="C56" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
       <c r="F56" s="9"/>
       <c r="G56" s="14"/>
       <c r="H56" s="15"/>
@@ -3541,29 +3432,29 @@
       <c r="B61" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="67" t="s">
+      <c r="C61" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="68"/>
-      <c r="E61" s="69"/>
+      <c r="D61" s="52"/>
+      <c r="E61" s="53"/>
       <c r="F61" s="9"/>
       <c r="G61" s="14"/>
       <c r="H61" s="15"/>
     </row>
     <row r="62" spans="1:8" s="35" customFormat="1" ht="15.75">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="37" t="s">
+      <c r="B62" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="D62" s="37" t="s">
+      <c r="D62" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="E62" s="37" t="s">
+      <c r="E62" s="69" t="s">
         <v>6</v>
       </c>
       <c r="F62" s="12" t="s">
@@ -3577,165 +3468,187 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.5">
-      <c r="A63" s="38">
+      <c r="A63" s="64">
         <v>1</v>
       </c>
-      <c r="B63" s="39" t="s">
+      <c r="B63" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D63" s="39" t="s">
+      <c r="D63" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="40"/>
-      <c r="F63" s="1" t="s">
+      <c r="E63" s="65"/>
+      <c r="F63" s="67" t="s">
         <v>22</v>
       </c>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
     </row>
     <row r="64" spans="1:8" ht="46.5">
-      <c r="A64" s="41">
+      <c r="A64" s="64">
         <v>2</v>
       </c>
-      <c r="B64" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" s="42" t="s">
+      <c r="B64" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="D64" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="43"/>
-      <c r="F64" s="1" t="s">
+      <c r="D64" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="65"/>
+      <c r="F64" s="67" t="s">
         <v>22</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="46.5">
-      <c r="A65" s="44"/>
-      <c r="B65" s="45"/>
-      <c r="C65" s="46" t="s">
+    <row r="65" spans="1:8" ht="16.5">
+      <c r="A65" s="64">
+        <v>3</v>
+      </c>
+      <c r="B65" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="1" t="s">
+      <c r="D65" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E65" s="65"/>
+      <c r="F65" s="63" t="s">
         <v>22</v>
       </c>
       <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-    </row>
-    <row r="66" spans="1:8" ht="46.5">
-      <c r="A66" s="41">
-        <v>3</v>
-      </c>
-      <c r="B66" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" s="42" t="s">
+      <c r="H65" s="49"/>
+    </row>
+    <row r="66" spans="1:8" ht="61.5">
+      <c r="A66" s="64">
+        <v>4</v>
+      </c>
+      <c r="B66" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="43"/>
-      <c r="F66" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66" s="20"/>
-      <c r="H66" s="72"/>
-    </row>
-    <row r="67" spans="1:8" ht="46.5">
-      <c r="A67" s="44"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="46" t="s">
+      <c r="D66" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="65"/>
+      <c r="F66" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="49"/>
+      <c r="H66" s="49"/>
+    </row>
+    <row r="67" spans="1:8" ht="16.5">
+      <c r="A67" s="64">
+        <v>5</v>
+      </c>
+      <c r="B67" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="73"/>
+      <c r="D67" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" s="65"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="49"/>
+      <c r="H67" s="49"/>
     </row>
     <row r="68" spans="1:8" ht="30.75">
-      <c r="A68" s="41">
-        <v>4</v>
-      </c>
-      <c r="B68" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C68" s="42" t="s">
+      <c r="A68" s="64">
+        <v>6</v>
+      </c>
+      <c r="B68" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="D68" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="43"/>
-      <c r="F68" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="72"/>
-      <c r="H68" s="72"/>
-    </row>
-    <row r="69" spans="1:8" ht="61.5">
-      <c r="A69" s="44"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="46" t="s">
+      <c r="D68" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="65"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+    </row>
+    <row r="69" spans="1:8" ht="30.75">
+      <c r="A69" s="64">
+        <v>7</v>
+      </c>
+      <c r="B69" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-    </row>
-    <row r="70" spans="1:8" ht="30.75">
-      <c r="A70" s="41">
-        <v>5</v>
-      </c>
-      <c r="B70" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" s="42" t="s">
+      <c r="D69" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="65"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+    </row>
+    <row r="70" spans="1:8" ht="16.5">
+      <c r="A70" s="64">
+        <v>8</v>
+      </c>
+      <c r="B70" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D70" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="43"/>
-      <c r="F70" s="70"/>
-      <c r="G70" s="72"/>
-      <c r="H70" s="72"/>
-    </row>
-    <row r="71" spans="1:8" ht="30.75">
-      <c r="A71" s="44"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="46" t="s">
+      <c r="D70" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E70" s="65"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+    </row>
+    <row r="71" spans="1:8" ht="92.25">
+      <c r="A71" s="64">
+        <v>9</v>
+      </c>
+      <c r="B71" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="71"/>
-      <c r="G71" s="73"/>
-      <c r="H71" s="73"/>
+      <c r="D71" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" s="65"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
     </row>
     <row r="72" spans="1:8" ht="15">
-      <c r="A72" s="9">
+      <c r="A72" s="70">
         <v>10</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="C72" s="64" t="s">
+      <c r="C72" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="D72" s="64"/>
-      <c r="E72" s="64"/>
+      <c r="D72" s="72"/>
+      <c r="E72" s="72"/>
       <c r="F72" s="9"/>
       <c r="G72" s="14"/>
       <c r="H72" s="15"/>
@@ -3853,7 +3766,7 @@
       <c r="B78" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="47" t="s">
+      <c r="C78" s="36" t="s">
         <v>95</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3957,39 +3870,39 @@
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="49"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="38"/>
     </row>
     <row r="84" spans="1:8" ht="15" customHeight="1">
-      <c r="A84" s="50">
+      <c r="A84" s="39">
         <v>11</v>
       </c>
-      <c r="B84" s="51" t="s">
+      <c r="B84" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C84" s="74" t="s">
+      <c r="C84" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="74"/>
-      <c r="E84" s="75"/>
+      <c r="D84" s="55"/>
+      <c r="E84" s="56"/>
       <c r="F84" s="9"/>
       <c r="G84" s="14"/>
       <c r="H84" s="15"/>
     </row>
     <row r="85" spans="1:8" ht="15">
-      <c r="A85" s="52" t="s">
+      <c r="A85" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B85" s="53" t="s">
+      <c r="B85" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C85" s="53" t="s">
+      <c r="C85" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="D85" s="53" t="s">
+      <c r="D85" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="E85" s="53" t="s">
+      <c r="E85" s="42" t="s">
         <v>6</v>
       </c>
       <c r="F85" s="12" t="s">
@@ -4003,19 +3916,19 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="15">
-      <c r="A86" s="54">
+      <c r="A86" s="43">
         <v>1</v>
       </c>
-      <c r="B86" s="55" t="s">
+      <c r="B86" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="55" t="s">
+      <c r="C86" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="D86" s="55" t="s">
+      <c r="D86" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E86" s="55" t="s">
+      <c r="E86" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -4025,19 +3938,19 @@
       <c r="H86" s="20"/>
     </row>
     <row r="87" spans="1:8" ht="15">
-      <c r="A87" s="60">
+      <c r="A87" s="58">
         <v>2</v>
       </c>
-      <c r="B87" s="62" t="s">
+      <c r="B87" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C87" s="55" t="s">
+      <c r="C87" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="D87" s="55" t="s">
+      <c r="D87" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E87" s="55" t="s">
+      <c r="E87" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F87" s="1" t="s">
@@ -4047,15 +3960,15 @@
       <c r="H87" s="20"/>
     </row>
     <row r="88" spans="1:8" ht="15">
-      <c r="A88" s="61"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="55" t="s">
+      <c r="A88" s="59"/>
+      <c r="B88" s="61"/>
+      <c r="C88" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="D88" s="55" t="s">
+      <c r="D88" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="55" t="s">
+      <c r="E88" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -4065,19 +3978,19 @@
       <c r="H88" s="20"/>
     </row>
     <row r="89" spans="1:8" ht="15">
-      <c r="A89" s="56">
+      <c r="A89" s="45">
         <v>3</v>
       </c>
-      <c r="B89" s="55" t="s">
+      <c r="B89" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="C89" s="55" t="s">
+      <c r="C89" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="D89" s="55" t="s">
+      <c r="D89" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E89" s="55" t="s">
+      <c r="E89" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F89" s="1" t="s">
@@ -4087,19 +4000,19 @@
       <c r="H89" s="20"/>
     </row>
     <row r="90" spans="1:8" ht="30.75">
-      <c r="A90" s="56">
+      <c r="A90" s="45">
         <v>4</v>
       </c>
-      <c r="B90" s="55" t="s">
+      <c r="B90" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="C90" s="55" t="s">
+      <c r="C90" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="D90" s="55" t="s">
+      <c r="D90" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E90" s="55" t="s">
+      <c r="E90" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F90" s="1" t="s">
@@ -4109,19 +4022,19 @@
       <c r="H90" s="20"/>
     </row>
     <row r="91" spans="1:8" ht="15">
-      <c r="A91" s="60">
+      <c r="A91" s="58">
         <v>5</v>
       </c>
-      <c r="B91" s="62" t="s">
+      <c r="B91" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="C91" s="55" t="s">
+      <c r="C91" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D91" s="55" t="s">
+      <c r="D91" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E91" s="55" t="s">
+      <c r="E91" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -4131,15 +4044,15 @@
       <c r="H91" s="20"/>
     </row>
     <row r="92" spans="1:8" ht="15">
-      <c r="A92" s="60"/>
-      <c r="B92" s="62"/>
-      <c r="C92" s="55" t="s">
+      <c r="A92" s="58"/>
+      <c r="B92" s="60"/>
+      <c r="C92" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="D92" s="55" t="s">
+      <c r="D92" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E92" s="55" t="s">
+      <c r="E92" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -4149,15 +4062,15 @@
       <c r="H92" s="20"/>
     </row>
     <row r="93" spans="1:8" ht="15">
-      <c r="A93" s="60"/>
-      <c r="B93" s="62"/>
-      <c r="C93" s="55" t="s">
+      <c r="A93" s="58"/>
+      <c r="B93" s="60"/>
+      <c r="C93" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="D93" s="55" t="s">
+      <c r="D93" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E93" s="55" t="s">
+      <c r="E93" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F93" s="1"/>
@@ -4165,15 +4078,15 @@
       <c r="H93" s="20"/>
     </row>
     <row r="94" spans="1:8" ht="15">
-      <c r="A94" s="61"/>
-      <c r="B94" s="63"/>
-      <c r="C94" s="55" t="s">
+      <c r="A94" s="59"/>
+      <c r="B94" s="61"/>
+      <c r="C94" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="D94" s="55" t="s">
+      <c r="D94" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="E94" s="55" t="s">
+      <c r="E94" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F94" s="1"/>
@@ -4187,11 +4100,11 @@
       <c r="B95" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C95" s="64" t="s">
+      <c r="C95" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="D95" s="64"/>
-      <c r="E95" s="64"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
       <c r="F95" s="9"/>
       <c r="G95" s="14"/>
       <c r="H95" s="15"/>
@@ -4249,7 +4162,7 @@
       <c r="B98" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C98" s="57" t="s">
+      <c r="C98" s="46" t="s">
         <v>119</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -4309,7 +4222,7 @@
       <c r="B101" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C101" s="47" t="s">
+      <c r="C101" s="36" t="s">
         <v>123</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -4329,7 +4242,7 @@
       <c r="B102" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="58" t="s">
+      <c r="C102" s="47" t="s">
         <v>124</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -4395,8 +4308,8 @@
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="48"/>
-      <c r="H105" s="49"/>
+      <c r="G105" s="37"/>
+      <c r="H105" s="38"/>
     </row>
     <row r="106" spans="1:8" ht="15">
       <c r="A106" s="9">
@@ -4405,11 +4318,11 @@
       <c r="B106" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C106" s="64" t="s">
+      <c r="C106" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="D106" s="64"/>
-      <c r="E106" s="64"/>
+      <c r="D106" s="54"/>
+      <c r="E106" s="54"/>
       <c r="F106" s="9"/>
       <c r="G106" s="14"/>
       <c r="H106" s="15"/>
@@ -4467,7 +4380,7 @@
       <c r="B109" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="57" t="s">
+      <c r="C109" s="46" t="s">
         <v>130</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -4527,7 +4440,7 @@
       <c r="B112" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="47" t="s">
+      <c r="C112" s="36" t="s">
         <v>134</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4547,7 +4460,7 @@
       <c r="B113" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="58" t="s">
+      <c r="C113" s="47" t="s">
         <v>135</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -4605,11 +4518,11 @@
       <c r="B116" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C116" s="64" t="s">
+      <c r="C116" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="D116" s="64"/>
-      <c r="E116" s="64"/>
+      <c r="D116" s="54"/>
+      <c r="E116" s="54"/>
       <c r="F116" s="9"/>
       <c r="G116" s="14"/>
       <c r="H116" s="15"/>
@@ -4667,7 +4580,7 @@
       <c r="B119" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C119" s="57" t="s">
+      <c r="C119" s="46" t="s">
         <v>140</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -4727,11 +4640,11 @@
       <c r="B122" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C122" s="64" t="s">
+      <c r="C122" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="D122" s="64"/>
-      <c r="E122" s="64"/>
+      <c r="D122" s="54"/>
+      <c r="E122" s="54"/>
       <c r="F122" s="9"/>
       <c r="G122" s="14"/>
       <c r="H122" s="15"/>
@@ -4789,7 +4702,7 @@
       <c r="B125" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C125" s="57" t="s">
+      <c r="C125" s="46" t="s">
         <v>145</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -4869,11 +4782,11 @@
       <c r="B129" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C129" s="66" t="s">
+      <c r="C129" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="D129" s="66"/>
-      <c r="E129" s="66"/>
+      <c r="D129" s="50"/>
+      <c r="E129" s="50"/>
       <c r="F129" s="9"/>
       <c r="G129" s="14"/>
       <c r="H129" s="15"/>
@@ -4931,7 +4844,7 @@
       <c r="B132" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C132" s="57" t="s">
+      <c r="C132" s="46" t="s">
         <v>152</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -5031,11 +4944,11 @@
       <c r="B137" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C137" s="66" t="s">
+      <c r="C137" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="D137" s="66"/>
-      <c r="E137" s="66"/>
+      <c r="D137" s="50"/>
+      <c r="E137" s="50"/>
       <c r="F137" s="9"/>
       <c r="G137" s="14"/>
       <c r="H137" s="15"/>
@@ -5073,7 +4986,7 @@
       <c r="B139" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C139" s="57" t="s">
+      <c r="C139" s="46" t="s">
         <v>160</v>
       </c>
       <c r="D139" s="1" t="s">
@@ -5138,25 +5051,18 @@
     <row r="173" ht="15"/>
     <row r="174" ht="15"/>
     <row r="175" ht="15"/>
+    <row r="176" ht="15"/>
+    <row r="178" ht="15"/>
+    <row r="179" ht="15"/>
+    <row r="180" ht="15"/>
   </sheetData>
   <autoFilter ref="A3:H32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="28">
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C122:E122"/>
+  <mergeCells count="20">
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="C95:E95"/>
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="C45:E45"/>
     <mergeCell ref="C27:E27"/>
@@ -5164,32 +5070,24 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="B91:B94"/>
-    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C122:E122"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F1 F72:F1048576 F3:F60">
-    <cfRule type="cellIs" dxfId="5" priority="67" operator="equal">
+  <conditionalFormatting sqref="F1 F3:F1048576">
+    <cfRule type="cellIs" dxfId="2" priority="67" operator="equal">
       <formula>"ongoing"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="68" operator="equal">
       <formula>"done"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="69" operator="equal">
-      <formula>"open"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F61:F66 F68 F70">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"ongoing"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"done"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="69" operator="equal">
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5217,16 +5115,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -5384,12 +5282,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5398,14 +5290,20 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD8C9434-3855-4EFD-872A-412CC9B888D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}"/>
 </file>